--- a/cuijpers_mmc3_overlap.xlsx
+++ b/cuijpers_mmc3_overlap.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>mmc3 Excluded Study ID (raw)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mmc3 Reason for Exclusion</t>
         </is>
       </c>
@@ -457,6 +462,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>A-Tjak 2018</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -479,6 +489,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Aagaard 2017</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -496,10 +511,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Alexopoulos 2003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Alexopoulos 2003a</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Conference abstract</t>
         </is>
@@ -523,6 +543,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Ayen 2004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Non-English language paper</t>
         </is>
       </c>
@@ -540,10 +565,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Barber 2012</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Barber 2012/Zilcha-Mano 2014</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Population: &gt;20% have coexisting personality disorder</t>
         </is>
@@ -567,6 +597,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Barnhofer 2009</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
@@ -574,7 +609,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Barret, 2001</t>
+          <t>Barrett, 2001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,6 +623,11 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>Barrett 2001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
@@ -611,6 +651,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Berger 2011</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -633,6 +678,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Bodenmann 2008</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
@@ -650,10 +700,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Bolton 2003</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Bolton 2003/Bass 2006</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Baseline severity cannot be categorised</t>
         </is>
@@ -677,6 +732,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Bright 1999</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -699,6 +759,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Brown 1984</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -721,6 +786,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Carr 2017</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -743,6 +813,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Carta 2012</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
@@ -765,6 +840,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Carter 2013</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Population: &gt;20% have coexisting personality disorder</t>
         </is>
       </c>
@@ -787,6 +867,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Castonguay 2004</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Design: Non-RCT</t>
         </is>
       </c>
@@ -804,10 +889,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Chan 2012</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>Chan 2012a</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Population: Further-line treatment</t>
         </is>
@@ -831,6 +921,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Chan 2013</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
@@ -853,6 +948,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Chiang 2015</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -875,6 +975,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Cho 2008</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Population: Antenatal or postnatal depression</t>
         </is>
       </c>
@@ -897,6 +1002,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Chowdhary 2016</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Baseline severity cannot be categorised</t>
         </is>
       </c>
@@ -919,6 +1029,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Choy 2016</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
@@ -936,10 +1051,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Collado 2016</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Collado 2016a</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
@@ -963,6 +1083,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Cooper 2003</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>Population: Antenatal or postnatal depression</t>
         </is>
       </c>
@@ -985,6 +1110,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>Cramer 2011</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -1007,6 +1137,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>DeRubeis 2005</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
@@ -1029,6 +1164,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>Dekker 2012</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
@@ -1051,6 +1191,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Delgadillo 2015</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -1073,6 +1218,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Dimidjian 2006</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
@@ -1095,6 +1245,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Dowrick 2000</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -1112,10 +1267,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Driessen 2013</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>Driessen 2013/2016</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
@@ -1139,6 +1299,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Duarte 2009</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
@@ -1161,6 +1326,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>Dwight-Johnson 2011</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -1183,6 +1353,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Ekeblad 2016</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>Population: Further-line treatment</t>
         </is>
       </c>
@@ -1205,6 +1380,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>Ekers 2011</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -1227,6 +1407,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Ekkers 2011</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -1234,108 +1419,133 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Elkin, 1989</t>
+          <t>Embling, 2002</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Elkin I, Shea MT, Watkins JT, Imber SD, Sotsky SM, Collins JF, et al. National institute of mental health treatment of depression collaborative research program. General effectiveness of treatments. Archives of General Psychiatry. 1989;46(11):971-82; discussion 83.</t>
+          <t>Embling S. The effectiveness of cognitive behavioural therapy in depression. Nursing Standard. 2002;17(14-15):33-41.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Elkin 1995</t>
+          <t>Embling 2002</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Secondary analysis with no new relevant or usable data</t>
+          <t>Embling 2002</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Population: Further-line treatment</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Embling, 2002</t>
+          <t>Euteneuer, 2017</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Embling S. The effectiveness of cognitive behavioural therapy in depression. Nursing Standard. 2002;17(14-15):33-41.</t>
+          <t>Euteneuer, F., Dannehl, K., Del Rey, A., Engler, H., Schedlowski, M., &amp; Rief, W. (2017). Immunological effects of behavioral activation with exercise in major depression: An exploratory randomized controlled trial. Translational Psychiatry, 7(5).</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Embling 2002</t>
+          <t>Euteneuer 2017</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Population: Further-line treatment</t>
+          <t>Euteneuer 2017</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Euteneuer, 2017</t>
+          <t>Faramarzi, 2008</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Euteneuer, F., Dannehl, K., Del Rey, A., Engler, H., Schedlowski, M., &amp; Rief, W. (2017). Immunological effects of behavioral activation with exercise in major depression: An exploratory randomized controlled trial. Translational Psychiatry, 7(5).</t>
+          <t>Faramarzi M, Alipor A, Esmaelzadeh S, Kheirkhah F, Poladi K, Pash H. Treatment of depression and anxiety in infertile women: Cognitive behavioral therapy versus fluoxetine. Journal of Affective Disorders. 2008;108(1-2):159-64.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Euteneuer 2017</t>
+          <t>Faramarzi 2008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Faramarzi 2008</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Faramarzi, 2008</t>
+          <t>Floyd, 2004</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Faramarzi M, Alipor A, Esmaelzadeh S, Kheirkhah F, Poladi K, Pash H. Treatment of depression and anxiety in infertile women: Cognitive behavioral therapy versus fluoxetine. Journal of Affective Disorders. 2008;108(1-2):159-64.</t>
+          <t>Floyd M, Scogin F, McKendree-Smith NL, Floyd DL, Rokke PD. Cognitive therapy for depression: A comparison of individual psychotherapy and bibliotherapy for depressed older adults. Behavior modification. 2004;28(2):297-318.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faramarzi 2008</t>
+          <t>Floyd 2004</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
+          <t>Floyd 2004</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Floyd, 2004</t>
+          <t>Folke, 2012</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Floyd M, Scogin F, McKendree-Smith NL, Floyd DL, Rokke PD. Cognitive therapy for depression: A comparison of individual psychotherapy and bibliotherapy for depressed older adults. Behavior modification. 2004;28(2):297-318.</t>
+          <t>Folke F, Parling T, Melin L. Acceptance and commitment therapy for depression: A preliminary randomized clinical trial for unemployed on long-term sick leave. Cognitive and Behavioral Practice. 2012;19(4):583-94.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Floyd 2004</t>
+          <t>Folke 2012</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
+        <is>
+          <t>Folke 2012</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
@@ -1344,218 +1554,268 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Folke, 2012</t>
+          <t>Freire, 2015</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Folke F, Parling T, Melin L. Acceptance and commitment therapy for depression: A preliminary randomized clinical trial for unemployed on long-term sick leave. Cognitive and Behavioral Practice. 2012;19(4):583-94.</t>
+          <t>Freire E, Williams C, Messow C-M, Cooper M, Elliott R, McConnachie A, et al. Counselling versus low-intensity cognitive behavioural therapy for persistent sub-threshold and mild depression (CLICD): A pilot/feasibility randomised controlled trial. BMC psychiatry. 2015;15.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Folke 2012</t>
+          <t>Freire 2015</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Freire 2015</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Freire, 2015</t>
+          <t>Furukawa, 2012</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Freire E, Williams C, Messow C-M, Cooper M, Elliott R, McConnachie A, et al. Counselling versus low-intensity cognitive behavioural therapy for persistent sub-threshold and mild depression (CLICD): A pilot/feasibility randomised controlled trial. BMC psychiatry. 2015;15.</t>
+          <t>Furukawa TA, Horikoshi M, Kawakami N, Kadota M, Sasaki M, Sekiya Y, et al. Telephone cognitive-behavioral therapy for subthreshold depression and presenteeism in workplace: A randomized controlled trial. PLoS One. 2012;7(4):e35330.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Freire 2015</t>
+          <t>Furukawa 2012</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Furukawa 2012</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Furukawa, 2012</t>
+          <t>Gellis, 2008</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Furukawa TA, Horikoshi M, Kawakami N, Kadota M, Sasaki M, Sekiya Y, et al. Telephone cognitive-behavioral therapy for subthreshold depression and presenteeism in workplace: A randomized controlled trial. PLoS One. 2012;7(4):e35330.</t>
+          <t>Gellis ZD, McGinty J, Tierney L, Jordan C, Burton J, Misener E. Randomized controlled trial of problem-solving therapy for minor depression in home care. Research on Social Work Practice. 2008;18(6):596-606.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Furukawa 2012</t>
+          <t>Gellis 2008</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest</t>
+          <t>Gellis 2008</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gellis, 2008</t>
+          <t>Geraedts, 2014</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gellis ZD, McGinty J, Tierney L, Jordan C, Burton J, Misener E. Randomized controlled trial of problem-solving therapy for minor depression in home care. Research on Social Work Practice. 2008;18(6):596-606.</t>
+          <t>Geraedts AS, Kleiboer AM, Wiezer NM, van Mechelen W, Cuijpers P. Short-term effects of a web-based guided self-help intervention for employees with depressive symptoms: Randomized controlled trial. Journal of Medical Internet Research. 2014;16(5):e121.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gellis 2008</t>
+          <t>Geraedts 2014</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
+          <t>Geraedts 2014c</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Secondary analysis with no new relevant or usable data</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Geraedts, 2014</t>
+          <t>Hagen, 2017</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Geraedts AS, Kleiboer AM, Wiezer NM, van Mechelen W, Cuijpers P. Short-term effects of a web-based guided self-help intervention for employees with depressive symptoms: Randomized controlled trial. Journal of Medical Internet Research. 2014;16(5):e121.</t>
+          <t>Hagen, R., Hjemdal, O., Solem, S., Kennair, L. E. O., Nordahl, H. M., Fisher, P., &amp; Wells, A. (2017). Metacognitive therapy for depression in adults: A waiting list randomized controlled trial with six months follow-up. Frontiers in Psychology, 8.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Geraedts 2014c</t>
+          <t>Hagen 2017</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Secondary analysis with no new relevant or usable data</t>
+          <t>Hagen 2017</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Population: &gt;20% have coexisting personality disorder</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hagen, 2017</t>
+          <t>Hallford, 2016</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hagen, R., Hjemdal, O., Solem, S., Kennair, L. E. O., Nordahl, H. M., Fisher, P., &amp; Wells, A. (2017). Metacognitive therapy for depression in adults: A waiting list randomized controlled trial with six months follow-up. Frontiers in Psychology, 8.</t>
+          <t>Hallford DJ, Mellor D. Autobiographical memory-based intervention for depressive symptoms in young adults: A randomized controlled trial of cognitive-reminiscence therapy. Psychotherapy and Psychosomatics. 2016;85(4):246-9.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hagen 2017</t>
+          <t>Hallford 2016</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Population: &gt;20% have coexisting personality disorder</t>
+          <t>Hallford 2016</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hallford, 2016</t>
+          <t>Hallgren, 2015</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hallford DJ, Mellor D. Autobiographical memory-based intervention for depressive symptoms in young adults: A randomized controlled trial of cognitive-reminiscence therapy. Psychotherapy and Psychosomatics. 2016;85(4):246-9.</t>
+          <t>Hallgren M, Kraepelien M, Öjehagen A, Lindefors N, Zeebari Z, Kaldo V, et al. Physical exercise and internet-based cognitive-behavioural therapy in the treatment of depression: Randomised controlled trial. British Journal of Psychiatry. 2015;207(3):227-34.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hallford 2016</t>
+          <t>Hallgren 2015</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest</t>
+          <t>Hallgren 2015/2016_Helgadottir 2016/2017</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hallgren, 2015</t>
+          <t>Harley, 2008</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hallgren M, Kraepelien M, Öjehagen A, Lindefors N, Zeebari Z, Kaldo V, et al. Physical exercise and internet-based cognitive-behavioural therapy in the treatment of depression: Randomised controlled trial. British Journal of Psychiatry. 2015;207(3):227-34.</t>
+          <t>Harley R, Sprich S, Safren S, Jacobo M, Fava M. Adaptation of dialectical behavior therapy skills training group for treatment-resistant depression. Journal of Nervous and Mental Disease. 2008;196(2):136-43.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hallgren 2015/2016_Helgadottir 2016/2017</t>
+          <t>Harley 2008</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Harley 2008</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Population: Further-line treatment</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Harley, 2008</t>
+          <t>Hautzinger, 2004</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Harley R, Sprich S, Safren S, Jacobo M, Fava M. Adaptation of dialectical behavior therapy skills training group for treatment-resistant depression. Journal of Nervous and Mental Disease. 2008;196(2):136-43.</t>
+          <t>Hautzinger M, Welz S. Kognitive Verhaltenstherapie bei Depressionen im Alter: Ergebnisse einer kontrollierten Vergleichsstudie unter ambulanten Bedingungen an Depressionen mittleren Schweregrads. = Cognitive behavioral therapy for depressed older outpatients: A controlled, randomized trial. Zeitschrift für Gerontologie und Geriatrie. 2004;37(6):427-35.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harley 2008</t>
+          <t>Hautzinger 2004</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Population: Further-line treatment</t>
+          <t>Hautzinger 2004</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Non-English language paper</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hautzinger, 2004</t>
+          <t>Hautzinger, 2008</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hautzinger M, Welz S. Kognitive Verhaltenstherapie bei Depressionen im Alter: Ergebnisse einer kontrollierten Vergleichsstudie unter ambulanten Bedingungen an Depressionen mittleren Schweregrads. = Cognitive behavioral therapy for depressed older outpatients: A controlled, randomized trial. Zeitschrift für Gerontologie und Geriatrie. 2004;37(6):427-35.</t>
+          <t>Hautzinger M, Welz S. Kurz- und längerfristige wirksamkeit psychologischer interventionen bei depressionen im alter. = Short- and long-term efficacy of psychological intervention for depression in older adults. Zeitschrift für Klinische Psychologie und Psychotherapie: Forschung und Praxis. 2008;37(1):52-60.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hautzinger 2004</t>
+          <t>Hautzinger 2008</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
+        <is>
+          <t>Hautzinger 2008</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>Non-English language paper</t>
         </is>
@@ -1564,174 +1824,214 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Hautzinger, 2008</t>
+          <t>Hayden, 2012</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hautzinger M, Welz S. Kurz- und längerfristige wirksamkeit psychologischer interventionen bei depressionen im alter. = Short- and long-term efficacy of psychological intervention for depression in older adults. Zeitschrift für Klinische Psychologie und Psychotherapie: Forschung und Praxis. 2008;37(1):52-60.</t>
+          <t>Hayden T, Perantie DC, Nix BD, Barnes LD, Mostello DJ, Holcomb WL, et al. Treating prepartum depression to improve infant developmental outcomes: A study of diabetes in pregnancy. Journal of clinical psychology in medical settings. 2012;19(3):285-92.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hautzinger 2008</t>
+          <t>Hayden 2012</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Non-English language paper</t>
+          <t>Hayden 2012</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Population: Antenatal or postnatal depression</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hayden, 2012</t>
+          <t>Hegerl, 2010</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hayden T, Perantie DC, Nix BD, Barnes LD, Mostello DJ, Holcomb WL, et al. Treating prepartum depression to improve infant developmental outcomes: A study of diabetes in pregnancy. Journal of clinical psychology in medical settings. 2012;19(3):285-92.</t>
+          <t>Hegerl U, Hautzinger M, Mergl R, Kohnen R, Sch¸tze M, Scheunemann W, et al. Effects of pharmacotherapy and psychotherapy in depressed primary-care patients: A randomized, controlled trial including a patients' choice arm. International Journal of Neuropsychopharmacology. 2010;13(1):31-44.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hayden 2012</t>
+          <t>Hegerl 2010</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Population: Antenatal or postnatal depression</t>
+          <t>Hegerl 2010</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hegerl, 2010</t>
+          <t>Hemanny, 2019</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hegerl U, Hautzinger M, Mergl R, Kohnen R, Sch¸tze M, Scheunemann W, et al. Effects of pharmacotherapy and psychotherapy in depressed primary-care patients: A randomized, controlled trial including a patients' choice arm. International Journal of Neuropsychopharmacology. 2010;13(1):31-44.</t>
+          <t>Hemanny, C., Carvalho, C., Maia, N., Reis, D., Botelho, A. C., Bonavides, D., . . . De Oliveira, I. R. (2019). Efficacy of trial-based cognitive therapy, behavioral activation and treatment as usual in the treatment of major depressive disorder: Preliminary findings from a randomized clinical trial. CNS Spectrums. doi:10.1017/S1092852919001457</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hegerl 2010</t>
+          <t>Hemanny 2019</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Hemanny 2019</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Population: Further-line treatment</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hemanny, 2019</t>
+          <t>Hoifodt, 2013</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hemanny, C., Carvalho, C., Maia, N., Reis, D., Botelho, A. C., Bonavides, D., . . . De Oliveira, I. R. (2019). Efficacy of trial-based cognitive therapy, behavioral activation and treatment as usual in the treatment of major depressive disorder: Preliminary findings from a randomized clinical trial. CNS Spectrums. doi:10.1017/S1092852919001457</t>
+          <t>Hoifodt, R. S., Lillevoll, K. R., Griffiths, K. M., Wilsgaard, T., Eisemann, M., Waterloo, K., &amp; Kolstrup, N. (2013). The clinical effectiveness of web-based cognitive behavioral therapy with face-to-face therapist support for depressed primary care patients: randomized controlled trial. J Med Internet Res, 15(8), e153. doi:10.2196/jmir.2714</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hemanny 2019</t>
+          <t>Hoifodt 2013</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Population: Further-line treatment</t>
+          <t>Hoifodt 2013</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hoifodt, 2013</t>
+          <t>Hopko, 2011</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hoifodt, R. S., Lillevoll, K. R., Griffiths, K. M., Wilsgaard, T., Eisemann, M., Waterloo, K., &amp; Kolstrup, N. (2013). The clinical effectiveness of web-based cognitive behavioral therapy with face-to-face therapist support for depressed primary care patients: randomized controlled trial. J Med Internet Res, 15(8), e153. doi:10.2196/jmir.2714</t>
+          <t>Hopko DR, Armento ME, Robertson SM, Ryba MM, Carvalho JP, Colman LK, et al. Brief behavioral activation and problem-solving therapy for depressed breast cancer patients: Randomized trial. Journal of Consulting and Clinical Psychology. 2011;79(6):834-49.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hoifodt 2013</t>
+          <t>Hopko 2011</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Hopko 2011</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hopko, 2011</t>
+          <t>Horrell, 2014</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hopko DR, Armento ME, Robertson SM, Ryba MM, Carvalho JP, Colman LK, et al. Brief behavioral activation and problem-solving therapy for depressed breast cancer patients: Randomized trial. Journal of Consulting and Clinical Psychology. 2011;79(6):834-49.</t>
+          <t>Horrell L, Goldsmith KA, Tylee AT, Schmidt UH, Murphy CL, Bonin E-M, et al. One-day cognitive–behavioural therapy self-confidence workshops for people with depression: Randomised controlled trial. The British Journal of Psychiatry. 2014;204(3):222-33.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hopko 2011</t>
+          <t>Horrell 2014</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
+          <t>Horrell 2014</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Horrell, 2014</t>
+          <t>Johansson, 2012 - I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Horrell L, Goldsmith KA, Tylee AT, Schmidt UH, Murphy CL, Bonin E-M, et al. One-day cognitive–behavioural therapy self-confidence workshops for people with depression: Randomised controlled trial. The British Journal of Psychiatry. 2014;204(3):222-33.</t>
+          <t>Johansson R, Ekbladh S, Hebert A, Lindström M, Möller S, Petitt E, et al. Psychodynamic guided self-help for adult depression through the internet: A randomised controlled trial. PloS One. 2012;7(5):e38021.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Horrell 2014</t>
+          <t>Johansson 2012</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest</t>
+          <t>Johansson 2012a</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Johansson, 2012 - I</t>
+          <t>Jordans, 2019</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Johansson R, Ekbladh S, Hebert A, Lindström M, Möller S, Petitt E, et al. Psychodynamic guided self-help for adult depression through the internet: A randomised controlled trial. PloS One. 2012;7(5):e38021.</t>
+          <t>Jordans, M. J. D., Luitel, N. P., Garman, E., Kohrt, B. A., Rathod, S. D., Shrestha, P., . . . Patel, V. (2019). Effectiveness of psychological treatments for depression and alcohol use disorder delivered by community-based counsellors: Two pragmatic randomised controlled trials within primary healthcare in Nepal. British Journal of Psychiatry, 215(2), 485-493. doi:10.1192/bjp.2018.300</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Johansson 2012a</t>
+          <t>Jordans 2019</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
+        <is>
+          <t>Jordans 2019</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
@@ -1740,64 +2040,79 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jordans, 2019</t>
+          <t>Kay-Lambkin, 2011</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jordans, M. J. D., Luitel, N. P., Garman, E., Kohrt, B. A., Rathod, S. D., Shrestha, P., . . . Patel, V. (2019). Effectiveness of psychological treatments for depression and alcohol use disorder delivered by community-based counsellors: Two pragmatic randomised controlled trials within primary healthcare in Nepal. British Journal of Psychiatry, 215(2), 485-493. doi:10.1192/bjp.2018.300</t>
+          <t>Kay-Lambkin FJ, Baker AL, Kelly B, Lewin TJ. Clinician-assisted computerised versus therapist-delivered treatment for depressive and addictive disorders: A randomised controlled trial. The Medical journal of Australia. 2011;195(3):S44-50.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordans 2019</t>
+          <t>Kay-Lambkin 2011</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Kay-Lambkin 2011</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Secondary analysis with no new relevant or usable data</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kay-Lambkin, 2011</t>
+          <t>Kenter, 2016</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kay-Lambkin FJ, Baker AL, Kelly B, Lewin TJ. Clinician-assisted computerised versus therapist-delivered treatment for depressive and addictive disorders: A randomised controlled trial. The Medical journal of Australia. 2011;195(3):S44-50.</t>
+          <t>Kenter, R. M. F., Cuijpers, P., Beekman, A., &amp; van Straten, A. (2016). Effectiveness of a Web-based guided self-help intervention for outpatients with a depressive disorder: Short-term results from a randomized controlled trial. Journal of medical Internet research, 18(3).</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kay-Lambkin 2011</t>
+          <t>Kenter 2016</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Secondary analysis with no new relevant or usable data</t>
+          <t>Kenter 2016</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kenter, 2016</t>
+          <t>Kessler, 2009</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kenter, R. M. F., Cuijpers, P., Beekman, A., &amp; van Straten, A. (2016). Effectiveness of a Web-based guided self-help intervention for outpatients with a depressive disorder: Short-term results from a randomized controlled trial. Journal of medical Internet research, 18(3).</t>
+          <t>Kessler D, Lewis G, Kaur S, Wiles N, King M, Weich S, et al. Therapist-delivered Internet psychotherapy for depression in primary care: A randomised controlled trial. Lancet. 2009;374(9690):628-34.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kenter 2016</t>
+          <t>Kessler 2009</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
+        <is>
+          <t>Kessler 2009</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
@@ -1806,20 +2121,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kessler, 2009</t>
+          <t>Kivi, 2014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kessler D, Lewis G, Kaur S, Wiles N, King M, Weich S, et al. Therapist-delivered Internet psychotherapy for depression in primary care: A randomised controlled trial. Lancet. 2009;374(9690):628-34.</t>
+          <t>Kivi M, Eriksson MCM, Hange D, Petersson E-L, Vernmark K, Johansson B, et al. Internet-based therapy for mild to moderate depression in Swedish primary care: Short term results from the PRIM-NET randomized controlled trial. Cognitive Behaviour Therapy. 2014;43(4):289-98.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kessler 2009</t>
+          <t>Kivi 2014</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
+        <is>
+          <t>Kivi 2014/Eriksson 2017/Hange 2017</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
@@ -1828,86 +2148,106 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kivi, 2014</t>
+          <t>Kleiboer, 2015</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Kivi M, Eriksson MCM, Hange D, Petersson E-L, Vernmark K, Johansson B, et al. Internet-based therapy for mild to moderate depression in Swedish primary care: Short term results from the PRIM-NET randomized controlled trial. Cognitive Behaviour Therapy. 2014;43(4):289-98.</t>
+          <t>Kleiboer A, Donker T, Seekles W, van Straten A, Riper H, Cuijpers P. A randomized controlled trial on the role of support in Internet-based problem solving therapy for depression and anxiety. Behaviour Research and Therapy. 2015;72:63-71.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kivi 2014/Eriksson 2017/Hange 2017</t>
+          <t>Kleiboer 2015</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Kleiboer 2015</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Completion data &lt;50%/&gt;50% left treatment early</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kleiboer, 2015</t>
+          <t>Korte, 2012</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kleiboer A, Donker T, Seekles W, van Straten A, Riper H, Cuijpers P. A randomized controlled trial on the role of support in Internet-based problem solving therapy for depression and anxiety. Behaviour Research and Therapy. 2015;72:63-71.</t>
+          <t>Korte J, Bohlmeijer ET, Cappeliez P, Smit F, Westerhof GJ. Life review therapy for older adults with moderate depressive symptomatology: A pragmatic randomized controlled trial. Psychological Medicine. 2012;42(6):1163-73.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kleiboer 2015</t>
+          <t>Korte 2012</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Completion data &lt;50%/&gt;50% left treatment early</t>
+          <t>Korte 2012</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Korte, 2012</t>
+          <t>Koszycki, 2012</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Korte J, Bohlmeijer ET, Cappeliez P, Smit F, Westerhof GJ. Life review therapy for older adults with moderate depressive symptomatology: A pragmatic randomized controlled trial. Psychological Medicine. 2012;42(6):1163-73.</t>
+          <t>Koszycki D, Bisserbe J-C, Blier P, Bradwejn J, Markowitz J. Interpersonal psychotherapy versus brief supportive therapy for depressed infertile women: First pilot randomized controlled trial. Archives of Women's Mental Health. 2012;15(3):193-201.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Korte 2012</t>
+          <t>Koszycki 2012</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest</t>
+          <t>Koszycki 2012</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Koszycki, 2012</t>
+          <t>Landreville, 1997</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Koszycki D, Bisserbe J-C, Blier P, Bradwejn J, Markowitz J. Interpersonal psychotherapy versus brief supportive therapy for depressed infertile women: First pilot randomized controlled trial. Archives of Women's Mental Health. 2012;15(3):193-201.</t>
+          <t>Landreville P, Bissonnette L. Effects of cognitive bibliotherapy for depressed older adults with a disability. Clinical Gerontologist. 1997;17(4):35-55.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Koszycki 2012</t>
+          <t>Landreville 1997</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
+        <is>
+          <t>Landreville 1997</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
@@ -1916,218 +2256,268 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Landreville, 1997</t>
+          <t>Lappalainen, 2015</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Landreville P, Bissonnette L. Effects of cognitive bibliotherapy for depressed older adults with a disability. Clinical Gerontologist. 1997;17(4):35-55.</t>
+          <t>Lappalainen P, Langrial S, Oinas-Kukkonen H, Tolvanen A, Lappalainen R. Web-based acceptance and commitment therapy for depressive symptoms with minimal support: A randomized controlled trial. Behavior modification. 2015;39(6):805-34.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Landreville 1997</t>
+          <t>Lappalainen 2015</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
+          <t>Lappalainen 2015</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Lappalainen, 2015</t>
+          <t>Lemmens, 2015</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lappalainen P, Langrial S, Oinas-Kukkonen H, Tolvanen A, Lappalainen R. Web-based acceptance and commitment therapy for depressive symptoms with minimal support: A randomized controlled trial. Behavior modification. 2015;39(6):805-34.</t>
+          <t>Lemmens LHJM, Arntz A, Peeters F, Hollon SD, Roefs A, Huibers MJH. Clinical effectiveness of cognitive therapy v. interpersonal psychotherapy for depression: Results of a randomized controlled trial. Psychological Medicine. 2015;45(10):2095-110.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lappalainen 2015</t>
+          <t>Lemmens 2015</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Lemmens 2015/2019</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Population: &gt;20% have coexisting personality disorder</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lemmens, 2015</t>
+          <t>Lexis, 2011</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lemmens LHJM, Arntz A, Peeters F, Hollon SD, Roefs A, Huibers MJH. Clinical effectiveness of cognitive therapy v. interpersonal psychotherapy for depression: Results of a randomized controlled trial. Psychological Medicine. 2015;45(10):2095-110.</t>
+          <t>Lexis MA, Jansen NW, Huibers MJ, Amelsvoort LG, Berkouwer A, Tjin ATG, et al. Prevention of long-term sickness absence and major depression in high-risk employees: A randomised controlled trial. Occupational and Environmental Medicine. 2011;68(6):400-7.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lemmens 2015/2019</t>
+          <t>Lexis 2011</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Population: &gt;20% have coexisting personality disorder</t>
+          <t>Lexis 2011</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Setting not relevant</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Lexis, 2011</t>
+          <t>Liu, 2009</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lexis MA, Jansen NW, Huibers MJ, Amelsvoort LG, Berkouwer A, Tjin ATG, et al. Prevention of long-term sickness absence and major depression in high-risk employees: A randomised controlled trial. Occupational and Environmental Medicine. 2011;68(6):400-7.</t>
+          <t>Liu ET-H, Chen W-L, Li Y-H, Wang CH, Mok TJ, Huang HS. Exploring the efficacy of cognitive bibliotherapy and a potential mechanism of change in the treatment of depressive symptoms among the Chinese: A randomized controlled trial. Cognitive Therapy and Research. 2009;33(5):449-61.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lexis 2011</t>
+          <t>Liu 2009</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Setting not relevant</t>
+          <t>Liu 2009b</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Outcome(s) not of interest</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Liu, 2009</t>
+          <t>Lovell, 2008</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Liu ET-H, Chen W-L, Li Y-H, Wang CH, Mok TJ, Huang HS. Exploring the efficacy of cognitive bibliotherapy and a potential mechanism of change in the treatment of depressive symptoms among the Chinese: A randomized controlled trial. Cognitive Therapy and Research. 2009;33(5):449-61.</t>
+          <t>Lovell K, Bower P, Richards D, Barkham Mi, Sibbald B, Roberts C, et al. Developing guided self-help for depression using the medical research council complex interventions framework: A description of the modelling phase and results of an exploratory randomised controlled trial. BMC psychiatry. 2008;8.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Liu 2009b</t>
+          <t>Lovell 2008</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Outcome(s) not of interest</t>
+          <t>Lovell 2008</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lovell, 2008</t>
+          <t>Luty, 2007</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lovell K, Bower P, Richards D, Barkham Mi, Sibbald B, Roberts C, et al. Developing guided self-help for depression using the medical research council complex interventions framework: A description of the modelling phase and results of an exploratory randomised controlled trial. BMC psychiatry. 2008;8.</t>
+          <t>Luty SE, Carter JD, McKenzie JM, Rae AM, Frampton CM, Mulder RT, et al. Randomised controlled trial of interpersonal psychotherapy and cognitive-behavioural therapy for depression. The British Journal of Psychiatry. 2007;190:496-502.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lovell 2008</t>
+          <t>Luty 2007</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Luty 2007</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Luty, 2007</t>
+          <t>Ly, 2014</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Luty SE, Carter JD, McKenzie JM, Rae AM, Frampton CM, Mulder RT, et al. Randomised controlled trial of interpersonal psychotherapy and cognitive-behavioural therapy for depression. The British Journal of Psychiatry. 2007;190:496-502.</t>
+          <t>Ly KH, Truschel A, Jarl L, Magnusson S, Windahl T, Johansson R, et al. Behavioural activation versus mindfulness-based guided self-help treatment administered through a smartphone application: A randomised controlled trial. BMJ Open. 2014;4(1):e003440.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Luty 2007</t>
+          <t>Ly 2014</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Ly 2014</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ly, 2014</t>
+          <t>Lynch, 2004</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ly KH, Truschel A, Jarl L, Magnusson S, Windahl T, Johansson R, et al. Behavioural activation versus mindfulness-based guided self-help treatment administered through a smartphone application: A randomised controlled trial. BMJ Open. 2014;4(1):e003440.</t>
+          <t>Lynch D, Tamburrino M, Nagel R, Smith MK. Telephone-based treatment for family practice patients with mild depression. Psychological reports. 2004;94(3 Pt 1):785-92.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ly 2014</t>
+          <t>Lynch 2004</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Lynch 2004</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lynch, 2004</t>
+          <t>MacPherson, 2013</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lynch D, Tamburrino M, Nagel R, Smith MK. Telephone-based treatment for family practice patients with mild depression. Psychological reports. 2004;94(3 Pt 1):785-92.</t>
+          <t>MacPherson H, Richmond S, Bland M, Brealey S, Gabe R, Hopton A, et al. Acupuncture and counselling for depression in primary care: A randomised controlled trial. PLoS medicine. 2013;10(9):e1001518.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lynch 2004</t>
+          <t>MacPherson 2013</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>MacPherson 2013</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MacPherson, 2013</t>
+          <t>Manicavasgar, 2011</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MacPherson H, Richmond S, Bland M, Brealey S, Gabe R, Hopton A, et al. Acupuncture and counselling for depression in primary care: A randomised controlled trial. PLoS medicine. 2013;10(9):e1001518.</t>
+          <t>Manicavasgar V, Parker G, Perich T. Mindfulness-based cognitive therapy vs cognitive behaviour therapy as a treatment for non-melancholic depression. Journal of Affective Disorders. 2011;130(1):138-44.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MacPherson 2013</t>
+          <t>Manicavasgar 2011</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
+        <is>
+          <t>Manicavasgar 2011/2012</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
@@ -2136,22 +2526,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Manicavasgar, 2011</t>
+          <t>Martin, 2015</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Manicavasgar V, Parker G, Perich T. Mindfulness-based cognitive therapy vs cognitive behaviour therapy as a treatment for non-melancholic depression. Journal of Affective Disorders. 2011;130(1):138-44.</t>
+          <t>Martin PR, Aiello R, Gilson K, Meadows G, Milgrom J, Reece J. Cognitive behavior therapy for comorbid migraine and/or tension-type headache and major depressive disorder: An exploratory randomized controlled trial. Behaviour Research and Therapy. 2015;73:8-18.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Manicavasgar 2011/2012</t>
+          <t>Martin 2015</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Martiny 2015</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Intervention: Physical intervention not of interest (only 1 arm meets inclusion criteria)</t>
         </is>
       </c>
     </row>
@@ -2173,6 +2568,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>Matsuzaka 2017</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Data cannot be extracted</t>
         </is>
       </c>
@@ -2195,6 +2595,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>McClay 2015</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -2217,6 +2622,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>McLean 1979</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Design: Non-RCT</t>
         </is>
       </c>
@@ -2239,6 +2649,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>Miller 2002</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
@@ -2261,6 +2676,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>Mohr 2001</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
@@ -2283,6 +2703,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>Mohr 2005</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
@@ -2305,6 +2730,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>Mohr 2013</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
@@ -2312,416 +2742,511 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mossey, 1996</t>
+          <t>Montero-Mar, 2016</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mossey JM, Knott KA, Higgins M, Talerico K. Effectiveness of a psychosocial intervention, interpersonal counseling, for subdysthymic depression in medically ill elderly. The journals of gerontology Series A, Biological sciences and medical sciences. 1996;51(4):M172-8.</t>
+          <t>Montero-Marín, J., Araya, R., Pérez-Yus, M. C., Mayoral, F., Gili, M., Botella, C., . . . López-Del-Hoyo, Y. (2016). An internet-based intervention for depression in primary Care in Spain: a randomized controlled trial. Journal of medical Internet research, 18(8), e231.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Mossey 1996</t>
+          <t>Montero-Mar 2016</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
+          <t>Montero-Marin 2016</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Population: Further-line treatment</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mukhtar, 2011</t>
+          <t>Mossey, 1996</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mukhtar F. Predictors of group cognitive behaviour therapy outcomes for the treatment of depression in Malaysia. Asian Journal of Psychiatry. 2011;4(2):125-8.</t>
+          <t>Mossey JM, Knott KA, Higgins M, Talerico K. Effectiveness of a psychosocial intervention, interpersonal counseling, for subdysthymic depression in medically ill elderly. The journals of gerontology Series A, Biological sciences and medical sciences. 1996;51(4):M172-8.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mukhtar 2011a</t>
+          <t>Mossey 1996</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Data cannot be extracted</t>
+          <t>Mossey 1996</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mulcahy, 2010</t>
+          <t>Mukhtar, 2011</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mulcahy R, Reay RE, Wilkinson RB, Owen C. A randomised control trial for the effectiveness of group interpersonal psychotherapy for postnatal depression. Archives of Women's Mental Health. 2010;13(2):125-39.</t>
+          <t>Mukhtar F. Predictors of group cognitive behaviour therapy outcomes for the treatment of depression in Malaysia. Asian Journal of Psychiatry. 2011;4(2):125-8.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mulcahey 2010</t>
+          <t>Mukhtar 2011</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Population: Antenatal or postnatal depression</t>
+          <t>Mukhtar 2011a</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Data cannot be extracted</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Neugebauer, 2006</t>
+          <t>Mulcahy, 2010</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Neugebauer R, Kline J, Markowitz JC, Bleiberg KL, Baxi L, Rosing MA, et al. Pilot randomized controlled trial of interpersonal counseling for subsyndromal depression following miscarriage. Journal of Clinical Psychiatry. 2006;67(8):1299-304.</t>
+          <t>Mulcahy R, Reay RE, Wilkinson RB, Owen C. A randomised control trial for the effectiveness of group interpersonal psychotherapy for postnatal depression. Archives of Women's Mental Health. 2010;13(2):125-39.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Neugebauer 2006</t>
+          <t>Mulcahy 2010</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Mulcahey 2010</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Population: Antenatal or postnatal depression</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Newby, 2014</t>
+          <t>Neugebauer, 2006</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Newby JM, Lang T, Werner-Seidler A, Holmes E, Moulds ML. Alleviating distressing intrusive memories in depression: A comparison between computerised cognitive bias modification and cognitive behavioural education. Behaviour Research and Therapy. 2014;56:60-7.</t>
+          <t>Neugebauer R, Kline J, Markowitz JC, Bleiberg KL, Baxi L, Rosing MA, et al. Pilot randomized controlled trial of interpersonal counseling for subsyndromal depression following miscarriage. Journal of Clinical Psychiatry. 2006;67(8):1299-304.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Newby 2014b</t>
+          <t>Neugebauer 2006</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Neugebauer 2006</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Nezu, 1986</t>
+          <t>Newby, 2014</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nezu AM. Efficacy of a social problem-solving therapy approach for unipolar depression. Journal of Consulting and Clinical Psychology. 1986;54(2):196-202.</t>
+          <t>Newby JM, Lang T, Werner-Seidler A, Holmes E, Moulds ML. Alleviating distressing intrusive memories in depression: A comparison between computerised cognitive bias modification and cognitive behavioural education. Behaviour Research and Therapy. 2014;56:60-7.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nezu 1986</t>
+          <t>Newby 2014</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Newby 2014b</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ng, 2013</t>
+          <t>Nezu, 1986</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ng SE, Tien A, Thayala JN, Ho RC, Chan MF. The effect of life story review on depression of older community-dwelling Chinese adults in Singapore: A preliminary result. International Journal of Geriatric Psychiatry. 2013;28(3):328-30.</t>
+          <t>Nezu AM. Efficacy of a social problem-solving therapy approach for unipolar depression. Journal of Consulting and Clinical Psychology. 1986;54(2):196-202.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ng 2013</t>
+          <t>Nezu 1986</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest</t>
+          <t>Nezu 1986</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>O'Hara, 2000</t>
+          <t>Ng, 2013</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>O'Hara MW, Stuart S, Gorman LL, Wenzel A. Efficacy of interpersonal psychotherapy for postpartum depression. Archives of General Psychiatry. 2000;57(11):1039-45.</t>
+          <t>Ng SE, Tien A, Thayala JN, Ho RC, Chan MF. The effect of life story review on depression of older community-dwelling Chinese adults in Singapore: A preliminary result. International Journal of Geriatric Psychiatry. 2013;28(3):328-30.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>O'Hara 2000</t>
+          <t>Ng 2013</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Population: Antenatal or postnatal depression</t>
+          <t>Ng 2013</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Omidi, 2013</t>
+          <t>O'Hara, 2000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Omidi A, Mohammadkhani P, Mohammadi A, Zargar F. Comparing mindfulness based cognitive therapy and traditional cognitive behavior therapy with treatments as usual on reduction of major depressive disorder symptoms. Iranian Red Crescent Medical Journal. 2013;15(2):142-6.</t>
+          <t>O'Hara MW, Stuart S, Gorman LL, Wenzel A. Efficacy of interpersonal psychotherapy for postpartum depression. Archives of General Psychiatry. 2000;57(11):1039-45.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Omidi 2013</t>
+          <t>O'Hara 2000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Population: Further-line treatment</t>
+          <t>O'Hara 2000</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Population: Antenatal or postnatal depression</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Padfield, 1976</t>
+          <t>Omidi, 2013</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Padfield M. The comparative effects of two counseling approaches on the intensity of depression among rural women of low socioeconomic status. Journal of Counseling Psychology. 1976;23(3):209.</t>
+          <t>Omidi A, Mohammadkhani P, Mohammadi A, Zargar F. Comparing mindfulness based cognitive therapy and traditional cognitive behavior therapy with treatments as usual on reduction of major depressive disorder symptoms. Iranian Red Crescent Medical Journal. 2013;15(2):142-6.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Padfield 1976</t>
+          <t>Omidi 2013</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Outcome measure(s) outside protocol</t>
+          <t>Omidi 2013</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Population: Further-line treatment</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pecheur, 1984</t>
+          <t>Padfield, 1976</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pecheur DR, Edwards KJ. A comparison of secular and religious versions of cognitive therapy with depressed Christian college students. Journal of Psychology and Theology. 1984.</t>
+          <t>Padfield M. The comparative effects of two counseling approaches on the intensity of depression among rural women of low socioeconomic status. Journal of Counseling Psychology. 1976;23(3):209.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pecheur 1984</t>
+          <t>Padfield 1976</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Padfield 1976</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Outcome measure(s) outside protocol</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Peden, 2000</t>
+          <t>Pecheur, 1984</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Peden AR, Hall LA, Rayens MK, Beebe LL. Reducing negative thinking and depressive symptoms in college women. Journal of Nursing Scholarship. 2000;32(2):145-51.</t>
+          <t>Pecheur DR, Edwards KJ. A comparison of secular and religious versions of cognitive therapy with depressed Christian college students. Journal of Psychology and Theology. 1984.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Peden 2000</t>
+          <t>Pecheur 1984</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Data cannot be extracted</t>
+          <t>Pecheur 1984</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Perini, 2009</t>
+          <t>Peden, 2000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Perini S, Titov N, Andrews G. Clinician-assisted Internet-based treatment is effective for depression: Randomized controlled trial. Australian and New Zealand Journal of Psychiatry. 2009;43(6):571-8.</t>
+          <t>Peden AR, Hall LA, Rayens MK, Beebe LL. Reducing negative thinking and depressive symptoms in college women. Journal of Nursing Scholarship. 2000;32(2):145-51.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Perini 2009</t>
+          <t>Peden 2000</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Peden 2000</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Data cannot be extracted</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pots, 2016</t>
+          <t>Perini, 2009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pots WT, Fledderus M, Meulenbeek PA, ten Klooster PM, Schreurs KM, Bohlmeijer ET. Acceptance and commitment therapy as a web-based intervention for depressive symptoms: Randomised controlled trial. The British Journal of Psychiatry. 2016;208(1):69-77.</t>
+          <t>Perini S, Titov N, Andrews G. Clinician-assisted Internet-based treatment is effective for depression: Randomized controlled trial. Australian and New Zealand Journal of Psychiatry. 2009;43(6):571-8.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pots 2016b</t>
+          <t>Perini 2009</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Secondary analysis with no new relevant or usable data</t>
+          <t>Perini 2009</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Power, 2012</t>
+          <t>Pots, 2016</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Power MJ, Freeman C. A randomized controlled trial of IPT versus CBT in primary care: With some cautionary notes about handling missing values in clinical trials. Clinical Psychology and Psychotherapy. 2012;19(2):159-69.</t>
+          <t>Pots WT, Fledderus M, Meulenbeek PA, ten Klooster PM, Schreurs KM, Bohlmeijer ET. Acceptance and commitment therapy as a web-based intervention for depressive symptoms: Randomised controlled trial. The British Journal of Psychiatry. 2016;208(1):69-77.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Power 2012</t>
+          <t>Pots 2016</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Data cannot be extracted</t>
+          <t>Pots 2016b</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Secondary analysis with no new relevant or usable data</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Preschl, 2012</t>
+          <t>Power, 2012</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Preschl B, Maercker A, Wagner B, Forstmeier S, Banos RM, Alcaniz M, et al. Life-review therapy with computer supplements for depression in the elderly: A randomized controlled trial. Aging and Mental Health. 2012;16(8):964-74.</t>
+          <t>Power MJ, Freeman C. A randomized controlled trial of IPT versus CBT in primary care: With some cautionary notes about handling missing values in clinical trials. Clinical Psychology and Psychotherapy. 2012;19(2):159-69.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Preschl 2012</t>
+          <t>Power 2012</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest</t>
+          <t>Power 2012</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Data cannot be extracted</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Propst, 1992</t>
+          <t>Preschl, 2012</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Propst LR, Ostrom R, Watkins P, Dean T, Mashburn D. Comparative efficacy of religious and nonreligious cognitive-behavioral therapy for the treatment of clinical depression in religious individuals. Journal of Consulting and Clinical Psychology. 1992;60(1):94-103.</t>
+          <t>Preschl B, Maercker A, Wagner B, Forstmeier S, Banos RM, Alcaniz M, et al. Life-review therapy with computer supplements for depression in the elderly: A randomized controlled trial. Aging and Mental Health. 2012;16(8):964-74.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Propst 1992</t>
+          <t>Preschl 2012</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Population: Chronic depression</t>
+          <t>Preschl 2012</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Richards, 2015</t>
+          <t>Propst, 1992</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Richards D, Timulak L, O'Brien E, Hayes C, Vigano N, Sharry J, et al. A randomized controlled trial of an internet-delivered treatment: Its potential as a low-intensity community intervention for adults with symptoms of depression. Behaviour Research and Therapy. 2015;75:20-31.</t>
+          <t>Propst LR, Ostrom R, Watkins P, Dean T, Mashburn D. Comparative efficacy of religious and nonreligious cognitive-behavioral therapy for the treatment of clinical depression in religious individuals. Journal of Consulting and Clinical Psychology. 1992;60(1):94-103.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Richards 2015</t>
+          <t>Propst 1992</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Propst 1992</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Population: Chronic depression</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Richards, 2016</t>
+          <t>Richards, 2015</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Richards, D. A., Ekers, D., McMillan, D., Taylor, R. S., Byford, S., Warren, F. C., . . . Finning, K. (2016). Cost and Outcome of Behavioural Activation versus Cognitive Behavioural Therapy for Depression (COBRA): a randomised, controlled, non-inferiority trial.</t>
+          <t>Richards D, Timulak L, O'Brien E, Hayes C, Vigano N, Sharry J, et al. A randomized controlled trial of an internet-delivered treatment: Its potential as a low-intensity community intervention for adults with symptoms of depression. Behaviour Research and Therapy. 2015;75:20-31.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Richards 2016/2017</t>
+          <t>Richards 2015</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
+        <is>
+          <t>Richards 2015</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
@@ -2730,900 +3255,1105 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Rief, 2018</t>
+          <t>Richards, 2016</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rief W, Bleichhardt G, Dannehl K, Euteneuer F, Wambach K. Comparing the Efficacy of CBASP with Two Versions of CBT for Depression in a Routine Care Center: a Randomized Clinical Trial. Psychotherapy and psychosomatics 2018;</t>
+          <t>Richards, D. A., Ekers, D., McMillan, D., Taylor, R. S., Byford, S., Warren, F. C., . . . Finning, K. (2016). Cost and Outcome of Behavioural Activation versus Cognitive Behavioural Therapy for Depression (COBRA): a randomised, controlled, non-inferiority trial.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rief 2018</t>
+          <t>Richards 2016</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Richards 2016/2017</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Rizvi, 2015</t>
+          <t>Rief, 2018</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Rizvi SJ, Zaretsky A, Schaffer A, Levitt A. Is immediate adjunctive CBT more beneficial than delayed CBT in treating depression?: A Pilot Study. Journal of Psychiatric Practice. 2015;21(2):107-13.</t>
+          <t>Rief W, Bleichhardt G, Dannehl K, Euteneuer F, Wambach K. Comparing the Efficacy of CBASP with Two Versions of CBT for Depression in a Routine Care Center: a Randomized Clinical Trial. Psychotherapy and psychosomatics 2018;</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rizvi 2015</t>
+          <t>Rief 2018</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest (only 1 arm meets inclusion criteria)</t>
+          <t>Rief 2018</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ross, 1985</t>
+          <t>Rizvi, 2015</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ross M, Scott M. An evaluation of the effectiveness of individual and group cognitive therapy in the treatment of depressed patients in an inner city health centre. The Journal of the Royal College of General Practitioners. 1985;35(274):239-42.</t>
+          <t>Rizvi SJ, Zaretsky A, Schaffer A, Levitt A. Is immediate adjunctive CBT more beneficial than delayed CBT in treating depression?: A Pilot Study. Journal of Psychiatric Practice. 2015;21(2):107-13.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ross 1985</t>
+          <t>Rizvi 2015</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Data cannot be extracted</t>
+          <t>Rizvi 2015</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest (only 1 arm meets inclusion criteria)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Russell, 2019</t>
+          <t>Ross, 1985</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Russell, A., Gaunt, D. M., Cooper, K., Barton, S., Horwood, J., Kessler, D., . . . et al. (2019). The feasibility of low-intensity psychological therapy for depression co-occurring with autism in adults: the Autism Depression Trial (ADEPT) â€“ a pilot randomised controlled trial. Autism. doi:10.1177/1362361319889272</t>
+          <t>Ross M, Scott M. An evaluation of the effectiveness of individual and group cognitive therapy in the treatment of depressed patients in an inner city health centre. The Journal of the Royal College of General Practitioners. 1985;35(274):239-42.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russell 2019b</t>
+          <t>Ross 1985</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Ross 1985</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Data cannot be extracted</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Schulberg, 1996</t>
+          <t>Russell, 2019</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Schulberg HC, Block MR, Madonia MJ, Scott CP, Rodriguez E, Imber SD, et al. Treating major depression in primary care practice. Eight-month clinical outcomes. Archives of General Psychiatry. 1996;53(10):913-9.</t>
+          <t>Russell, A., Gaunt, D. M., Cooper, K., Barton, S., Horwood, J., Kessler, D., . . . et al. (2019). The feasibility of low-intensity psychological therapy for depression co-occurring with autism in adults: the Autism Depression Trial (ADEPT) â€“ a pilot randomised controlled trial. Autism. doi:10.1177/1362361319889272</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Schulberg 1996</t>
+          <t>Russell 2019</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Data cannot be extracted</t>
+          <t>Russell 2019b</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Scogin, 1987</t>
+          <t>Schulberg, 1996</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Scogin F, Hamblin D, Beutler L. Bibliotherapy for depressed older adults: A self-help alternative. The Gerontologist. 1987;27(3):383-7.</t>
+          <t>Schulberg HC, Block MR, Madonia MJ, Scott CP, Rodriguez E, Imber SD, et al. Treating major depression in primary care practice. Eight-month clinical outcomes. Archives of General Psychiatry. 1996;53(10):913-9.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scogin 1987</t>
+          <t>Schulberg 1996</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Schulberg 1996</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Data cannot be extracted</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Scogin, 1989</t>
+          <t>Scogin, 1987</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Scogin F, Jamison C, Gochneaur K. Comparative efficacy of cognitive and behavioral bibliotherapy for mildly and moderately depressed older adults. Journal of Consulting and Clinical Psychology. 1989;57(3):403-7.</t>
+          <t>Scogin F, Hamblin D, Beutler L. Bibliotherapy for depressed older adults: A self-help alternative. The Gerontologist. 1987;27(3):383-7.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scogin 1989</t>
+          <t>Scogin 1987</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Scogin 1987</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Scott, 1990</t>
+          <t>Scogin, 1989</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Scott MJ, Stradling SG. Group cognitive therapy for depression produces clinically significant reliable change in community-based settings. Behavioural Psychotherapy. 1990;18(01):1-19.</t>
+          <t>Scogin F, Jamison C, Gochneaur K. Comparative efficacy of cognitive and behavioral bibliotherapy for mildly and moderately depressed older adults. Journal of Consulting and Clinical Psychology. 1989;57(3):403-7.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Scott 1990</t>
+          <t>Scogin 1989</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Design: Non-RCT</t>
+          <t>Scogin 1989</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Selmi, 1990</t>
+          <t>Scott, 1990</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Selmi PM, Klein MH, Greist JH, Sorrell SP, Erdman HP. Computer-administered cognitive-behavioral therapy for depression. American Journal of Psychiatry. 1990;147(1):51-6.</t>
+          <t>Scott MJ, Stradling SG. Group cognitive therapy for depression produces clinically significant reliable change in community-based settings. Behavioural Psychotherapy. 1990;18(01):1-19.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Selmi 1990</t>
+          <t>Scott 1990</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Scott 1990</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Design: Non-RCT</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Serfaty, 2009</t>
+          <t>Selmi, 1990</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Serfaty MA, Haworth D, Blanchard M, Buszewicz M, Murad S, King M. Clinical effectiveness of individual cognitive behavioral therapy for depressed older people in primary care: A randomized controlled trial. Archives of General Psychiatry. 2009;66(12):1332-40.</t>
+          <t>Selmi PM, Klein MH, Greist JH, Sorrell SP, Erdman HP. Computer-administered cognitive-behavioral therapy for depression. American Journal of Psychiatry. 1990;147(1):51-6.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serfaty 2009</t>
+          <t>Selmi 1990</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Selmi 1990</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Serrano, 2004</t>
+          <t>Serfaty, 2009</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Serrano JP, Latorre JM, Gatz M, Montanes J. Life review therapy using autobiographical retrieval practice for older adults with depressive symptomatology. Psychology and Aging. 2004;19(2):270-7.</t>
+          <t>Serfaty MA, Haworth D, Blanchard M, Buszewicz M, Murad S, King M. Clinical effectiveness of individual cognitive behavioral therapy for depressed older people in primary care: A randomized controlled trial. Archives of General Psychiatry. 2009;66(12):1332-40.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serrano 2004</t>
+          <t>Serfaty 2009</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Design: Non-RCT</t>
+          <t>Serfaty 2009</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Shapiro, 1990</t>
+          <t>Serrano, 2004</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shapiro DA, Barkham M, Hardy GE, Morrison LA. The Second Sheffield Psychotherapy Project: rationale, design and preliminary outcome data. The British journal of medical psychology. 1990;63(2):97-108.</t>
+          <t>Serrano JP, Latorre JM, Gatz M, Montanes J. Life review therapy using autobiographical retrieval practice for older adults with depressive symptomatology. Psychology and Aging. 2004;19(2):270-7.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Shapiro 1990</t>
+          <t>Serrano 2004</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Secondary analysis with no new relevant or usable data</t>
+          <t>Serrano 2004</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Design: Non-RCT</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Shaw, 1977</t>
+          <t>Serrano, 2012</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shaw BF. Comparison of cognitive therapy and behavior therapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 1977;45(4):543.</t>
+          <t>Serrano Selva JP, Latorre Postigo JM, Ros Segura L, Navarro Bravo B, Aguilar Corcoles MJ, Nieto Lopez M, et al. Life review therapy using autobiographical retrieval practice for older adults with clinical depression. Psicothema. 2012;24(2):224-9.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Shaw 1977</t>
+          <t>Serrano 2012</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Serrano 2012</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Simpson, 2003</t>
+          <t>Shapiro, 1990</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Simpson S, Corney R, Beecham J. A randomized controlled trial to evaluate the effectiveness and cost-effectiveness of psychodynamic counselling for general practice patients with chronic depression. Psychological Medicine. 2003;33(2):229-39.</t>
+          <t>Shapiro DA, Barkham M, Hardy GE, Morrison LA. The Second Sheffield Psychotherapy Project: rationale, design and preliminary outcome data. The British journal of medical psychology. 1990;63(2):97-108.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Simpson 2003</t>
+          <t>Shapiro 1990</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Shapiro 1990</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Secondary analysis with no new relevant or usable data</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sinniah, 2017</t>
+          <t>Shaw, 1977</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sinniah, A., Oei, T., Maniam, T., &amp; Subramaniam, P. (2017). Positive effects of Individual Cognitive Behavior Therapy for patients with unipolar mood disorders with suicidal ideation in Malaysia: a randomised controlled trial. Psychiatry research, 254, 179-189.</t>
+          <t>Shaw BF. Comparison of cognitive therapy and behavior therapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 1977;45(4):543.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sinniah 2017</t>
+          <t>Shaw 1977</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Shaw 1977</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sloane, 1985</t>
+          <t>Simpson, 2003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sloane R, Staples F, Schneider L. Interpersonal therapy versus nortriptyline for depression in the elderly. Clinical and Pharmacological Studies in Psychiatric Disorders. 1985:344-6.</t>
+          <t>Simpson S, Corney R, Beecham J. A randomized controlled trial to evaluate the effectiveness and cost-effectiveness of psychodynamic counselling for general practice patients with chronic depression. Psychological Medicine. 2003;33(2):229-39.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sloane 1985</t>
+          <t>Simpson 2003</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Design: Non-primary paper</t>
+          <t>Simpson 2003</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Smit, 2006</t>
+          <t>Sinniah, 2017</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Smit A, Kluiter H, Conradi HJ, Meer K, Tiemens BG, Jenner JA, et al. Short-term effects of enhanced treatment for depression in primary care: Results from a randomized controlled trial. Psychological Medicine. 2006;36(1):15-26.</t>
+          <t>Sinniah, A., Oei, T., Maniam, T., &amp; Subramaniam, P. (2017). Positive effects of Individual Cognitive Behavior Therapy for patients with unipolar mood disorders with suicidal ideation in Malaysia: a randomised controlled trial. Psychiatry research, 254, 179-189.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Smit 2006</t>
+          <t>Sinniah 2017</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Sinniah 2017</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Smith, 2017</t>
+          <t>Sloane, 1985</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Smith, J., Newby, J. M., Burston, N., Murphy, M. J., Michael, S., Mackenzie, A., . . . Andrews, G. (2017). Help from home for depression: A randomised controlled trial comparing internet-delivered cognitive behaviour therapy with bibliotherapy for depression. Internet Interventions, 9, 25-37.</t>
+          <t>Sloane R, Staples F, Schneider L. Interpersonal therapy versus nortriptyline for depression in the elderly. Clinical and Pharmacological Studies in Psychiatric Disorders. 1985:344-6.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Smith 2017</t>
+          <t>Sloane 1985</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Sloane 1985</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Design: Non-primary paper</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Soares, 2018</t>
+          <t>Smit, 2006</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Soares MC, Mondin TC, Silva G, et al. Comparison of Clinical Significance of Cognitive-Behavioral Therapy and Psychodynamic Therapy for Major Depressive Disorder: a Randomized Clinical Trial. Journal of nervous and mental disease 2018; 206(9): 686‐93.</t>
+          <t>Smit A, Kluiter H, Conradi HJ, Meer K, Tiemens BG, Jenner JA, et al. Short-term effects of enhanced treatment for depression in primary care: Results from a randomized controlled trial. Psychological Medicine. 2006;36(1):15-26.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Soares 2018</t>
+          <t>Smit 2006</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Data cannot be extracted</t>
+          <t>Smit 2006</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Songprakun, 2012</t>
+          <t>Smith, 2017</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Songprakun W, McCann TV. Evaluation of a cognitive behavioural self-help manual for reducing depression: A randomized controlled trial. Journal of psychiatric and mental health nursing. 2012;19(7):647-53.</t>
+          <t>Smith, J., Newby, J. M., Burston, N., Murphy, M. J., Michael, S., Mackenzie, A., . . . Andrews, G. (2017). Help from home for depression: A randomised controlled trial comparing internet-delivered cognitive behaviour therapy with bibliotherapy for depression. Internet Interventions, 9, 25-37.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Songprakun 2012</t>
+          <t>Smith 2017</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Population: Further-line treatment</t>
+          <t>Smith 2017</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Strong, 2008</t>
+          <t>Soares, 2018</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Strong V, Waters R, Hibberd C, Murray G, Wall L, Walker J, et al. Management of depression for people with cancer (SMaRT oncology 1): A randomised trial. Lancet. 2008;372(9632):40-8.</t>
+          <t>Soares MC, Mondin TC, Silva G, et al. Comparison of Clinical Significance of Cognitive-Behavioral Therapy and Psychodynamic Therapy for Major Depressive Disorder: a Randomized Clinical Trial. Journal of nervous and mental disease 2018; 206(9): 686‐93.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Strong 2008</t>
+          <t>Soares 2018</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
+          <t>Soares 2018</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Data cannot be extracted</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Swartz, 2008</t>
+          <t>Songprakun, 2012</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Swartz HA, Frank E, Zuckoff A, Cyranowski JM, Houck PR, Cheng Y, et al. Brief interpersonal psychotherapy for depressed mothers whose children are receiving psychiatric treatment. American Journal of Psychiatry. 2008;165(9):1155-62.</t>
+          <t>Songprakun W, McCann TV. Evaluation of a cognitive behavioural self-help manual for reducing depression: A randomized controlled trial. Journal of psychiatric and mental health nursing. 2012;19(7):647-53.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Swartz 2008</t>
+          <t>Songprakun 2012</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Songprakun 2012</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Population: Further-line treatment</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Takagaki, 2016</t>
+          <t>Strong, 2008</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Takagaki K, Okamoto Y, Jinnin R, Mori A, Nishiyama Y, Yamamura T, et al. Behavioral activation for late adolescents with subthreshold depression: A randomized controlled trial. European Child and Adolescent Psychiatry. 2016;25(11):1171-82.</t>
+          <t>Strong V, Waters R, Hibberd C, Murray G, Wall L, Walker J, et al. Management of depression for people with cancer (SMaRT oncology 1): A randomised trial. Lancet. 2008;372(9632):40-8.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Takagaki 2016</t>
+          <t>Strong 2008</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Data cannot be extracted</t>
+          <t>Strong 2008</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Talbot, 2011</t>
+          <t>Swartz, 2008</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Talbot NL, Chaudron LH, Ward EA, Duberstein PR, Conwell Y, O'Hara MW, et al. A randomized effectiveness trial of interpersonal psychotherapy for depressed women with sexual abuse histories. Psychiatric Services. 2011;62(4):374-80.</t>
+          <t>Swartz HA, Frank E, Zuckoff A, Cyranowski JM, Houck PR, Cheng Y, et al. Brief interpersonal psychotherapy for depressed mothers whose children are receiving psychiatric treatment. American Journal of Psychiatry. 2008;165(9):1155-62.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Talbot 2011</t>
+          <t>Swartz 2008</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Swartz 2008</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Taylor, 1977</t>
+          <t>Takagaki, 2016</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Taylor FG, Marshall WL. Experimental analysis of a cognitive-behavioral therapy for depression. Cognitive Therapy and Research. 1977;1(1):59-72.</t>
+          <t>Takagaki K, Okamoto Y, Jinnin R, Mori A, Nishiyama Y, Yamamura T, et al. Behavioral activation for late adolescents with subthreshold depression: A randomized controlled trial. European Child and Adolescent Psychiatry. 2016;25(11):1171-82.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Taylor 1977</t>
+          <t>Takagaki 2016</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Takagaki 2016</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Data cannot be extracted</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Taylor, 2009</t>
+          <t>Talbot, 2011</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Taylor CB, Conrad A, Wilhelm FH, Strachowski D, Khaylis A, Neri E, et al. Does improving mood in depressed patients alter factors that may affect cardiovascular disease risk? Journal of Psychiatric Research. 2009;43(16):1246-52.</t>
+          <t>Talbot NL, Chaudron LH, Ward EA, Duberstein PR, Conwell Y, O'Hara MW, et al. A randomized effectiveness trial of interpersonal psychotherapy for depressed women with sexual abuse histories. Psychiatric Services. 2011;62(4):374-80.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Taylor 2009</t>
+          <t>Talbot 2011</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
+          <t>Talbot 2011</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Teasdale, 1984</t>
+          <t>Taylor, 1977</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Teasdale JD, Fennell MJ, Hibbert GA, Amies PL. Cognitive therapy for major depressive disorder in primary care. The British Journal of Psychiatry. 1984;144:400-6.</t>
+          <t>Taylor FG, Marshall WL. Experimental analysis of a cognitive-behavioral therapy for depression. Cognitive Therapy and Research. 1977;1(1):59-72.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Teasdale 1984</t>
+          <t>Taylor 1977</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Taylor 1977</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Teichman, 1995</t>
+          <t>Taylor, 2009</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Teichman Y, Bar-el Z, Shor H, Sirota P, Elizur A. A comparison of two modalities of cognitive therapy (individual and marital) in treating depression. Psychiatry. 1995;58(2):136-48.</t>
+          <t>Taylor CB, Conrad A, Wilhelm FH, Strachowski D, Khaylis A, Neri E, et al. Does improving mood in depressed patients alter factors that may affect cardiovascular disease risk? Journal of Psychiatric Research. 2009;43(16):1246-52.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Teichman 1995</t>
+          <t>Taylor 2009</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Taylor 2009</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Population: Trial specifically recruited participants with physical health conditions in addition to depression</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Thompson, 1987</t>
+          <t>Teasdale, 1984</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Thompson LW, Gallagher D, Breckenridge JS. Comparative effectiveness of psychotherapies for depressed elders. Journal of Consulting and Clinical Psychology. 1987;55(3):385.</t>
+          <t>Teasdale JD, Fennell MJ, Hibbert GA, Amies PL. Cognitive therapy for major depressive disorder in primary care. The British Journal of Psychiatry. 1984;144:400-6.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Thompson 1987</t>
+          <t>Teasdale 1984</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Teasdale 1984</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Titov, 2010</t>
+          <t>Teichman, 1995</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Titov N, Andrews G, Davies M, McIntyre K, Robinson E, Solley K. Internet treatment for depression: A randomized controlled trial comparing clinician vs. technician assistance. PLoS One. 2010;5(6):e10939.</t>
+          <t>Teichman Y, Bar-el Z, Shor H, Sirota P, Elizur A. A comparison of two modalities of cognitive therapy (individual and marital) in treating depression. Psychiatry. 1995;58(2):136-48.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Titov 2010</t>
+          <t>Teichman 1995</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Teichman 1995</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Titov, 2015</t>
+          <t>Thompson, 1987</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Titov N, Dear BF, Ali S, Zou JB, Lorian CN, Johnston L, et al. Clinical and cost-effectiveness of therapist-guided internet-delivered cognitive behavior therapy for older adults with symptoms of depression: A randomized controlled trial. Behavior Therapy. 2015;46(2):193-205.</t>
+          <t>Thompson LW, Gallagher D, Breckenridge JS. Comparative effectiveness of psychotherapies for depressed elders. Journal of Consulting and Clinical Psychology. 1987;55(3):385.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Titov 2015a</t>
+          <t>Thompson 1987</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Thompson 1987</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tomasino, 2017</t>
+          <t>Titov, 2010</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tomasino, K., Lattie, E., Ho, J., Palac, H., Kaiser, S., &amp; Mohr, D. (2017). Harnessing Peer Support in an Online Intervention for Older Adults with Depression. American Journal of Geriatric Psychiatry, 25(10), 1109-1119.</t>
+          <t>Titov N, Andrews G, Davies M, McIntyre K, Robinson E, Solley K. Internet treatment for depression: A randomized controlled trial comparing clinician vs. technician assistance. PLoS One. 2010;5(6):e10939.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tomasino 2017</t>
+          <t>Titov 2010</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Design: Non-RCT</t>
+          <t>Titov 2010</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tulbure, 2018</t>
+          <t>Titov, 2015</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Tulbure BT, Andersson G, Salagean N, Pearce M, Koenig HG. Religious versus Conventional Internet-based Cognitive Behavioral Therapy for Depression. J Relig Health 2018; 57(5): 1634-48.</t>
+          <t>Titov N, Dear BF, Ali S, Zou JB, Lorian CN, Johnston L, et al. Clinical and cost-effectiveness of therapist-guided internet-delivered cognitive behavior therapy for older adults with symptoms of depression: A randomized controlled trial. Behavior Therapy. 2015;46(2):193-205.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tulbure 2018a</t>
+          <t>Titov 2015</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Design: Non-RCT</t>
+          <t>Titov 2015a</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Turner, 1979</t>
+          <t>Tomasino, 2017</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Turner RW, Ward MF, Turner DJ. Behavioral treatment for depression: An evaluation of therapeutic components. Journal of clinical psychology. 1979;35(1):166-75.</t>
+          <t>Tomasino, K., Lattie, E., Ho, J., Palac, H., Kaiser, S., &amp; Mohr, D. (2017). Harnessing Peer Support in an Online Intervention for Older Adults with Depression. American Journal of Geriatric Psychiatry, 25(10), 1109-1119.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Turner 1979</t>
+          <t>Tomasino 2017</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Outcome(s) not of interest</t>
+          <t>Tomasino 2017</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Design: Non-RCT</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Verduyn, 2003</t>
+          <t>Tulbure, 2018</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Verduyn C, Barrowclough C, Roberts J, Tarrier N, Harrington R. Maternal depression and child behaviour problems: Randomised placebo-controlled trial of a cognitive-behavioural group intervention. British Journal of Psychiatry. 2003;183(OCT.):342-8.</t>
+          <t>Tulbure BT, Andersson G, Salagean N, Pearce M, Koenig HG. Religious versus Conventional Internet-based Cognitive Behavioral Therapy for Depression. J Relig Health 2018; 57(5): 1634-48.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Verduyn 2003</t>
+          <t>Tulbure 2018</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Tulbure 2018a</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Design: Non-RCT</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Watson, 2003</t>
+          <t>Turner, 1979</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Watson JC, Gordon LB, Stermac L, Kalogerakos F, Steckley P. Comparing the effectiveness of process-experiential with cognitive-behavioral psychotherapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 2003;71(4):773-81.</t>
+          <t>Turner RW, Ward MF, Turner DJ. Behavioral treatment for depression: An evaluation of therapeutic components. Journal of clinical psychology. 1979;35(1):166-75.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Watson 2003</t>
+          <t>Turner 1979</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Population: &gt;20% have coexisting personality disorder</t>
+          <t>Turner 1979</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Outcome(s) not of interest</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Westerhof, 2019</t>
+          <t>Verduyn, 2003</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Westerhof, G. J., Lamers, S. M. A., Postel, M. G., &amp; Bohlmeijer, E. T. (2019). Online Therapy for Depressive Symptoms: An Evaluation of Counselor-Led and Peer-Supported Life Review Therapy. The Gerontologist, 59(1), 135-146. doi:10.1093/geront/gnx140</t>
+          <t>Verduyn C, Barrowclough C, Roberts J, Tarrier N, Harrington R. Maternal depression and child behaviour problems: Randomised placebo-controlled trial of a cognitive-behavioural group intervention. British Journal of Psychiatry. 2003;183(OCT.):342-8.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Westerhof 2019</t>
+          <t>Verduyn 2003</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Intervention: Psychological intervention not of interest</t>
+          <t>Verduyn 2003</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Williams, 2000</t>
+          <t>Watson, 2003</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Williams JW, Barrett J, Oxman T, Frank E, Katon W, Sullivan M, et al. Treatment of dysthymia and minor depression in primary care: A randomized controlled trial in older adults. JAMA. 2000;284(12):1519-26.</t>
+          <t>Watson JC, Gordon LB, Stermac L, Kalogerakos F, Steckley P. Comparing the effectiveness of process-experiential with cognitive-behavioral psychotherapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 2003;71(4):773-81.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Williams 2000</t>
+          <t>Watson 2003</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Population: &lt;80% non-chronic depression</t>
+          <t>Watson 2003</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Population: &gt;20% have coexisting personality disorder</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Williams, 2013 I</t>
+          <t>Westerhof, 2019</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Williams AD, Blackwell SE, Mackenzie A, Holmes EA, Andrews G. Combining imagination and reason in the treatment of depression: A randomized controlled trial of internet-based cognitive-bias modification and internet-CBT for depression. Journal of Consulting and Clinical Psychology. 2013;81(5):793-9.</t>
+          <t>Westerhof, G. J., Lamers, S. M. A., Postel, M. G., &amp; Bohlmeijer, E. T. (2019). Online Therapy for Depressive Symptoms: An Evaluation of Counselor-Led and Peer-Supported Life Review Therapy. The Gerontologist, 59(1), 135-146. doi:10.1093/geront/gnx140</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Williams 2013b</t>
+          <t>Westerhof 2019</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Westerhof 2019</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Intervention: Psychological intervention not of interest</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Williams, 2013 II</t>
+          <t>Williams, 2000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Williams C, Wilson P, Morrison J, McMahon A, Andrew W, Allan L, et al. Guided self-help cognitive behavioural therapy for depression in primary care: A randomised controlled trial. PLoS One. 2013;8(1):e52735.</t>
+          <t>Williams JW, Barrett J, Oxman T, Frank E, Katon W, Sullivan M, et al. Treatment of dysthymia and minor depression in primary care: A randomized controlled trial in older adults. JAMA. 2000;284(12):1519-26.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Williams 2013c</t>
+          <t>Williams 2000</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Williams 2000</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% non-chronic depression</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Williams, 2018</t>
+          <t>Williams, 2013 I</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Williams C, McClay CA, Matthews L, et al. Community-based group guided self-help intervention for low mood and stress: Randomised controlled trial. British Journal of Psychiatry 2018; 212(2): 88-95.</t>
+          <t>Williams AD, Blackwell SE, Mackenzie A, Holmes EA, Andrews G. Combining imagination and reason in the treatment of depression: A randomized controlled trial of internet-based cognitive-bias modification and internet-CBT for depression. Journal of Consulting and Clinical Psychology. 2013;81(5):793-9.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Williams 2018</t>
+          <t>Williams 2013</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
+        <is>
+          <t>Williams 2013b</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
         <is>
           <t>Population: &lt;80% first-line treatment</t>
         </is>
@@ -3632,152 +4362,241 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Wilson, 1983</t>
+          <t>Williams, 2013 II</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Wilson PH, Goldin JC, Charbonneau-Powis M. Comparative efficacy of behavioral and cognitive treatments of depression. Cognitive Therapy and Research. 1983;7(2):111-24.</t>
+          <t>Williams C, Wilson P, Morrison J, McMahon A, Andrew W, Allan L, et al. Guided self-help cognitive behavioural therapy for depression in primary care: A randomised controlled trial. PLoS One. 2013;8(1):e52735.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wilson 1983</t>
+          <t>Williams 2013</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Williams 2013c</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Wollersheim, 1991</t>
+          <t>Williams, 2018</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Wollersheim JP, Wilson GL. Group treatment of unipolar depression: A comparison of coping, supportive, bibliotherapy, and delayed treatment groups. Professional Psychology: Research and Practice. 1991;22(6):496.</t>
+          <t>Williams C, McClay CA, Matthews L, et al. Community-based group guided self-help intervention for low mood and stress: Randomised controlled trial. British Journal of Psychiatry 2018; 212(2): 88-95.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wollersheim 1991</t>
+          <t>Williams 2018</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Sample size N&lt;10 per arm</t>
+          <t>Williams 2018</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Wong, 2018</t>
+          <t>Wilson, 1983</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Wong SYS, Sun YY, Chan ATY, et al. Treating Subthreshold Depression in Primary Care: a Randomized Controlled Trial of Behavioral Activation With Mindfulness. Annals of family medicine 2018; 16(2): 111‐9.</t>
+          <t>Wilson PH, Goldin JC, Charbonneau-Powis M. Comparative efficacy of behavioral and cognitive treatments of depression. Cognitive Therapy and Research. 1983;7(2):111-24.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wong 2018</t>
+          <t>Wilson 1983</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Population: Not depression</t>
+          <t>Wilson 1983</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Wuthrich, 2013</t>
+          <t>Wollersheim, 1991</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Wuthrich VM, Rapee RM. Randomised controlled trial of group cognitive behavioural therapy for comorbid anxiety and depression in older adults. Behaviour Research and Therapy. 2013;51(12):779-86.</t>
+          <t>Wollersheim JP, Wilson GL. Group treatment of unipolar depression: A comparison of coping, supportive, bibliotherapy, and delayed treatment groups. Professional Psychology: Research and Practice. 1991;22(6):496.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wuthrich 2013</t>
+          <t>Wollersheim 1991</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Population: &lt;80% first-line treatment</t>
+          <t>Wollersheim 1991</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Sample size N&lt;10 per arm</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Xie, 2019</t>
+          <t>Wong, 2018</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Xie, J., He, G., Ding, S., Pan, C., Zhang, X., Zhou, J., &amp; Iennaco, J. D. (2019). A randomized study on the effect of modified behavioral activation treatment for depressive symptoms in rural left-behind elderly. Psychotherapy research : journal of the Society for Psychotherapy Research, 29(3), 372-382. doi:10.1080/10503307.2017.1364444</t>
+          <t>Wong SYS, Sun YY, Chan ATY, et al. Treating Subthreshold Depression in Primary Care: a Randomized Controlled Trial of Behavioral Activation With Mindfulness. Annals of family medicine 2018; 16(2): 111‐9.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Xie 2019</t>
+          <t>Wong 2018</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Baseline severity cannot be categorised</t>
+          <t>Wong 2018</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Population: Not depression</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Yeung, 2017</t>
+          <t>Wuthrich, 2013</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Yeung, A., Wang, F., Feng, F., Zhang, J., Cooper, A., Hong, L., . . . Fava, M. (2017). Outcomes of an online computerized cognitive behavioral treatment program for treating chinese patients with depression: A pilot study. Asian journal of psychiatry. doi:10.1016/j.ajp.2017</t>
+          <t>Wuthrich VM, Rapee RM. Randomised controlled trial of group cognitive behavioural therapy for comorbid anxiety and depression in older adults. Behaviour Research and Therapy. 2013;51(12):779-86.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Yeung 2017</t>
+          <t>Wuthrich 2013</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Baseline severity cannot be categorised</t>
+          <t>Wuthrich 2013</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Population: &lt;80% first-line treatment</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>Xie, 2019</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Xie, J., He, G., Ding, S., Pan, C., Zhang, X., Zhou, J., &amp; Iennaco, J. D. (2019). A randomized study on the effect of modified behavioral activation treatment for depressive symptoms in rural left-behind elderly. Psychotherapy research : journal of the Society for Psychotherapy Research, 29(3), 372-382. doi:10.1080/10503307.2017.1364444</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Xie 2019</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Xie 2019</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Baseline severity cannot be categorised</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Yeung, 2017</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Yeung, A., Wang, F., Feng, F., Zhang, J., Cooper, A., Hong, L., . . . Fava, M. (2017). Outcomes of an online computerized cognitive behavioral treatment program for treating chinese patients with depression: A pilot study. Asian journal of psychiatry. doi:10.1016/j.ajp.2017</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Yeung 2017</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Yeung 2017</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Baseline severity cannot be categorised</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>Zettle, 1989</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Zettle RD, Rains JC. Group cognitive and contextual therapies in treatment of depression. Journal of clinical psychology. 1989;45(3):436-45.</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Zettle 1989</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Zettle 1989</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
         <is>
           <t>Intervention: Psychological intervention not of interest (only 1 arm meets inclusion criteria)</t>
         </is>
@@ -3794,7 +4613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C303"/>
+  <dimension ref="A1:C302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3877,7 +4696,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Allart, 2003</t>
+          <t>Allart-Van, 2003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3952,7 +4771,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Barret, 2001</t>
+          <t>Barrett, 2001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4987,12 +5806,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Gallagher, 1994</t>
+          <t>Garcia-Pena, 2015</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gallagher-Thompson D, Steffen AM. Comparative effects of cognitive-behavioral and brief psychodynamic psychotherapies for depressed family caregivers. Journal of Consulting and Clinical Psychology. 1994;62(3):543-9.</t>
+          <t>García-Peña C, Vázquez-Estupiñan F, Avalos-Pérez F, Jiménez LVR, Sánchez-Garcia S, Juárez-Cedillo T. Clinical effectiveness of group cognitive-behavioural therapy for depressed older people in primary care: A randomised controlled trial. Salud Mental. 2015;38(1):33-9.</t>
         </is>
       </c>
       <c r="C80" t="b">
@@ -5002,12 +5821,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Garcia-Pena, 2015</t>
+          <t>Gawrysiak, 2009</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>García-Peña C, Vázquez-Estupiñan F, Avalos-Pérez F, Jiménez LVR, Sánchez-Garcia S, Juárez-Cedillo T. Clinical effectiveness of group cognitive-behavioural therapy for depressed older people in primary care: A randomised controlled trial. Salud Mental. 2015;38(1):33-9.</t>
+          <t>Gawrysiak M, Nicholas C, Hopko DR. Behavioral activation for moderately depressed university students: Randomized controlled trial. Journal of Counseling Psychology. 2009;56(3):468-75.</t>
         </is>
       </c>
       <c r="C81" t="b">
@@ -5017,12 +5836,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gawrysiak, 2009</t>
+          <t>Gellis, 2008</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gawrysiak M, Nicholas C, Hopko DR. Behavioral activation for moderately depressed university students: Randomized controlled trial. Journal of Counseling Psychology. 2009;56(3):468-75.</t>
+          <t>Gellis ZD, McGinty J, Tierney L, Jordan C, Burton J, Misener E. Randomized controlled trial of problem-solving therapy for minor depression in home care. Research on Social Work Practice. 2008;18(6):596-606.</t>
         </is>
       </c>
       <c r="C82" t="b">
@@ -5032,12 +5851,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gellis, 2008</t>
+          <t>Gellis, 2010</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gellis ZD, McGinty J, Tierney L, Jordan C, Burton J, Misener E. Randomized controlled trial of problem-solving therapy for minor depression in home care. Research on Social Work Practice. 2008;18(6):596-606.</t>
+          <t>Gellis ZD, Bruce ML. Problem solving therapy for subthreshold depression in home healthcare patients with cardiovascular disease. The American Journal of Geriatric Psychiatry. 2010;18(6):464-74.</t>
         </is>
       </c>
       <c r="C83" t="b">
@@ -5047,12 +5866,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Gellis, 2010</t>
+          <t>Geraedts, 2014</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Gellis ZD, Bruce ML. Problem solving therapy for subthreshold depression in home healthcare patients with cardiovascular disease. The American Journal of Geriatric Psychiatry. 2010;18(6):464-74.</t>
+          <t>Geraedts AS, Kleiboer AM, Wiezer NM, van Mechelen W, Cuijpers P. Short-term effects of a web-based guided self-help intervention for employees with depressive symptoms: Randomized controlled trial. Journal of Medical Internet Research. 2014;16(5):e121.</t>
         </is>
       </c>
       <c r="C84" t="b">
@@ -5062,12 +5881,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Geraedts, 2014</t>
+          <t>Gibbons, 2012</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Geraedts AS, Kleiboer AM, Wiezer NM, van Mechelen W, Cuijpers P. Short-term effects of a web-based guided self-help intervention for employees with depressive symptoms: Randomized controlled trial. Journal of Medical Internet Research. 2014;16(5):e121.</t>
+          <t>Gibbons MB, Thompson SM, Scott K, Schauble LA, Mooney T, Thompson D, et al. Supportive-expressive dynamic psychotherapy in the community mental health system: A pilot effectiveness trial for the treatment of depression. Psychotherapy (Chicago, Ill). 2012;49(3):303-16.</t>
         </is>
       </c>
       <c r="C85" t="b">
@@ -5077,12 +5896,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Gibbons, 2012</t>
+          <t>Greenberg, 2018</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gibbons MB, Thompson SM, Scott K, Schauble LA, Mooney T, Thompson D, et al. Supportive-expressive dynamic psychotherapy in the community mental health system: A pilot effectiveness trial for the treatment of depression. Psychotherapy (Chicago, Ill). 2012;49(3):303-16.</t>
+          <t>Greenberg J, Datta T, Shapero BG, Sevinc G, Mischoulon D, Lazar SW. Compassionate hearts protect against wandering minds: Self-compassion moderates the effect of mind-wandering on depression. Spirituality in Clinical Practice 2018; 5(3): 155-69.</t>
         </is>
       </c>
       <c r="C86" t="b">
@@ -5092,12 +5911,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Greenberg, 2018</t>
+          <t>Grote, 2009</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Greenberg J, Datta T, Shapero BG, Sevinc G, Mischoulon D, Lazar SW. Compassionate hearts protect against wandering minds: Self-compassion moderates the effect of mind-wandering on depression. Spirituality in Clinical Practice 2018; 5(3): 155-69.</t>
+          <t>Grote NK, Swartz HA, Geibel SL, Zuckoff A, Houck PR, Frank E. A randomized controlled trial of culturally relevant, brief interpersonal psychotherapy for perinatal depression. Psychiatric Services. 2009;60(3):313-21.</t>
         </is>
       </c>
       <c r="C87" t="b">
@@ -5107,12 +5926,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Grote, 2009</t>
+          <t>Hagen, 2017</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Grote NK, Swartz HA, Geibel SL, Zuckoff A, Houck PR, Frank E. A randomized controlled trial of culturally relevant, brief interpersonal psychotherapy for perinatal depression. Psychiatric Services. 2009;60(3):313-21.</t>
+          <t>Hagen, R., Hjemdal, O., Solem, S., Kennair, L. E. O., Nordahl, H. M., Fisher, P., &amp; Wells, A. (2017). Metacognitive therapy for depression in adults: A waiting list randomized controlled trial with six months follow-up. Frontiers in Psychology, 8.</t>
         </is>
       </c>
       <c r="C88" t="b">
@@ -5122,12 +5941,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hagen, 2017</t>
+          <t>Hallford, 2016</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hagen, R., Hjemdal, O., Solem, S., Kennair, L. E. O., Nordahl, H. M., Fisher, P., &amp; Wells, A. (2017). Metacognitive therapy for depression in adults: A waiting list randomized controlled trial with six months follow-up. Frontiers in Psychology, 8.</t>
+          <t>Hallford DJ, Mellor D. Autobiographical memory-based intervention for depressive symptoms in young adults: A randomized controlled trial of cognitive-reminiscence therapy. Psychotherapy and Psychosomatics. 2016;85(4):246-9.</t>
         </is>
       </c>
       <c r="C89" t="b">
@@ -5137,12 +5956,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hallford, 2016</t>
+          <t>Hallgren, 2015</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Hallford DJ, Mellor D. Autobiographical memory-based intervention for depressive symptoms in young adults: A randomized controlled trial of cognitive-reminiscence therapy. Psychotherapy and Psychosomatics. 2016;85(4):246-9.</t>
+          <t>Hallgren M, Kraepelien M, Öjehagen A, Lindefors N, Zeebari Z, Kaldo V, et al. Physical exercise and internet-based cognitive-behavioural therapy in the treatment of depression: Randomised controlled trial. British Journal of Psychiatry. 2015;207(3):227-34.</t>
         </is>
       </c>
       <c r="C90" t="b">
@@ -5152,12 +5971,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Hallgren, 2015</t>
+          <t>Haringsma, 2005</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hallgren M, Kraepelien M, Öjehagen A, Lindefors N, Zeebari Z, Kaldo V, et al. Physical exercise and internet-based cognitive-behavioural therapy in the treatment of depression: Randomised controlled trial. British Journal of Psychiatry. 2015;207(3):227-34.</t>
+          <t>Haringsma R, Engels G, Cuijpers P, Spinhoven P. Effectiveness of the Coping With Depression (CWD) course for older adults provided by the community-based mental health care system in the Netherlands: A randomized controlled field trial. International Psychogeriatrics. 2006;18(02):307-25.</t>
         </is>
       </c>
       <c r="C91" t="b">
@@ -5167,12 +5986,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Haringsma, 2005</t>
+          <t>Harley, 2008</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Haringsma R, Engels G, Cuijpers P, Spinhoven P. Effectiveness of the Coping With Depression (CWD) course for older adults provided by the community-based mental health care system in the Netherlands: A randomized controlled field trial. International Psychogeriatrics. 2006;18(02):307-25.</t>
+          <t>Harley R, Sprich S, Safren S, Jacobo M, Fava M. Adaptation of dialectical behavior therapy skills training group for treatment-resistant depression. Journal of Nervous and Mental Disease. 2008;196(2):136-43.</t>
         </is>
       </c>
       <c r="C92" t="b">
@@ -5182,12 +6001,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Harley, 2008</t>
+          <t>Hassiotis, 2013</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Harley R, Sprich S, Safren S, Jacobo M, Fava M. Adaptation of dialectical behavior therapy skills training group for treatment-resistant depression. Journal of Nervous and Mental Disease. 2008;196(2):136-43.</t>
+          <t>Hassiotis A, Serfaty M, Azam K, Strydom A, Blizard R, Romeo R, et al. Manualised individual cognitive behavioural therapy for mood disorders in people with mild to moderate intellectual disability: A feasibility randomised controlled trial. Journal of Affective Disorders. 2013;151(1):186-95.</t>
         </is>
       </c>
       <c r="C93" t="b">
@@ -5197,12 +6016,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Hassiotis, 2013</t>
+          <t>Hautzinger, 2004</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hassiotis A, Serfaty M, Azam K, Strydom A, Blizard R, Romeo R, et al. Manualised individual cognitive behavioural therapy for mood disorders in people with mild to moderate intellectual disability: A feasibility randomised controlled trial. Journal of Affective Disorders. 2013;151(1):186-95.</t>
+          <t>Hautzinger M, Welz S. Kognitive Verhaltenstherapie bei Depressionen im Alter: Ergebnisse einer kontrollierten Vergleichsstudie unter ambulanten Bedingungen an Depressionen mittleren Schweregrads. = Cognitive behavioral therapy for depressed older outpatients: A controlled, randomized trial. Zeitschrift für Gerontologie und Geriatrie. 2004;37(6):427-35.</t>
         </is>
       </c>
       <c r="C94" t="b">
@@ -5212,12 +6031,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Hautzinger, 2004</t>
+          <t>Hautzinger, 2008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hautzinger M, Welz S. Kognitive Verhaltenstherapie bei Depressionen im Alter: Ergebnisse einer kontrollierten Vergleichsstudie unter ambulanten Bedingungen an Depressionen mittleren Schweregrads. = Cognitive behavioral therapy for depressed older outpatients: A controlled, randomized trial. Zeitschrift für Gerontologie und Geriatrie. 2004;37(6):427-35.</t>
+          <t>Hautzinger M, Welz S. Kurz- und längerfristige wirksamkeit psychologischer interventionen bei depressionen im alter. = Short- and long-term efficacy of psychological intervention for depression in older adults. Zeitschrift für Klinische Psychologie und Psychotherapie: Forschung und Praxis. 2008;37(1):52-60.</t>
         </is>
       </c>
       <c r="C95" t="b">
@@ -5227,12 +6046,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Hautzinger, 2008</t>
+          <t>Hayden, 2012</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hautzinger M, Welz S. Kurz- und längerfristige wirksamkeit psychologischer interventionen bei depressionen im alter. = Short- and long-term efficacy of psychological intervention for depression in older adults. Zeitschrift für Klinische Psychologie und Psychotherapie: Forschung und Praxis. 2008;37(1):52-60.</t>
+          <t>Hayden T, Perantie DC, Nix BD, Barnes LD, Mostello DJ, Holcomb WL, et al. Treating prepartum depression to improve infant developmental outcomes: A study of diabetes in pregnancy. Journal of clinical psychology in medical settings. 2012;19(3):285-92.</t>
         </is>
       </c>
       <c r="C96" t="b">
@@ -5242,12 +6061,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hayden, 2012</t>
+          <t>Heckman, 2017</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hayden T, Perantie DC, Nix BD, Barnes LD, Mostello DJ, Holcomb WL, et al. Treating prepartum depression to improve infant developmental outcomes: A study of diabetes in pregnancy. Journal of clinical psychology in medical settings. 2012;19(3):285-92.</t>
+          <t>Heckman, T. G., Heckman, B. D., Anderson, T., Lovejoy, T. I., Markowitz, J. C., Shen, Y., &amp; Sutton, M. (2017). Tele-interpersonal psychotherapy acutely reduces depressive symptoms in depressed HIV-infected rural persons: A randomized clinical trial. Behavioral Medicine, 43(4), 285-295.</t>
         </is>
       </c>
       <c r="C97" t="b">
@@ -5257,12 +6076,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Heckman, 2017</t>
+          <t>Hegerl, 2010</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Heckman, T. G., Heckman, B. D., Anderson, T., Lovejoy, T. I., Markowitz, J. C., Shen, Y., &amp; Sutton, M. (2017). Tele-interpersonal psychotherapy acutely reduces depressive symptoms in depressed HIV-infected rural persons: A randomized clinical trial. Behavioral Medicine, 43(4), 285-295.</t>
+          <t>Hegerl U, Hautzinger M, Mergl R, Kohnen R, Sch¸tze M, Scheunemann W, et al. Effects of pharmacotherapy and psychotherapy in depressed primary-care patients: A randomized, controlled trial including a patients' choice arm. International Journal of Neuropsychopharmacology. 2010;13(1):31-44.</t>
         </is>
       </c>
       <c r="C98" t="b">
@@ -5272,12 +6091,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Hegerl, 2010</t>
+          <t>Hemanny, 2019</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hegerl U, Hautzinger M, Mergl R, Kohnen R, Sch¸tze M, Scheunemann W, et al. Effects of pharmacotherapy and psychotherapy in depressed primary-care patients: A randomized, controlled trial including a patients' choice arm. International Journal of Neuropsychopharmacology. 2010;13(1):31-44.</t>
+          <t>Hemanny, C., Carvalho, C., Maia, N., Reis, D., Botelho, A. C., Bonavides, D., . . . De Oliveira, I. R. (2019). Efficacy of trial-based cognitive therapy, behavioral activation and treatment as usual in the treatment of major depressive disorder: Preliminary findings from a randomized clinical trial. CNS Spectrums. doi:10.1017/S1092852919001457</t>
         </is>
       </c>
       <c r="C99" t="b">
@@ -5287,12 +6106,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Hemanny, 2019</t>
+          <t>Hermanns, 2015</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Hemanny, C., Carvalho, C., Maia, N., Reis, D., Botelho, A. C., Bonavides, D., . . . De Oliveira, I. R. (2019). Efficacy of trial-based cognitive therapy, behavioral activation and treatment as usual in the treatment of major depressive disorder: Preliminary findings from a randomized clinical trial. CNS Spectrums. doi:10.1017/S1092852919001457</t>
+          <t>Hermanns N, Schmitt A, Gahr A, Herder C, Nowotny B, Roden M, et al. The effect of a diabetes-specific cognitive behavioral treatment program (DIAMOS) for patients with diabetes and subclinical depression: Results of a randomized controlled trial. Diabetes care. 2015;38(4):551-60.</t>
         </is>
       </c>
       <c r="C100" t="b">
@@ -5302,12 +6121,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Hermanns, 2015</t>
+          <t>Herrmann-Lingen, 2016</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Hermanns N, Schmitt A, Gahr A, Herder C, Nowotny B, Roden M, et al. The effect of a diabetes-specific cognitive behavioral treatment program (DIAMOS) for patients with diabetes and subclinical depression: Results of a randomized controlled trial. Diabetes care. 2015;38(4):551-60.</t>
+          <t>Herrmann-Lingen C, Beutel ME, Bosbach A, Deter HC, Fritzsche K, Hellmich M, et al. A stepwise psychotherapy intervention for reducing risk in coronary artery disease (SPIRR-CAD): Results of an observer-blinded, multicenter, randomized trial in depressed patients with coronary artery disease. Psychosomatic Medicine. 2016;78(6):704-15.</t>
         </is>
       </c>
       <c r="C101" t="b">
@@ -5317,12 +6136,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Herrmann-Lingen, 2016</t>
+          <t>Hofheinz, 2019</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Herrmann-Lingen C, Beutel ME, Bosbach A, Deter HC, Fritzsche K, Hellmich M, et al. A stepwise psychotherapy intervention for reducing risk in coronary artery disease (SPIRR-CAD): Results of an observer-blinded, multicenter, randomized trial in depressed patients with coronary artery disease. Psychosomatic Medicine. 2016;78(6):704-15.</t>
+          <t>Hofheinz, C., Reder, M., &amp; Michalak, J. (2019). How specific is cognitive change? A randomized controlled trial comparing brief cognitive and mindfulness interventions for depression. research : journal of the Society for Research, 1-17. doi:10.1080/10503307.2019.1685138</t>
         </is>
       </c>
       <c r="C102" t="b">
@@ -5332,12 +6151,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hofheinz, 2019</t>
+          <t>Hoifodt, 2013</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hofheinz, C., Reder, M., &amp; Michalak, J. (2019). How specific is cognitive change? A randomized controlled trial comparing brief cognitive and mindfulness interventions for depression. research : journal of the Society for Research, 1-17. doi:10.1080/10503307.2019.1685138</t>
+          <t>Hoifodt, R. S., Lillevoll, K. R., Griffiths, K. M., Wilsgaard, T., Eisemann, M., Waterloo, K., &amp; Kolstrup, N. (2013). The clinical effectiveness of web-based cognitive behavioral therapy with face-to-face therapist support for depressed primary care patients: randomized controlled trial. J Med Internet Res, 15(8), e153. doi:10.2196/jmir.2714</t>
         </is>
       </c>
       <c r="C103" t="b">
@@ -5347,12 +6166,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hoifodt, 2013</t>
+          <t>Holden, 1989</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hoifodt, R. S., Lillevoll, K. R., Griffiths, K. M., Wilsgaard, T., Eisemann, M., Waterloo, K., &amp; Kolstrup, N. (2013). The clinical effectiveness of web-based cognitive behavioral therapy with face-to-face therapist support for depressed primary care patients: randomized controlled trial. J Med Internet Res, 15(8), e153. doi:10.2196/jmir.2714</t>
+          <t>Holden JM, Sagovsky R, Cox JL. Counselling in a general practice setting: Controlled study of heath visitor intervention in treatment of postnatal depression. British Medical Journal. 1989;298(6668):223-6.</t>
         </is>
       </c>
       <c r="C104" t="b">
@@ -5362,12 +6181,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Holden, 1989</t>
+          <t>Honey, 2002</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Holden JM, Sagovsky R, Cox JL. Counselling in a general practice setting: Controlled study of heath visitor intervention in treatment of postnatal depression. British Medical Journal. 1989;298(6668):223-6.</t>
+          <t>Honey KL, Bennett P, Morgan M. A brief psycho‐educational group intervention for postnatal depression. British Journal of Clinical Psychology. 2002;41(4):405-9.</t>
         </is>
       </c>
       <c r="C105" t="b">
@@ -5377,12 +6196,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Honey, 2002</t>
+          <t>Hopko, 2011</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Honey KL, Bennett P, Morgan M. A brief psycho‐educational group intervention for postnatal depression. British Journal of Clinical Psychology. 2002;41(4):405-9.</t>
+          <t>Hopko DR, Armento ME, Robertson SM, Ryba MM, Carvalho JP, Colman LK, et al. Brief behavioral activation and problem-solving therapy for depressed breast cancer patients: Randomized trial. Journal of Consulting and Clinical Psychology. 2011;79(6):834-49.</t>
         </is>
       </c>
       <c r="C106" t="b">
@@ -5392,12 +6211,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Hopko, 2011</t>
+          <t>Horrell, 2014</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hopko DR, Armento ME, Robertson SM, Ryba MM, Carvalho JP, Colman LK, et al. Brief behavioral activation and problem-solving therapy for depressed breast cancer patients: Randomized trial. Journal of Consulting and Clinical Psychology. 2011;79(6):834-49.</t>
+          <t>Horrell L, Goldsmith KA, Tylee AT, Schmidt UH, Murphy CL, Bonin E-M, et al. One-day cognitive–behavioural therapy self-confidence workshops for people with depression: Randomised controlled trial. The British Journal of Psychiatry. 2014;204(3):222-33.</t>
         </is>
       </c>
       <c r="C107" t="b">
@@ -5407,12 +6226,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Horrell, 2014</t>
+          <t>Hou, 2014</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Horrell L, Goldsmith KA, Tylee AT, Schmidt UH, Murphy CL, Bonin E-M, et al. One-day cognitive–behavioural therapy self-confidence workshops for people with depression: Randomised controlled trial. The British Journal of Psychiatry. 2014;204(3):222-33.</t>
+          <t>Hou Y, Hu P, Zhang Y, Lu Q, Wang D, Yin L, et al. Cognitive behavioral therapy in combination with systemic family therapy improves mild to moderate postpartum depression. Revista Brasileira de Psiquiatria. 2014;36(1):47-52.</t>
         </is>
       </c>
       <c r="C108" t="b">
@@ -5422,12 +6241,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Hou, 2014</t>
+          <t>Huang, 2016</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hou Y, Hu P, Zhang Y, Lu Q, Wang D, Yin L, et al. Cognitive behavioral therapy in combination with systemic family therapy improves mild to moderate postpartum depression. Revista Brasileira de Psiquiatria. 2014;36(1):47-52.</t>
+          <t>Huang, C.-Y., Lai, H.-L., Chen, C.-I., Lu, Y.-C., Li, S.-C., Wang, L.-W., &amp; Su, Y. (2016). Effects of motivational enhancement therapy plus cognitive behaviour therapy on depressive symptoms and health-related quality of life in adults with type II diabetes mellitus: A randomised controlled trial. Quality of Life Research: An International Journal of Quality of Life Aspects of Treatment, Care &amp; Rehabilitation, 25(5), 1275-1283.</t>
         </is>
       </c>
       <c r="C109" t="b">
@@ -5437,12 +6256,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Huang, 2016</t>
+          <t>Hum, 2019</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Huang, C.-Y., Lai, H.-L., Chen, C.-I., Lu, Y.-C., Li, S.-C., Wang, L.-W., &amp; Su, Y. (2016). Effects of motivational enhancement therapy plus cognitive behaviour therapy on depressive symptoms and health-related quality of life in adults with type II diabetes mellitus: A randomised controlled trial. Quality of Life Research: An International Journal of Quality of Life Aspects of Treatment, Care &amp; Rehabilitation, 25(5), 1275-1283.</t>
+          <t>Hum, K. M., Chan, C. J., Gane, J., Conway, L., McAndrews, M. P., &amp; Smith, M. L. (2019). Do distance-delivery group interventions improve depression in people with epilepsy? Epilepsy &amp; Behavior, 98, 153‐160. doi:10.1016/j.yebeh.2019.06.037</t>
         </is>
       </c>
       <c r="C110" t="b">
@@ -5452,12 +6271,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Hum, 2019</t>
+          <t>Hummel, 2017</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hum, K. M., Chan, C. J., Gane, J., Conway, L., McAndrews, M. P., &amp; Smith, M. L. (2019). Do distance-delivery group interventions improve depression in people with epilepsy? Epilepsy &amp; Behavior, 98, 153‐160. doi:10.1016/j.yebeh.2019.06.037</t>
+          <t>Hummel, J., Weisbrod, C., Boesch, L., Himpler, K., Hauer, K., Hautzinger, M., . . . Kopf, D. (2017). AIDE–Acute Illness and Depression in Elderly Patients. Cognitive Behavioral Group Psychotherapy in Geriatric Patients With Comorbid Depression: A Randomized, Controlled Trial. Journal of the american medical directors association, 18(4), 341-349.</t>
         </is>
       </c>
       <c r="C111" t="b">
@@ -5467,12 +6286,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Hummel, 2017</t>
+          <t>Hunter, 2012 I</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Hummel, J., Weisbrod, C., Boesch, L., Himpler, K., Hauer, K., Hautzinger, M., . . . Kopf, D. (2017). AIDE–Acute Illness and Depression in Elderly Patients. Cognitive Behavioral Group Psychotherapy in Geriatric Patients With Comorbid Depression: A Randomized, Controlled Trial. Journal of the american medical directors association, 18(4), 341-349.</t>
+          <t>Hunter SB, Watkins KE, Hepner KA, Paddock SM, Ewing BA, Osilla KC, et al. Treating depression and substance use: A randomized controlled trial. Journal of substance abuse treatment. 2012;43(2):137-51.</t>
         </is>
       </c>
       <c r="C112" t="b">
@@ -5482,12 +6301,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Hunter, 2012 I</t>
+          <t>Husain, 2017</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hunter SB, Watkins KE, Hepner KA, Paddock SM, Ewing BA, Osilla KC, et al. Treating depression and substance use: A randomized controlled trial. Journal of substance abuse treatment. 2012;43(2):137-51.</t>
+          <t>Husain, N., Zulqernain, F., Carter, L.-A., Chaudhry, I., Fatima, B., Kiran, T., . . . Rahman, A. (2017). Treatment of maternal depression in urban slums of Karachi, Pakistan: a randomized controlled trial (RCT) of an integrated maternal psychological and early child development intervention. Asian journal of psychiatry, 29, 63-70.</t>
         </is>
       </c>
       <c r="C113" t="b">
@@ -5497,12 +6316,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Husain, 2017</t>
+          <t>Jarett, 1999</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Husain, N., Zulqernain, F., Carter, L.-A., Chaudhry, I., Fatima, B., Kiran, T., . . . Rahman, A. (2017). Treatment of maternal depression in urban slums of Karachi, Pakistan: a randomized controlled trial (RCT) of an integrated maternal psychological and early child development intervention. Asian journal of psychiatry, 29, 63-70.</t>
+          <t>Jarrett RB, Schaffer M, McIntire D, Witt-Browder A, Kraft D, Risser RC. Treatment of atypical depression with cognitive therapy or phenelzine: A double-blind, placebo-controlled trial. Archives of General Psychiatry. 1999;56(5):431-7.</t>
         </is>
       </c>
       <c r="C114" t="b">
@@ -5512,12 +6331,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jarett, 1999</t>
+          <t>Jesse, 2015</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jarrett RB, Schaffer M, McIntire D, Witt-Browder A, Kraft D, Risser RC. Treatment of atypical depression with cognitive therapy or phenelzine: A double-blind, placebo-controlled trial. Archives of General Psychiatry. 1999;56(5):431-7.</t>
+          <t>Jesse DE, Gaynes BN, Feldhousen EB, Newton ER, Bunch S, Hollon SD. Performance of a culturally tailored cognitive-behavioral intervention integrated in a public health setting to reduce risk of antepartum depression: A randomized controlled trial. Journal of Midwifery and Women's Health. 2015;60(5):578-92.</t>
         </is>
       </c>
       <c r="C115" t="b">
@@ -5527,12 +6346,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Jesse, 2015</t>
+          <t>Johansson, 2012 - I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jesse DE, Gaynes BN, Feldhousen EB, Newton ER, Bunch S, Hollon SD. Performance of a culturally tailored cognitive-behavioral intervention integrated in a public health setting to reduce risk of antepartum depression: A randomized controlled trial. Journal of Midwifery and Women's Health. 2015;60(5):578-92.</t>
+          <t>Johansson R, Ekbladh S, Hebert A, Lindström M, Möller S, Petitt E, et al. Psychodynamic guided self-help for adult depression through the internet: A randomised controlled trial. PloS One. 2012;7(5):e38021.</t>
         </is>
       </c>
       <c r="C116" t="b">
@@ -5542,12 +6361,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Johansson, 2012 - I</t>
+          <t>Johansson, 2019</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Johansson R, Ekbladh S, Hebert A, Lindström M, Möller S, Petitt E, et al. Psychodynamic guided self-help for adult depression through the internet: A randomised controlled trial. PloS One. 2012;7(5):e38021.</t>
+          <t>Johansson, O., Bjärehed, J., Andersson, G., Carlbring, P., &amp; Lundh, L. G. (2019). Effectiveness of guided internet-delivered cognitive behavior therapy for depression in routine psychiatry: A randomized controlled trial. Internet Interventions, 17. doi:10.1016/j.invent.2019.100247</t>
         </is>
       </c>
       <c r="C117" t="b">
@@ -5557,12 +6376,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Johansson, 2019</t>
+          <t>Johnson, 2016</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Johansson, O., Bjärehed, J., Andersson, G., Carlbring, P., &amp; Lundh, L. G. (2019). Effectiveness of guided internet-delivered cognitive behavior therapy for depression in routine psychiatry: A randomized controlled trial. Internet Interventions, 17. doi:10.1016/j.invent.2019.100247</t>
+          <t>Johnson, J. E., Price, A. B., Kao, J. C., Fernandes, K., Stout, R., Gobin, R. L., &amp; Zlotnick, C. (2016). Interpersonal psychotherapy (IPT) for major depression following perinatal loss: a pilot randomized controlled trial. Archives of Women's Mental Health, 19(5), 845-859.</t>
         </is>
       </c>
       <c r="C118" t="b">
@@ -5572,12 +6391,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Johnson, 2016</t>
+          <t>Johnson, 2019</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Johnson, J. E., Price, A. B., Kao, J. C., Fernandes, K., Stout, R., Gobin, R. L., &amp; Zlotnick, C. (2016). Interpersonal psychotherapy (IPT) for major depression following perinatal loss: a pilot randomized controlled trial. Archives of Women's Mental Health, 19(5), 845-859.</t>
+          <t>Johnson, J. E., Stout, R. L., Miller, T. R., Zlotnick, C., Cerbo, L. A., Andrade, J. T., . . . Wiltsey-Stirman, S. (2019). Randomized cost-effectiveness trial of group interpersonal psychotherapy (IPT) for prisoners with major depression. Journal of consulting and clinical psychology, 87(4), 392-406. doi:10.1037/ccp0000379</t>
         </is>
       </c>
       <c r="C119" t="b">
@@ -5587,12 +6406,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Johnson, 2019</t>
+          <t>Joling, 2011</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Johnson, J. E., Stout, R. L., Miller, T. R., Zlotnick, C., Cerbo, L. A., Andrade, J. T., . . . Wiltsey-Stirman, S. (2019). Randomized cost-effectiveness trial of group interpersonal psychotherapy (IPT) for prisoners with major depression. Journal of consulting and clinical psychology, 87(4), 392-406. doi:10.1037/ccp0000379</t>
+          <t>Joling KJ, Hout HP, van't Veer-Tazelaar PJ, Horst HE, Cuijpers P, Ven PM, et al. How effective is bibliotherapy for very old adults with subthreshold depression? A randomized controlled trial. American Journal of Geriatric Psychiatry. 2011;19(3):256-65.</t>
         </is>
       </c>
       <c r="C120" t="b">
@@ -5602,12 +6421,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Joling, 2011</t>
+          <t>Jordans, 2019</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Joling KJ, Hout HP, van't Veer-Tazelaar PJ, Horst HE, Cuijpers P, Ven PM, et al. How effective is bibliotherapy for very old adults with subthreshold depression? A randomized controlled trial. American Journal of Geriatric Psychiatry. 2011;19(3):256-65.</t>
+          <t>Jordans, M. J. D., Luitel, N. P., Garman, E., Kohrt, B. A., Rathod, S. D., Shrestha, P., . . . Patel, V. (2019). Effectiveness of psychological treatments for depression and alcohol use disorder delivered by community-based counsellors: Two pragmatic randomised controlled trials within primary healthcare in Nepal. British Journal of Psychiatry, 215(2), 485-493. doi:10.1192/bjp.2018.300</t>
         </is>
       </c>
       <c r="C121" t="b">
@@ -5617,12 +6436,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Jordans, 2019</t>
+          <t>Kamga, 2017</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jordans, M. J. D., Luitel, N. P., Garman, E., Kohrt, B. A., Rathod, S. D., Shrestha, P., . . . Patel, V. (2019). Effectiveness of psychological treatments for depression and alcohol use disorder delivered by community-based counsellors: Two pragmatic randomised controlled trials within primary healthcare in Nepal. British Journal of Psychiatry, 215(2), 485-493. doi:10.1192/bjp.2018.300</t>
+          <t>Kamga, H., McCusker, J., Yaffe, M., Sewitch, M., Sussman, T., Strumpf, E., . . . Freeman, E. (2017). Self-care tools to treat depressive symptoms in patients with age-related eye disease: a randomized controlled clinical trial. Clinical &amp; experimental ophthalmology, 45(4), 371-378.</t>
         </is>
       </c>
       <c r="C122" t="b">
@@ -5632,12 +6451,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kamga, 2017</t>
+          <t>Kay-Lambkin, 2011</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Kamga, H., McCusker, J., Yaffe, M., Sewitch, M., Sussman, T., Strumpf, E., . . . Freeman, E. (2017). Self-care tools to treat depressive symptoms in patients with age-related eye disease: a randomized controlled clinical trial. Clinical &amp; experimental ophthalmology, 45(4), 371-378.</t>
+          <t>Kay-Lambkin FJ, Baker AL, Kelly B, Lewin TJ. Clinician-assisted computerised versus therapist-delivered treatment for depressive and addictive disorders: A randomised controlled trial. The Medical journal of Australia. 2011;195(3):S44-50.</t>
         </is>
       </c>
       <c r="C123" t="b">
@@ -5647,12 +6466,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kay-Lambkin, 2011</t>
+          <t>Kelly, 1993</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Kay-Lambkin FJ, Baker AL, Kelly B, Lewin TJ. Clinician-assisted computerised versus therapist-delivered treatment for depressive and addictive disorders: A randomised controlled trial. The Medical journal of Australia. 2011;195(3):S44-50.</t>
+          <t>Kelly JA, Murphy DA, Bahr GR, Kalichman SC, Morgan MG, Stevenson LY, et al. Outcome of cognitive-behavioral and support group brief therapies for depressed, HIV-infected persons. American Journal of Psychiatry. 1993;150(11):1679-86.</t>
         </is>
       </c>
       <c r="C124" t="b">
@@ -5662,12 +6481,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kelly, 1993</t>
+          <t>Kenter, 2016</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kelly JA, Murphy DA, Bahr GR, Kalichman SC, Morgan MG, Stevenson LY, et al. Outcome of cognitive-behavioral and support group brief therapies for depressed, HIV-infected persons. American Journal of Psychiatry. 1993;150(11):1679-86.</t>
+          <t>Kenter, R. M. F., Cuijpers, P., Beekman, A., &amp; van Straten, A. (2016). Effectiveness of a Web-based guided self-help intervention for outpatients with a depressive disorder: Short-term results from a randomized controlled trial. Journal of medical Internet research, 18(3).</t>
         </is>
       </c>
       <c r="C125" t="b">
@@ -5677,12 +6496,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Kenter, 2016</t>
+          <t>Kessler, 2009</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Kenter, R. M. F., Cuijpers, P., Beekman, A., &amp; van Straten, A. (2016). Effectiveness of a Web-based guided self-help intervention for outpatients with a depressive disorder: Short-term results from a randomized controlled trial. Journal of medical Internet research, 18(3).</t>
+          <t>Kessler D, Lewis G, Kaur S, Wiles N, King M, Weich S, et al. Therapist-delivered Internet psychotherapy for depression in primary care: A randomised controlled trial. Lancet. 2009;374(9690):628-34.</t>
         </is>
       </c>
       <c r="C126" t="b">
@@ -5692,12 +6511,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kessler, 2009</t>
+          <t>Kim, 2018</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kessler D, Lewis G, Kaur S, Wiles N, King M, Weich S, et al. Therapist-delivered Internet psychotherapy for depression in primary care: A randomised controlled trial. Lancet. 2009;374(9690):628-34.</t>
+          <t>Kim YH, Choi KS, Han K, Kim HW. A psychological intervention programme for patients with breast cancer under chemotherapy and at a high risk of depression: a randomised clinical trial. Journal of clinical nursing 2018; 27(3‐4): 572‐81.</t>
         </is>
       </c>
       <c r="C127" t="b">
@@ -5707,12 +6526,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kim, 2018</t>
+          <t>King, 2000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kim YH, Choi KS, Han K, Kim HW. A psychological intervention programme for patients with breast cancer under chemotherapy and at a high risk of depression: a randomised clinical trial. Journal of clinical nursing 2018; 27(3‐4): 572‐81.</t>
+          <t>King M, Sibbald B, Ward E, Bower P, Lloyd M, Gabbay M, et al. Randomised controlled trial of non-directive counselling, cognitive-behaviour therapy and usual general practitioner care in the management of depression as well as mixed anxiety and depression in primary care. Health Technology Assessment. 2000;4(19):1-83.</t>
         </is>
       </c>
       <c r="C128" t="b">
@@ -5722,12 +6541,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>King, 2000</t>
+          <t>Kiosses, 2010</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>King M, Sibbald B, Ward E, Bower P, Lloyd M, Gabbay M, et al. Randomised controlled trial of non-directive counselling, cognitive-behaviour therapy and usual general practitioner care in the management of depression as well as mixed anxiety and depression in primary care. Health Technology Assessment. 2000;4(19):1-83.</t>
+          <t>Kiosses DN, Arean PA, Teri L, Alexopoulos GS. Home-delivered problem adaptation therapy (PATH) for depressed, cognitively impaired, disabled elders: A preliminary study. The American Journal of Geriatric Psychiatry. 2010;18(11):988-98.</t>
         </is>
       </c>
       <c r="C129" t="b">
@@ -5737,12 +6556,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kiosses, 2010</t>
+          <t>Kiosses, 2015</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kiosses DN, Arean PA, Teri L, Alexopoulos GS. Home-delivered problem adaptation therapy (PATH) for depressed, cognitively impaired, disabled elders: A preliminary study. The American Journal of Geriatric Psychiatry. 2010;18(11):988-98.</t>
+          <t>Kiosses DN, Ravdin LD, Gross JJ, Raue P, Kotbi N, Alexopoulos GS. Problem adaptation therapy for older adults with major depression and cognitive impairment: A randomized clinical trial. JAMA psychiatry. 2015;72(1):22-30.</t>
         </is>
       </c>
       <c r="C130" t="b">
@@ -5752,12 +6571,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kiosses, 2015</t>
+          <t>Kivi, 2014</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Kiosses DN, Ravdin LD, Gross JJ, Raue P, Kotbi N, Alexopoulos GS. Problem adaptation therapy for older adults with major depression and cognitive impairment: A randomized clinical trial. JAMA psychiatry. 2015;72(1):22-30.</t>
+          <t>Kivi M, Eriksson MCM, Hange D, Petersson E-L, Vernmark K, Johansson B, et al. Internet-based therapy for mild to moderate depression in Swedish primary care: Short term results from the PRIM-NET randomized controlled trial. Cognitive Behaviour Therapy. 2014;43(4):289-98.</t>
         </is>
       </c>
       <c r="C131" t="b">
@@ -5767,12 +6586,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kivi, 2014</t>
+          <t>Kleiboer, 2015</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Kivi M, Eriksson MCM, Hange D, Petersson E-L, Vernmark K, Johansson B, et al. Internet-based therapy for mild to moderate depression in Swedish primary care: Short term results from the PRIM-NET randomized controlled trial. Cognitive Behaviour Therapy. 2014;43(4):289-98.</t>
+          <t>Kleiboer A, Donker T, Seekles W, van Straten A, Riper H, Cuijpers P. A randomized controlled trial on the role of support in Internet-based problem solving therapy for depression and anxiety. Behaviour Research and Therapy. 2015;72:63-71.</t>
         </is>
       </c>
       <c r="C132" t="b">
@@ -5782,12 +6601,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Kleiboer, 2015</t>
+          <t>Korte, 2012</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kleiboer A, Donker T, Seekles W, van Straten A, Riper H, Cuijpers P. A randomized controlled trial on the role of support in Internet-based problem solving therapy for depression and anxiety. Behaviour Research and Therapy. 2015;72:63-71.</t>
+          <t>Korte J, Bohlmeijer ET, Cappeliez P, Smit F, Westerhof GJ. Life review therapy for older adults with moderate depressive symptomatology: A pragmatic randomized controlled trial. Psychological Medicine. 2012;42(6):1163-73.</t>
         </is>
       </c>
       <c r="C133" t="b">
@@ -5797,12 +6616,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Korte, 2012</t>
+          <t>Koszycki, 2012</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Korte J, Bohlmeijer ET, Cappeliez P, Smit F, Westerhof GJ. Life review therapy for older adults with moderate depressive symptomatology: A pragmatic randomized controlled trial. Psychological Medicine. 2012;42(6):1163-73.</t>
+          <t>Koszycki D, Bisserbe J-C, Blier P, Bradwejn J, Markowitz J. Interpersonal psychotherapy versus brief supportive therapy for depressed infertile women: First pilot randomized controlled trial. Archives of Women's Mental Health. 2012;15(3):193-201.</t>
         </is>
       </c>
       <c r="C134" t="b">
@@ -5812,12 +6631,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Koszycki, 2012</t>
+          <t>Laidlaw, 2008</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Koszycki D, Bisserbe J-C, Blier P, Bradwejn J, Markowitz J. Interpersonal psychotherapy versus brief supportive therapy for depressed infertile women: First pilot randomized controlled trial. Archives of Women's Mental Health. 2012;15(3):193-201.</t>
+          <t>Laidlaw K, Davidson K, Toner H, Jackson G, Clark S, Law J, et al. A randomised controlled trial of cognitive behaviour therapy vs treatment as usual in the treatment of mild to moderate late life depression. International Journal of Geriatric Psychiatry. 2008;23(8):843-50.</t>
         </is>
       </c>
       <c r="C135" t="b">
@@ -5827,12 +6646,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Laidlaw, 2008</t>
+          <t>Lamers, 2010</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Laidlaw K, Davidson K, Toner H, Jackson G, Clark S, Law J, et al. A randomised controlled trial of cognitive behaviour therapy vs treatment as usual in the treatment of mild to moderate late life depression. International Journal of Geriatric Psychiatry. 2008;23(8):843-50.</t>
+          <t>Lamers F, Jonkers CC, Bosma H, Kempen GI, Meijer JA, Penninx BW, et al. A minimal psychological intervention in chronically ill elderly patients with depression: A randomized trial. Psychotherapy and Psychosomatics. 2010;79(4):217-26.</t>
         </is>
       </c>
       <c r="C136" t="b">
@@ -5842,12 +6661,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Lamers, 2010</t>
+          <t>Lamers, 2015</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lamers F, Jonkers CC, Bosma H, Kempen GI, Meijer JA, Penninx BW, et al. A minimal psychological intervention in chronically ill elderly patients with depression: A randomized trial. Psychotherapy and Psychosomatics. 2010;79(4):217-26.</t>
+          <t>Lamers SMA, Bohlmeijer ET, Korte J, Westerhof GJ. The efficacy of life-review as online-guided self-help for adults: A randomized trial. The Journals of Gerontology: Series B: Psychological Sciences and Social Sciences 2015; 70B(1): 24-34.</t>
         </is>
       </c>
       <c r="C137" t="b">
@@ -5857,12 +6676,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Lamers, 2015</t>
+          <t>Landreville, 1997</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Lamers SMA, Bohlmeijer ET, Korte J, Westerhof GJ. The efficacy of life-review as online-guided self-help for adults: A randomized trial. The Journals of Gerontology: Series B: Psychological Sciences and Social Sciences 2015; 70B(1): 24-34.</t>
+          <t>Landreville P, Bissonnette L. Effects of cognitive bibliotherapy for depressed older adults with a disability. Clinical Gerontologist. 1997;17(4):35-55.</t>
         </is>
       </c>
       <c r="C138" t="b">
@@ -5872,12 +6691,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Landreville, 1997</t>
+          <t>Lappalainen, 2015</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Landreville P, Bissonnette L. Effects of cognitive bibliotherapy for depressed older adults with a disability. Clinical Gerontologist. 1997;17(4):35-55.</t>
+          <t>Lappalainen P, Langrial S, Oinas-Kukkonen H, Tolvanen A, Lappalainen R. Web-based acceptance and commitment therapy for depressive symptoms with minimal support: A randomized controlled trial. Behavior modification. 2015;39(6):805-34.</t>
         </is>
       </c>
       <c r="C139" t="b">
@@ -5887,12 +6706,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Lappalainen, 2015</t>
+          <t>Larcombe, 1984</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Lappalainen P, Langrial S, Oinas-Kukkonen H, Tolvanen A, Lappalainen R. Web-based acceptance and commitment therapy for depressive symptoms with minimal support: A randomized controlled trial. Behavior modification. 2015;39(6):805-34.</t>
+          <t>Larcombe NA, Wilson PH. An evaluation of cognitive-behaviour therapy for depression in patients with multiple sclerosis. The British Journal of Psychiatry. 1984;145:366-71.</t>
         </is>
       </c>
       <c r="C140" t="b">
@@ -5902,12 +6721,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Larcombe, 1984</t>
+          <t>Lemmens, 2015</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Larcombe NA, Wilson PH. An evaluation of cognitive-behaviour therapy for depression in patients with multiple sclerosis. The British Journal of Psychiatry. 1984;145:366-71.</t>
+          <t>Lemmens LHJM, Arntz A, Peeters F, Hollon SD, Roefs A, Huibers MJH. Clinical effectiveness of cognitive therapy v. interpersonal psychotherapy for depression: Results of a randomized controlled trial. Psychological Medicine. 2015;45(10):2095-110.</t>
         </is>
       </c>
       <c r="C141" t="b">
@@ -5917,12 +6736,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lemmens, 2015</t>
+          <t>Lenze, 2017</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Lemmens LHJM, Arntz A, Peeters F, Hollon SD, Roefs A, Huibers MJH. Clinical effectiveness of cognitive therapy v. interpersonal psychotherapy for depression: Results of a randomized controlled trial. Psychological Medicine. 2015;45(10):2095-110.</t>
+          <t>Lenze, S., &amp; Potts, M. (2017). Brief Interpersonal Psychotherapy for depression during pregnancy in a low-income population: a randomized controlled trial. Journal of Affective Disorders, 210, 151-157.</t>
         </is>
       </c>
       <c r="C142" t="b">
@@ -5932,12 +6751,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lenze, 2017</t>
+          <t>Lerner, 2015</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lenze, S., &amp; Potts, M. (2017). Brief Interpersonal Psychotherapy for depression during pregnancy in a low-income population: a randomized controlled trial. Journal of Affective Disorders, 210, 151-157.</t>
+          <t>Lerner D, Adler DA, Rogers WH, Chang H, Greenhill A, Cymerman E, et al. A randomized clinical trial of a telephone depression intervention to reduce employee presenteeism and absenteeism. Psychiatric Services. 2015;66(6):570-7.</t>
         </is>
       </c>
       <c r="C143" t="b">
@@ -5947,12 +6766,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Lerner, 2015</t>
+          <t>Leuzinger-Bohleber, 2019</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Lerner D, Adler DA, Rogers WH, Chang H, Greenhill A, Cymerman E, et al. A randomized clinical trial of a telephone depression intervention to reduce employee presenteeism and absenteeism. Psychiatric Services. 2015;66(6):570-7.</t>
+          <t>Leuzinger-Bohleber, M., Hautzinger, M., Fiedler, G., Keller, W., Bahrke, U., Kallenbach, L., . . . Beutel, M. (2019). Outcome of Psychoanalytic and Cognitive-Behavioural Long-Term Therapy with Chronically Depressed Patients: A Controlled Trial with Preferential and Randomized Allocation. Canadian Journal of Psychiatry, 64(1), 47-58. doi:10.1177/0706743718780340</t>
         </is>
       </c>
       <c r="C144" t="b">
@@ -5962,12 +6781,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Leuzinger-Bohleber, 2019</t>
+          <t>Lexis, 2011</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Leuzinger-Bohleber, M., Hautzinger, M., Fiedler, G., Keller, W., Bahrke, U., Kallenbach, L., . . . Beutel, M. (2019). Outcome of Psychoanalytic and Cognitive-Behavioural Long-Term Therapy with Chronically Depressed Patients: A Controlled Trial with Preferential and Randomized Allocation. Canadian Journal of Psychiatry, 64(1), 47-58. doi:10.1177/0706743718780340</t>
+          <t>Lexis MA, Jansen NW, Huibers MJ, Amelsvoort LG, Berkouwer A, Tjin ATG, et al. Prevention of long-term sickness absence and major depression in high-risk employees: A randomised controlled trial. Occupational and Environmental Medicine. 2011;68(6):400-7.</t>
         </is>
       </c>
       <c r="C145" t="b">
@@ -5977,12 +6796,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Lexis, 2011</t>
+          <t>Liu, 2009</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lexis MA, Jansen NW, Huibers MJ, Amelsvoort LG, Berkouwer A, Tjin ATG, et al. Prevention of long-term sickness absence and major depression in high-risk employees: A randomised controlled trial. Occupational and Environmental Medicine. 2011;68(6):400-7.</t>
+          <t>Liu ET-H, Chen W-L, Li Y-H, Wang CH, Mok TJ, Huang HS. Exploring the efficacy of cognitive bibliotherapy and a potential mechanism of change in the treatment of depressive symptoms among the Chinese: A randomized controlled trial. Cognitive Therapy and Research. 2009;33(5):449-61.</t>
         </is>
       </c>
       <c r="C146" t="b">
@@ -5992,12 +6811,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Liu, 2009</t>
+          <t>Losada, 2015</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Liu ET-H, Chen W-L, Li Y-H, Wang CH, Mok TJ, Huang HS. Exploring the efficacy of cognitive bibliotherapy and a potential mechanism of change in the treatment of depressive symptoms among the Chinese: A randomized controlled trial. Cognitive Therapy and Research. 2009;33(5):449-61.</t>
+          <t>Losada A, Márquez-González M, Romero-Moreno R, Mausbach BT, López J, Fernández-Fernández V, et al. Cognitive–behavioral therapy (CBT) versus acceptance and commitment therapy (ACT) for dementia family caregivers with significant depressive symptoms: Results of a randomized clinical trial. Journal of Consulting and Clinical Psychology. 2015;83(4):760-72.</t>
         </is>
       </c>
       <c r="C147" t="b">
@@ -6007,12 +6826,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Losada, 2015</t>
+          <t>Lovell, 2008</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Losada A, Márquez-González M, Romero-Moreno R, Mausbach BT, López J, Fernández-Fernández V, et al. Cognitive–behavioral therapy (CBT) versus acceptance and commitment therapy (ACT) for dementia family caregivers with significant depressive symptoms: Results of a randomized clinical trial. Journal of Consulting and Clinical Psychology. 2015;83(4):760-72.</t>
+          <t>Lovell K, Bower P, Richards D, Barkham Mi, Sibbald B, Roberts C, et al. Developing guided self-help for depression using the medical research council complex interventions framework: A description of the modelling phase and results of an exploratory randomised controlled trial. BMC psychiatry. 2008;8.</t>
         </is>
       </c>
       <c r="C148" t="b">
@@ -6022,12 +6841,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Lovell, 2008</t>
+          <t>Lustman, 1998</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lovell K, Bower P, Richards D, Barkham Mi, Sibbald B, Roberts C, et al. Developing guided self-help for depression using the medical research council complex interventions framework: A description of the modelling phase and results of an exploratory randomised controlled trial. BMC psychiatry. 2008;8.</t>
+          <t>Lustman PJ, Griffith LS, Freedland KE, Kissel SS, Clouse RE. Cognitive behavior therapy for depression in type 2 diabetes mellitus. A randomized, controlled trial. Annals of Internal Medicine. 1998;129(8):613-21.</t>
         </is>
       </c>
       <c r="C149" t="b">
@@ -6037,12 +6856,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Lustman, 1998</t>
+          <t>Luty, 2007</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lustman PJ, Griffith LS, Freedland KE, Kissel SS, Clouse RE. Cognitive behavior therapy for depression in type 2 diabetes mellitus. A randomized, controlled trial. Annals of Internal Medicine. 1998;129(8):613-21.</t>
+          <t>Luty SE, Carter JD, McKenzie JM, Rae AM, Frampton CM, Mulder RT, et al. Randomised controlled trial of interpersonal psychotherapy and cognitive-behavioural therapy for depression. The British Journal of Psychiatry. 2007;190:496-502.</t>
         </is>
       </c>
       <c r="C150" t="b">
@@ -6052,12 +6871,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Luty, 2007</t>
+          <t>Ly, 2014</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Luty SE, Carter JD, McKenzie JM, Rae AM, Frampton CM, Mulder RT, et al. Randomised controlled trial of interpersonal psychotherapy and cognitive-behavioural therapy for depression. The British Journal of Psychiatry. 2007;190:496-502.</t>
+          <t>Ly KH, Truschel A, Jarl L, Magnusson S, Windahl T, Johansson R, et al. Behavioural activation versus mindfulness-based guided self-help treatment administered through a smartphone application: A randomised controlled trial. BMJ Open. 2014;4(1):e003440.</t>
         </is>
       </c>
       <c r="C151" t="b">
@@ -6067,12 +6886,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ly, 2014</t>
+          <t>Lynch, 1997</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ly KH, Truschel A, Jarl L, Magnusson S, Windahl T, Johansson R, et al. Behavioural activation versus mindfulness-based guided self-help treatment administered through a smartphone application: A randomised controlled trial. BMJ Open. 2014;4(1):e003440.</t>
+          <t>Lynch DJ, Tamburrino MB, Nagel R. Telephone counseling for patients with minor depression: Preliminary findings in a family practice setting. The Journal of family practice. 1997;44(3):293-8.</t>
         </is>
       </c>
       <c r="C152" t="b">
@@ -6082,12 +6901,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Lynch, 1997</t>
+          <t>Lynch, 2004</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lynch DJ, Tamburrino MB, Nagel R. Telephone counseling for patients with minor depression: Preliminary findings in a family practice setting. The Journal of family practice. 1997;44(3):293-8.</t>
+          <t>Lynch D, Tamburrino M, Nagel R, Smith MK. Telephone-based treatment for family practice patients with mild depression. Psychological reports. 2004;94(3 Pt 1):785-92.</t>
         </is>
       </c>
       <c r="C153" t="b">
@@ -6097,12 +6916,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Lynch, 2004</t>
+          <t>Lök, 2019</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lynch D, Tamburrino M, Nagel R, Smith MK. Telephone-based treatment for family practice patients with mild depression. Psychological reports. 2004;94(3 Pt 1):785-92.</t>
+          <t>Lök, N., Bademli, K., &amp; Selçuk-Tosun, A. (2019). The effect of reminiscence therapy on cognitive functions, depression, and quality of life in Alzheimer patients: randomized controlled trial. International Journal of Geriatric Psychiatry, 34(1), 47‐53. doi:10.1002/gps.4980</t>
         </is>
       </c>
       <c r="C154" t="b">
@@ -6112,12 +6931,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Lök, 2019</t>
+          <t>MacPherson, 2013</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lök, N., Bademli, K., &amp; Selçuk-Tosun, A. (2019). The effect of reminiscence therapy on cognitive functions, depression, and quality of life in Alzheimer patients: randomized controlled trial. International Journal of Geriatric Psychiatry, 34(1), 47‐53. doi:10.1002/gps.4980</t>
+          <t>MacPherson H, Richmond S, Bland M, Brealey S, Gabe R, Hopton A, et al. Acupuncture and counselling for depression in primary care: A randomised controlled trial. PLoS medicine. 2013;10(9):e1001518.</t>
         </is>
       </c>
       <c r="C155" t="b">
@@ -6127,12 +6946,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MacPherson, 2013</t>
+          <t>Maina, 2005</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MacPherson H, Richmond S, Bland M, Brealey S, Gabe R, Hopton A, et al. Acupuncture and counselling for depression in primary care: A randomised controlled trial. PLoS medicine. 2013;10(9):e1001518.</t>
+          <t>Maina G, Forner F, Bogetto F. Randomized controlled trial comparing brief dynamic and supportive therapy with waiting list condition in minor depressive disorders. Psychotherapy and Psychosomatics. 2005;74(1):43-50.</t>
         </is>
       </c>
       <c r="C156" t="b">
@@ -6142,12 +6961,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Maina, 2005</t>
+          <t>Maldonado, 1982</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Maina G, Forner F, Bogetto F. Randomized controlled trial comparing brief dynamic and supportive therapy with waiting list condition in minor depressive disorders. Psychotherapy and Psychosomatics. 2005;74(1):43-50.</t>
+          <t>Maldonado López A. Terapia de conducta y depresión: Un análisis experimental de los modelos conductual y cognitivo. Revista de Psicologia General y Aplicada. 1982.</t>
         </is>
       </c>
       <c r="C157" t="b">
@@ -6157,12 +6976,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Maldonado, 1982</t>
+          <t>Malouff, 1988</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Maldonado López A. Terapia de conducta y depresión: Un análisis experimental de los modelos conductual y cognitivo. Revista de Psicologia General y Aplicada. 1982.</t>
+          <t>Malouff JM, Lanyon RI, Schutte NS. Effectiveness of a brief group RET treatment for divorce-related dysphoria. Journal of Rational-Emotive and Cognitive-Behavior Therapy. 1988;6(3):162-71.</t>
         </is>
       </c>
       <c r="C158" t="b">
@@ -6172,12 +6991,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Malouff, 1988</t>
+          <t>Manicavasgar, 2011</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Malouff JM, Lanyon RI, Schutte NS. Effectiveness of a brief group RET treatment for divorce-related dysphoria. Journal of Rational-Emotive and Cognitive-Behavior Therapy. 1988;6(3):162-71.</t>
+          <t>Manicavasgar V, Parker G, Perich T. Mindfulness-based cognitive therapy vs cognitive behaviour therapy as a treatment for non-melancholic depression. Journal of Affective Disorders. 2011;130(1):138-44.</t>
         </is>
       </c>
       <c r="C159" t="b">
@@ -6187,12 +7006,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Manicavasgar, 2011</t>
+          <t>Markowitz, 1998</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Manicavasgar V, Parker G, Perich T. Mindfulness-based cognitive therapy vs cognitive behaviour therapy as a treatment for non-melancholic depression. Journal of Affective Disorders. 2011;130(1):138-44.</t>
+          <t>Markowitz JC, Kocsis JH, Fishman B, Spielman LA, Jacobsberg LB, Frances AJ, et al. Treatment of depressive symptoms in human immunodeficiency virus-positive patients. Archives of General Psychiatry. 1998;55(5):452-7.</t>
         </is>
       </c>
       <c r="C160" t="b">
@@ -6202,12 +7021,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Markowitz, 1998</t>
+          <t>Markowitz, 2005</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Markowitz JC, Kocsis JH, Fishman B, Spielman LA, Jacobsberg LB, Frances AJ, et al. Treatment of depressive symptoms in human immunodeficiency virus-positive patients. Archives of General Psychiatry. 1998;55(5):452-7.</t>
+          <t>Markowitz JC, Kocsis JH, Bleiberg KL, Christos PJ, Sacks M. A comparative trial of psychotherapy and pharmacotherapy for "pure" dysthymic patients. Journal of Affective Disorders. 2005;89(1-3):167-75.</t>
         </is>
       </c>
       <c r="C161" t="b">
@@ -6217,12 +7036,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Markowitz, 2005</t>
+          <t>Markowitz, 2008</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Markowitz JC, Kocsis JH, Bleiberg KL, Christos PJ, Sacks M. A comparative trial of psychotherapy and pharmacotherapy for "pure" dysthymic patients. Journal of Affective Disorders. 2005;89(1-3):167-75.</t>
+          <t>Markowitz JC, Kocsis JH, Christos P, Bleiberg K, Carlin A. Pilot study of interpersonal psychotherapy versus supportive psychotherapy for dysthymic patients with secondary alcohol abuse or dependence. Journal of Nervous and Mental Disease. 2008;196(6):468-74.</t>
         </is>
       </c>
       <c r="C162" t="b">
@@ -6232,12 +7051,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Markowitz, 2008</t>
+          <t>Martin, 2015</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Markowitz JC, Kocsis JH, Christos P, Bleiberg K, Carlin A. Pilot study of interpersonal psychotherapy versus supportive psychotherapy for dysthymic patients with secondary alcohol abuse or dependence. Journal of Nervous and Mental Disease. 2008;196(6):468-74.</t>
+          <t>Martin PR, Aiello R, Gilson K, Meadows G, Milgrom J, Reece J. Cognitive behavior therapy for comorbid migraine and/or tension-type headache and major depressive disorder: An exploratory randomized controlled trial. Behaviour Research and Therapy. 2015;73:8-18.</t>
         </is>
       </c>
       <c r="C163" t="b">
@@ -6247,12 +7066,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Martin, 2015</t>
+          <t>Matsuzaka, 2017</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Martin PR, Aiello R, Gilson K, Meadows G, Milgrom J, Reece J. Cognitive behavior therapy for comorbid migraine and/or tension-type headache and major depressive disorder: An exploratory randomized controlled trial. Behaviour Research and Therapy. 2015;73:8-18.</t>
+          <t>Matsuzaka, C., Wainberg, M., Norcini, P. A., Hoffmann, E., Coimbra, B., Braga, R., . . . Mello, M. (2017). Task shifting interpersonal counseling for depression: a pragmatic randomized controlled trial in primary care. BMC Psychiatry, 17(1)</t>
         </is>
       </c>
       <c r="C164" t="b">
@@ -6262,12 +7081,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Matsuzaka, 2017</t>
+          <t>McClay, 2015</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Matsuzaka, C., Wainberg, M., Norcini, P. A., Hoffmann, E., Coimbra, B., Braga, R., . . . Mello, M. (2017). Task shifting interpersonal counseling for depression: a pragmatic randomized controlled trial in primary care. BMC Psychiatry, 17(1)</t>
+          <t>McClay CA, Collins K, Matthews L, Haig C, McConnachie A, Morrison J, et al. A community-based pilot randomised controlled study of life skills classes for individuals with low mood and depression. BMC psychiatry. 2015;15:17.</t>
         </is>
       </c>
       <c r="C165" t="b">
@@ -6277,12 +7096,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>McClay, 2015</t>
+          <t>McIndoo, 2016</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>McClay CA, Collins K, Matthews L, Haig C, McConnachie A, Morrison J, et al. A community-based pilot randomised controlled study of life skills classes for individuals with low mood and depression. BMC psychiatry. 2015;15:17.</t>
+          <t>McIndoo CC, File AA, Preddy T, Clark CG, Hopko DR. Mindfulness-based therapy and behavioral activation: A randomized controlled trial with depressed college students. Behaviour Research and Therapy. 2016;77:118-28.</t>
         </is>
       </c>
       <c r="C166" t="b">
@@ -6292,12 +7111,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>McIndoo, 2016</t>
+          <t>McKee, 2006</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>McIndoo CC, File AA, Preddy T, Clark CG, Hopko DR. Mindfulness-based therapy and behavioral activation: A randomized controlled trial with depressed college students. Behaviour Research and Therapy. 2016;77:118-28.</t>
+          <t>McKee MD, Zayas LH, Fletcher J, Boyd RC, Nam SH. Results of an intervention to reduce perinatal depression among low-income minority women in community primary care. Journal of Social Service Research. 2006;32(4):63-81.</t>
         </is>
       </c>
       <c r="C167" t="b">
@@ -6307,12 +7126,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>McKee, 2006</t>
+          <t>McLean, 1979</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>McKee MD, Zayas LH, Fletcher J, Boyd RC, Nam SH. Results of an intervention to reduce perinatal depression among low-income minority women in community primary care. Journal of Social Service Research. 2006;32(4):63-81.</t>
+          <t>McLean PD, Hakstian AR. Clinical depression: Comparative efficacy of outpatient treatments. Journal of Consulting and Clinical Psychology. 1979;47(5):818-36.</t>
         </is>
       </c>
       <c r="C168" t="b">
@@ -6322,12 +7141,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>McLean, 1979</t>
+          <t>Michalak, 2015</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>McLean PD, Hakstian AR. Clinical depression: Comparative efficacy of outpatient treatments. Journal of Consulting and Clinical Psychology. 1979;47(5):818-36.</t>
+          <t>Michalak J, Schultze M, Heidenreich T, Schramm E. A randomized controlled trial on the efficacy of mindfulness-based cognitive therapy and a group version of cognitive behavioral analysis system of psychotherapy for chronically depressed patients. Journal of Consulting and Clinical Psychology. 2015;83(5):951-63.</t>
         </is>
       </c>
       <c r="C169" t="b">
@@ -6337,12 +7156,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Michalak, 2015</t>
+          <t>Milgrom, 2005</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Michalak J, Schultze M, Heidenreich T, Schramm E. A randomized controlled trial on the efficacy of mindfulness-based cognitive therapy and a group version of cognitive behavioral analysis system of psychotherapy for chronically depressed patients. Journal of Consulting and Clinical Psychology. 2015;83(5):951-63.</t>
+          <t>Milgrom J, Negri LM, Gemmill AW, McNeil M, Martin PR. A randomized controlled trial of psychological interventions for postnatal depression. British Journal of Clinical Psychology. 2005;44(4):529-42.</t>
         </is>
       </c>
       <c r="C170" t="b">
@@ -6352,12 +7171,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Milgrom, 2005</t>
+          <t>Milgrom, 2011</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Milgrom J, Negri LM, Gemmill AW, McNeil M, Martin PR. A randomized controlled trial of psychological interventions for postnatal depression. British Journal of Clinical Psychology. 2005;44(4):529-42.</t>
+          <t>Milgrom J, Holt CJ, Gemmill AW, Ericksen J, Leigh B, Buist A, et al. Treating postnatal depressive symptoms in primary care: A randomised controlled trial of GP management, with and without adjunctive counselling. BMC psychiatry. 2011;11:95.</t>
         </is>
       </c>
       <c r="C171" t="b">
@@ -6367,12 +7186,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Milgrom, 2011</t>
+          <t>Milgrom, 2015 II</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Milgrom J, Holt CJ, Gemmill AW, Ericksen J, Leigh B, Buist A, et al. Treating postnatal depressive symptoms in primary care: A randomised controlled trial of GP management, with and without adjunctive counselling. BMC psychiatry. 2011;11:95.</t>
+          <t>Milgrom J, Holt C, Holt CJ, Ross J, Ericksen J, Gemmill AW. Feasibility study and pilot randomised trial of an antenatal depression treatment with infant follow-up. Archives of Women's Mental Health. 2015;18(5):717-30.</t>
         </is>
       </c>
       <c r="C172" t="b">
@@ -6382,12 +7201,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Milgrom, 2015 II</t>
+          <t>Milgrom, 2016</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Milgrom J, Holt C, Holt CJ, Ross J, Ericksen J, Gemmill AW. Feasibility study and pilot randomised trial of an antenatal depression treatment with infant follow-up. Archives of Women's Mental Health. 2015;18(5):717-30.</t>
+          <t>Milgrom J, Danaher BG, Gemmill AW, Holt C, Holt CJ, Seeley JR, et al. Internet cognitive behavioral therapy for women with postnatal depression: A randomized controlled trial of MumMoodBooster. Journal of Medical Internet Research. 2016;18(3):e54.</t>
         </is>
       </c>
       <c r="C173" t="b">
@@ -6397,12 +7216,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Milgrom, 2016</t>
+          <t>Miller, 2002</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Milgrom J, Danaher BG, Gemmill AW, Holt C, Holt CJ, Seeley JR, et al. Internet cognitive behavioral therapy for women with postnatal depression: A randomized controlled trial of MumMoodBooster. Journal of Medical Internet Research. 2016;18(3):e54.</t>
+          <t>Miller L, Weissman M. Interpersonal psychotherapy delivered over the telephone to recurrent depressives. A pilot study. Depression and anxiety. 2002;16(3):114-7.</t>
         </is>
       </c>
       <c r="C174" t="b">
@@ -6412,12 +7231,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Miller, 2002</t>
+          <t>Mohr, 2000</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Miller L, Weissman M. Interpersonal psychotherapy delivered over the telephone to recurrent depressives. A pilot study. Depression and anxiety. 2002;16(3):114-7.</t>
+          <t>Mohr DC, Likosky W, Bertagnolli A, Goodkin DE, Van Der Wende J, Dwyer P, et al. Telephone-administered cognitive-behavioral therapy for the treatment of depressive symptoms in multiple sclerosis. Journal of Consulting and Clinical Psychology. 2000;68(2):356-61.</t>
         </is>
       </c>
       <c r="C175" t="b">
@@ -6427,12 +7246,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mohr, 2000</t>
+          <t>Mohr, 2001</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mohr DC, Likosky W, Bertagnolli A, Goodkin DE, Van Der Wende J, Dwyer P, et al. Telephone-administered cognitive-behavioral therapy for the treatment of depressive symptoms in multiple sclerosis. Journal of Consulting and Clinical Psychology. 2000;68(2):356-61.</t>
+          <t>Mohr DC, Boudewyn AC, Goodkin DE, Bostrom A, Epstein L. Comparative outcomes for individual cognitive-behavior therapy, supportive-expressive group psychotherapy, and sertraline for the treatment of depression in multiple sclerosis. Journal of Consulting and Clinical Psychology. 2001;69(6):942-9.</t>
         </is>
       </c>
       <c r="C176" t="b">
@@ -6442,12 +7261,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mohr, 2001</t>
+          <t>Mohr, 2005</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mohr DC, Boudewyn AC, Goodkin DE, Bostrom A, Epstein L. Comparative outcomes for individual cognitive-behavior therapy, supportive-expressive group psychotherapy, and sertraline for the treatment of depression in multiple sclerosis. Journal of Consulting and Clinical Psychology. 2001;69(6):942-9.</t>
+          <t>Mohr DC, Hart SL, Julian L, Catledge C, Honos-Webb L, Vella L, et al. Telephone-administered psychotherapy for depression. Archives of General Psychiatry. 2005;62(9):1007-14.</t>
         </is>
       </c>
       <c r="C177" t="b">
@@ -6457,12 +7276,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Mohr, 2005</t>
+          <t>Mohr, 2013</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mohr DC, Hart SL, Julian L, Catledge C, Honos-Webb L, Vella L, et al. Telephone-administered psychotherapy for depression. Archives of General Psychiatry. 2005;62(9):1007-14.</t>
+          <t>Mohr DC, Duffecy J, Ho J, Kwasny M, Cai X, Burns MN, et al. A randomized controlled trial evaluating a manualized TeleCoaching protocol for improving adherence to a web-based intervention for the treatment of depression. PLoS One. 2013;8(8):e70086.</t>
         </is>
       </c>
       <c r="C178" t="b">
@@ -6472,12 +7291,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Mohr, 2013</t>
+          <t>Montero-Mar, 2016</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mohr DC, Duffecy J, Ho J, Kwasny M, Cai X, Burns MN, et al. A randomized controlled trial evaluating a manualized TeleCoaching protocol for improving adherence to a web-based intervention for the treatment of depression. PLoS One. 2013;8(8):e70086.</t>
+          <t>Montero-Marín, J., Araya, R., Pérez-Yus, M. C., Mayoral, F., Gili, M., Botella, C., . . . López-Del-Hoyo, Y. (2016). An internet-based intervention for depression in primary Care in Spain: a randomized controlled trial. Journal of medical Internet research, 18(8), e231.</t>
         </is>
       </c>
       <c r="C179" t="b">
@@ -6487,12 +7306,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Montero-Marín, 2016</t>
+          <t>Mossey, 1996</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Montero-Marín, J., Araya, R., Pérez-Yus, M. C., Mayoral, F., Gili, M., Botella, C., . . . López-Del-Hoyo, Y. (2016). An internet-based intervention for depression in primary Care in Spain: a randomized controlled trial. Journal of medical Internet research, 18(8), e231.</t>
+          <t>Mossey JM, Knott KA, Higgins M, Talerico K. Effectiveness of a psychosocial intervention, interpersonal counseling, for subdysthymic depression in medically ill elderly. The journals of gerontology Series A, Biological sciences and medical sciences. 1996;51(4):M172-8.</t>
         </is>
       </c>
       <c r="C180" t="b">
@@ -6502,12 +7321,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mossey, 1996</t>
+          <t>Mukhtar, 2011</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mossey JM, Knott KA, Higgins M, Talerico K. Effectiveness of a psychosocial intervention, interpersonal counseling, for subdysthymic depression in medically ill elderly. The journals of gerontology Series A, Biological sciences and medical sciences. 1996;51(4):M172-8.</t>
+          <t>Mukhtar F. Predictors of group cognitive behaviour therapy outcomes for the treatment of depression in Malaysia. Asian Journal of Psychiatry. 2011;4(2):125-8.</t>
         </is>
       </c>
       <c r="C181" t="b">
@@ -6517,12 +7336,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mukhtar, 2011</t>
+          <t>Mulcahy, 2010</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mukhtar F. Predictors of group cognitive behaviour therapy outcomes for the treatment of depression in Malaysia. Asian Journal of Psychiatry. 2011;4(2):125-8.</t>
+          <t>Mulcahy R, Reay RE, Wilkinson RB, Owen C. A randomised control trial for the effectiveness of group interpersonal psychotherapy for postnatal depression. Archives of Women's Mental Health. 2010;13(2):125-39.</t>
         </is>
       </c>
       <c r="C182" t="b">
@@ -6532,12 +7351,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Mulcahy, 2010</t>
+          <t>Naeem, 2013</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mulcahy R, Reay RE, Wilkinson RB, Owen C. A randomised control trial for the effectiveness of group interpersonal psychotherapy for postnatal depression. Archives of Women's Mental Health. 2010;13(2):125-39.</t>
+          <t>Naeem F, Sarhandi I, Gul M, Khalid M, Aslam M, Anbrin A. A multicentre randomised controlled trial of a carer supervised culturally adapted cbt (cacbt) based self-help for depression in pakistan. Journal of Affective Disorders. 2013;156:224-7.</t>
         </is>
       </c>
       <c r="C183" t="b">
@@ -6547,12 +7366,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Naeem, 2013</t>
+          <t>Nakagawa, 2017</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Naeem F, Sarhandi I, Gul M, Khalid M, Aslam M, Anbrin A. A multicentre randomised controlled trial of a carer supervised culturally adapted cbt (cacbt) based self-help for depression in pakistan. Journal of Affective Disorders. 2013;156:224-7.</t>
+          <t>Nakagawa, A., Mitsuda, D., Sado, M., Abe, T., Fujisawa, D., Kikuchi, T., . . . Ono, Y. (2017). Effectiveness of supplementary cognitive-behavioral therapy for pharmacotherapy-resistant depression: A randomized controlled trial. Journal of clinical psychiatry, 78(8), 1126-1135</t>
         </is>
       </c>
       <c r="C184" t="b">
@@ -6562,12 +7381,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Nakagawa, 2017</t>
+          <t>Nasrin, 2017</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Nakagawa, A., Mitsuda, D., Sado, M., Abe, T., Fujisawa, D., Kikuchi, T., . . . Ono, Y. (2017). Effectiveness of supplementary cognitive-behavioral therapy for pharmacotherapy-resistant depression: A randomized controlled trial. Journal of clinical psychiatry, 78(8), 1126-1135</t>
+          <t>Nasrin, F., Rimes, K., Reinecke, A., Rinck, M., &amp; Barnhofer, T. (2017). Effects of Brief Behavioural Activation on Approach and Avoidance Tendencies in Acute Depression: preliminary Findings. Behavioural and Cognitive Psychotherapy, 45(1), 58-72.</t>
         </is>
       </c>
       <c r="C185" t="b">
@@ -6577,12 +7396,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nasrin, 2017</t>
+          <t>Neugebauer, 2006</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Nasrin, F., Rimes, K., Reinecke, A., Rinck, M., &amp; Barnhofer, T. (2017). Effects of Brief Behavioural Activation on Approach and Avoidance Tendencies in Acute Depression: preliminary Findings. Behavioural and Cognitive Psychotherapy, 45(1), 58-72.</t>
+          <t>Neugebauer R, Kline J, Markowitz JC, Bleiberg KL, Baxi L, Rosing MA, et al. Pilot randomized controlled trial of interpersonal counseling for subsyndromal depression following miscarriage. Journal of Clinical Psychiatry. 2006;67(8):1299-304.</t>
         </is>
       </c>
       <c r="C186" t="b">
@@ -6592,12 +7411,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Neugebauer, 2006</t>
+          <t>Newby, 2014</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Neugebauer R, Kline J, Markowitz JC, Bleiberg KL, Baxi L, Rosing MA, et al. Pilot randomized controlled trial of interpersonal counseling for subsyndromal depression following miscarriage. Journal of Clinical Psychiatry. 2006;67(8):1299-304.</t>
+          <t>Newby JM, Lang T, Werner-Seidler A, Holmes E, Moulds ML. Alleviating distressing intrusive memories in depression: A comparison between computerised cognitive bias modification and cognitive behavioural education. Behaviour Research and Therapy. 2014;56:60-7.</t>
         </is>
       </c>
       <c r="C187" t="b">
@@ -6607,12 +7426,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Newby, 2014</t>
+          <t>Newby, 2017</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Newby JM, Lang T, Werner-Seidler A, Holmes E, Moulds ML. Alleviating distressing intrusive memories in depression: A comparison between computerised cognitive bias modification and cognitive behavioural education. Behaviour Research and Therapy. 2014;56:60-7.</t>
+          <t>Newby, J., Robins, L., Wilhelm, K., Smith, J., Fletcher, T., Gillis, I., . . . Andrews, G. (2017). Web-Based Cognitive Behavior Therapy for Depression in People With Diabetes Mellitus: a Randomized Controlled Trial. Journal of medical Internet research, 19(5), e157.</t>
         </is>
       </c>
       <c r="C188" t="b">
@@ -6622,12 +7441,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Newby, 2017</t>
+          <t>Nezu, 1986</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Newby, J., Robins, L., Wilhelm, K., Smith, J., Fletcher, T., Gillis, I., . . . Andrews, G. (2017). Web-Based Cognitive Behavior Therapy for Depression in People With Diabetes Mellitus: a Randomized Controlled Trial. Journal of medical Internet research, 19(5), e157.</t>
+          <t>Nezu AM. Efficacy of a social problem-solving therapy approach for unipolar depression. Journal of Consulting and Clinical Psychology. 1986;54(2):196-202.</t>
         </is>
       </c>
       <c r="C189" t="b">
@@ -6637,12 +7456,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Nezu, 1986</t>
+          <t>Ng, 2013</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Nezu AM. Efficacy of a social problem-solving therapy approach for unipolar depression. Journal of Consulting and Clinical Psychology. 1986;54(2):196-202.</t>
+          <t>Ng SE, Tien A, Thayala JN, Ho RC, Chan MF. The effect of life story review on depression of older community-dwelling Chinese adults in Singapore: A preliminary result. International Journal of Geriatric Psychiatry. 2013;28(3):328-30.</t>
         </is>
       </c>
       <c r="C190" t="b">
@@ -6652,12 +7471,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ng, 2013</t>
+          <t>Ngai, 2015</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ng SE, Tien A, Thayala JN, Ho RC, Chan MF. The effect of life story review on depression of older community-dwelling Chinese adults in Singapore: A preliminary result. International Journal of Geriatric Psychiatry. 2013;28(3):328-30.</t>
+          <t>Ngai FW, Wong P-C, Leung KY, Chau PH, Chung KF. The effect of telephone-based cognitive-behavioral therapy on postnatal depression: A randomized controlled trial. Psychotherapy and Psychosomatics. 2015;84(5):294-303.</t>
         </is>
       </c>
       <c r="C191" t="b">
@@ -6667,12 +7486,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ngai, 2015</t>
+          <t>Nollett, 2016</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ngai FW, Wong P-C, Leung KY, Chau PH, Chung KF. The effect of telephone-based cognitive-behavioral therapy on postnatal depression: A randomized controlled trial. Psychotherapy and Psychosomatics. 2015;84(5):294-303.</t>
+          <t>Nollett CL, Bray N, Bunce C, Casten RJ, Edwards RT, Hegel MT, et al. Depression in Visual Impairment Trial (DEPVIT): A randomized clinical trial of depression treatments in people with low vision. Investigative Ophthalmology and Visual Science. 2016;57(10):4247-54.</t>
         </is>
       </c>
       <c r="C192" t="b">
@@ -6682,12 +7501,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Nollett, 2016</t>
+          <t>Nyström, 2017</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nollett CL, Bray N, Bunce C, Casten RJ, Edwards RT, Hegel MT, et al. Depression in Visual Impairment Trial (DEPVIT): A randomized clinical trial of depression treatments in people with low vision. Investigative Ophthalmology and Visual Science. 2016;57(10):4247-54.</t>
+          <t>Nyström, M., Stenling, A., Sjöström, E., Neely, G., Lindner, P., HassmÈn, P., . . . Carlbring, P. (2017). Behavioral activation versus physical activity via the internet: a randomized controlled trial. Journal of Affective Disorders, 215, 85-93.</t>
         </is>
       </c>
       <c r="C193" t="b">
@@ -6697,12 +7516,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Nyström, 2017</t>
+          <t>O'Hara, 2000</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Nyström, M., Stenling, A., Sjöström, E., Neely, G., Lindner, P., HassmÈn, P., . . . Carlbring, P. (2017). Behavioral activation versus physical activity via the internet: a randomized controlled trial. Journal of Affective Disorders, 215, 85-93.</t>
+          <t>O'Hara MW, Stuart S, Gorman LL, Wenzel A. Efficacy of interpersonal psychotherapy for postpartum depression. Archives of General Psychiatry. 2000;57(11):1039-45.</t>
         </is>
       </c>
       <c r="C194" t="b">
@@ -6712,12 +7531,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>O'Hara, 2000</t>
+          <t>O'Mahen, 2013</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>O'Hara MW, Stuart S, Gorman LL, Wenzel A. Efficacy of interpersonal psychotherapy for postpartum depression. Archives of General Psychiatry. 2000;57(11):1039-45.</t>
+          <t>O'Mahen H, Himle JA, Fedock G, Henshaw E, Flynn H. A pilot randomized controlled trial of cognitive behavioral therapy for perinatal depression adapted for women with low incomes. Depression and anxiety. 2013;30(7):679-87.</t>
         </is>
       </c>
       <c r="C195" t="b">
@@ -6727,12 +7546,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>O'Mahen, 2013</t>
+          <t>O'Neil, 2014</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>O'Mahen H, Himle JA, Fedock G, Henshaw E, Flynn H. A pilot randomized controlled trial of cognitive behavioral therapy for perinatal depression adapted for women with low incomes. Depression and anxiety. 2013;30(7):679-87.</t>
+          <t>O'Neil A, Taylor B, Sanderson K, Cyril S, Chan B, Hawkes AL, et al. Efficacy and feasibility of a tele-health intervention for acute coronary syndrome patients with depression: Results of the "MoodCare" randomized controlled trial. Annals of Behavioral Medicine. 2014;48(2):163-74.</t>
         </is>
       </c>
       <c r="C196" t="b">
@@ -6742,12 +7561,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>O'Neil, 2014</t>
+          <t>Olukolade, 2017</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>O'Neil A, Taylor B, Sanderson K, Cyril S, Chan B, Hawkes AL, et al. Efficacy and feasibility of a tele-health intervention for acute coronary syndrome patients with depression: Results of the "MoodCare" randomized controlled trial. Annals of Behavioral Medicine. 2014;48(2):163-74.</t>
+          <t>Olukolade, O., &amp; Osinowo, H. (2017). Efficacy of Cognitive Rehabilitation Therapy on Poststroke Depression among Survivors of First Stroke Attack in Ibadan, Nigeria. Behavioural Neurology, 2017</t>
         </is>
       </c>
       <c r="C197" t="b">
@@ -6757,12 +7576,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Olukolade, 2017</t>
+          <t>Omidi, 2013</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Olukolade, O., &amp; Osinowo, H. (2017). Efficacy of Cognitive Rehabilitation Therapy on Poststroke Depression among Survivors of First Stroke Attack in Ibadan, Nigeria. Behavioural Neurology, 2017</t>
+          <t>Omidi A, Mohammadkhani P, Mohammadi A, Zargar F. Comparing mindfulness based cognitive therapy and traditional cognitive behavior therapy with treatments as usual on reduction of major depressive disorder symptoms. Iranian Red Crescent Medical Journal. 2013;15(2):142-6.</t>
         </is>
       </c>
       <c r="C198" t="b">
@@ -6772,12 +7591,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Omidi, 2013</t>
+          <t>Onuigbo, 2019</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Omidi A, Mohammadkhani P, Mohammadi A, Zargar F. Comparing mindfulness based cognitive therapy and traditional cognitive behavior therapy with treatments as usual on reduction of major depressive disorder symptoms. Iranian Red Crescent Medical Journal. 2013;15(2):142-6.</t>
+          <t>Onuigbo, L. N., Eseadi, C., Ebifa, S., Ugwu, U. C., Onyishi, C. N., &amp; Oyeoku, E. K. (2019). Effect of rational emotive behavior therapy program on depressive symptoms among university students with blindness in Nigeria. Journal of Rational-Emotive &amp; Cognitive-Behavior Therapy, 37(1), 17-38. doi:10.1007/s10942-018-0297-3</t>
         </is>
       </c>
       <c r="C199" t="b">
@@ -6787,12 +7606,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Onuigbo, 2019</t>
+          <t>Pace, 1993</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Onuigbo, L. N., Eseadi, C., Ebifa, S., Ugwu, U. C., Onyishi, C. N., &amp; Oyeoku, E. K. (2019). Effect of rational emotive behavior therapy program on depressive symptoms among university students with blindness in Nigeria. Journal of Rational-Emotive &amp; Cognitive-Behavior Therapy, 37(1), 17-38. doi:10.1007/s10942-018-0297-3</t>
+          <t>Pace TM, Dixon DN. Changes in depressive self-schemata and depressive symptoms following cognitive therapy. Journal of Counseling Psychology. 1993;40(3):288.</t>
         </is>
       </c>
       <c r="C200" t="b">
@@ -6802,12 +7621,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Pace, 1993</t>
+          <t>Padfield, 1976</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Pace TM, Dixon DN. Changes in depressive self-schemata and depressive symptoms following cognitive therapy. Journal of Counseling Psychology. 1993;40(3):288.</t>
+          <t>Padfield M. The comparative effects of two counseling approaches on the intensity of depression among rural women of low socioeconomic status. Journal of Counseling Psychology. 1976;23(3):209.</t>
         </is>
       </c>
       <c r="C201" t="b">
@@ -6817,12 +7636,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Padfield, 1976</t>
+          <t>Pecheur, 1984</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Padfield M. The comparative effects of two counseling approaches on the intensity of depression among rural women of low socioeconomic status. Journal of Counseling Psychology. 1976;23(3):209.</t>
+          <t>Pecheur DR, Edwards KJ. A comparison of secular and religious versions of cognitive therapy with depressed Christian college students. Journal of Psychology and Theology. 1984.</t>
         </is>
       </c>
       <c r="C202" t="b">
@@ -6832,12 +7651,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Pecheur, 1984</t>
+          <t>Peden, 2000</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Pecheur DR, Edwards KJ. A comparison of secular and religious versions of cognitive therapy with depressed Christian college students. Journal of Psychology and Theology. 1984.</t>
+          <t>Peden AR, Hall LA, Rayens MK, Beebe LL. Reducing negative thinking and depressive symptoms in college women. Journal of Nursing Scholarship. 2000;32(2):145-51.</t>
         </is>
       </c>
       <c r="C203" t="b">
@@ -6847,12 +7666,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Peden, 2000</t>
+          <t>Penckofer, 2012</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Peden AR, Hall LA, Rayens MK, Beebe LL. Reducing negative thinking and depressive symptoms in college women. Journal of Nursing Scholarship. 2000;32(2):145-51.</t>
+          <t>Penckofer SM, Ferrans C, Mumby P, Byrn M, Emanuele MA, Harrison PR, et al. A psychoeducational intervention (SWEEP) for depressed women with diabetes. Annals of Behavioral Medicine. 2012;44(2):192-206.</t>
         </is>
       </c>
       <c r="C204" t="b">
@@ -6862,12 +7681,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Penckofer, 2012</t>
+          <t>Perini, 2009</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Penckofer SM, Ferrans C, Mumby P, Byrn M, Emanuele MA, Harrison PR, et al. A psychoeducational intervention (SWEEP) for depressed women with diabetes. Annals of Behavioral Medicine. 2012;44(2):192-206.</t>
+          <t>Perini S, Titov N, Andrews G. Clinician-assisted Internet-based treatment is effective for depression: Randomized controlled trial. Australian and New Zealand Journal of Psychiatry. 2009;43(6):571-8.</t>
         </is>
       </c>
       <c r="C205" t="b">
@@ -6877,12 +7696,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Perini, 2009</t>
+          <t>Petersen, 2014</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Perini S, Titov N, Andrews G. Clinician-assisted Internet-based treatment is effective for depression: Randomized controlled trial. Australian and New Zealand Journal of Psychiatry. 2009;43(6):571-8.</t>
+          <t>Petersen I, Hanass Hancock J, Bhana A, Govender K. A group-based counselling intervention for depression comorbid with HIV/AIDS using a task shifting approach in South Africa: A randomized controlled pilot study. Journal of Affective Disorders. 2014;158:78-84.</t>
         </is>
       </c>
       <c r="C206" t="b">
@@ -6892,12 +7711,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Petersen, 2014</t>
+          <t>Pibernik-Okanovi, 2015</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Petersen I, Hanass Hancock J, Bhana A, Govender K. A group-based counselling intervention for depression comorbid with HIV/AIDS using a task shifting approach in South Africa: A randomized controlled pilot study. Journal of Affective Disorders. 2014;158:78-84.</t>
+          <t>Pibernik-Okanović M, Hermanns N, Ajduković D, Kos J, Prašek M, Šekerija M, Lovrenčić MV. Does treatment of subsyndromal depression improve depression-related and diabetes-related outcomes? A randomised controlled comparison of psychoeducation, physical exercise and enhanced treatment as usual. Trials. 2015 Jul 15;16:305.</t>
         </is>
       </c>
       <c r="C207" t="b">
@@ -6907,12 +7726,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Pibernik, 2015</t>
+          <t>Poleshuck, 2014</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Pibernik-Okanović M, Hermanns N, Ajduković D, Kos J, Prašek M, Šekerija M, Lovrenčić MV. Does treatment of subsyndromal depression improve depression-related and diabetes-related outcomes? A randomised controlled comparison of psychoeducation, physical exercise and enhanced treatment as usual. Trials. 2015 Jul 15;16:305.</t>
+          <t>Poleshuck EL, Gamble SA, Bellenger K, Lu N, Tu X, Sorensen S, et al. Randomized controlled trial of interpersonal psychotherapy versus enhanced treatment as usual for women with co-occurring depression and pelvic pain. Journal of psychosomatic research. 2014;77(4):264-72.</t>
         </is>
       </c>
       <c r="C208" t="b">
@@ -6922,12 +7741,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Poleshuck, 2014</t>
+          <t>Pots, 2014</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Poleshuck EL, Gamble SA, Bellenger K, Lu N, Tu X, Sorensen S, et al. Randomized controlled trial of interpersonal psychotherapy versus enhanced treatment as usual for women with co-occurring depression and pelvic pain. Journal of psychosomatic research. 2014;77(4):264-72.</t>
+          <t>Pots WTM, Meulenbeek PAM, Veehof MM, Klungers J, Bohlmeijer ET. The efficacy of mindfulness-based cognitive therapy as a public mental health intervention for adults with mild to moderate depressive symptomatology: A randomized controlled trial. PLoS One. 2014;9(10).</t>
         </is>
       </c>
       <c r="C209" t="b">
@@ -6937,12 +7756,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Pots, 2014</t>
+          <t>Pots, 2016</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Pots WTM, Meulenbeek PAM, Veehof MM, Klungers J, Bohlmeijer ET. The efficacy of mindfulness-based cognitive therapy as a public mental health intervention for adults with mild to moderate depressive symptomatology: A randomized controlled trial. PLoS One. 2014;9(10).</t>
+          <t>Pots WT, Fledderus M, Meulenbeek PA, ten Klooster PM, Schreurs KM, Bohlmeijer ET. Acceptance and commitment therapy as a web-based intervention for depressive symptoms: Randomised controlled trial. The British Journal of Psychiatry. 2016;208(1):69-77.</t>
         </is>
       </c>
       <c r="C210" t="b">
@@ -6952,12 +7771,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Pots, 2016</t>
+          <t>Power, 2012</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Pots WT, Fledderus M, Meulenbeek PA, ten Klooster PM, Schreurs KM, Bohlmeijer ET. Acceptance and commitment therapy as a web-based intervention for depressive symptoms: Randomised controlled trial. The British Journal of Psychiatry. 2016;208(1):69-77.</t>
+          <t>Power MJ, Freeman C. A randomized controlled trial of IPT versus CBT in primary care: With some cautionary notes about handling missing values in clinical trials. Clinical Psychology and Psychotherapy. 2012;19(2):159-69.</t>
         </is>
       </c>
       <c r="C211" t="b">
@@ -6967,12 +7786,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Power, 2012</t>
+          <t>Preschl, 2012</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Power MJ, Freeman C. A randomized controlled trial of IPT versus CBT in primary care: With some cautionary notes about handling missing values in clinical trials. Clinical Psychology and Psychotherapy. 2012;19(2):159-69.</t>
+          <t>Preschl B, Maercker A, Wagner B, Forstmeier S, Banos RM, Alcaniz M, et al. Life-review therapy with computer supplements for depression in the elderly: A randomized controlled trial. Aging and Mental Health. 2012;16(8):964-74.</t>
         </is>
       </c>
       <c r="C212" t="b">
@@ -6982,12 +7801,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Preschl, 2012</t>
+          <t>Propst, 1992</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Preschl B, Maercker A, Wagner B, Forstmeier S, Banos RM, Alcaniz M, et al. Life-review therapy with computer supplements for depression in the elderly: A randomized controlled trial. Aging and Mental Health. 2012;16(8):964-74.</t>
+          <t>Propst LR, Ostrom R, Watkins P, Dean T, Mashburn D. Comparative efficacy of religious and nonreligious cognitive-behavioral therapy for the treatment of clinical depression in religious individuals. Journal of Consulting and Clinical Psychology. 1992;60(1):94-103.</t>
         </is>
       </c>
       <c r="C213" t="b">
@@ -6997,12 +7816,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Propst, 1992</t>
+          <t>Pugh, 2016</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Propst LR, Ostrom R, Watkins P, Dean T, Mashburn D. Comparative efficacy of religious and nonreligious cognitive-behavioral therapy for the treatment of clinical depression in religious individuals. Journal of Consulting and Clinical Psychology. 1992;60(1):94-103.</t>
+          <t>Pugh, N. E., Hadjistavropoulos, H. D., &amp; Dirkse, D. (2016). A Randomised Controlled Trial of Therapist-Assisted, Internet-Delivered Cognitive Behavior Therapy for Women with Maternal Depression. PLoS ONE, 11(3), e0149186.</t>
         </is>
       </c>
       <c r="C214" t="b">
@@ -7012,12 +7831,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Pugh, 2016</t>
+          <t>Qiu, 2013</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Pugh, N. E., Hadjistavropoulos, H. D., &amp; Dirkse, D. (2016). A Randomised Controlled Trial of Therapist-Assisted, Internet-Delivered Cognitive Behavior Therapy for Women with Maternal Depression. PLoS ONE, 11(3), e0149186.</t>
+          <t>Qiu J, Chen W, Gao X, Xu Y, Tong H, Yang M, et al. A randomized controlled trial of group cognitive behavioral therapy for Chinese breast cancer patients with major depression. Journal of psychosomatic obstetrics and gynaecology. 2013;34(2):60-7.</t>
         </is>
       </c>
       <c r="C215" t="b">
@@ -7027,12 +7846,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Qiu, 2013</t>
+          <t>Ransom, 2008</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Qiu J, Chen W, Gao X, Xu Y, Tong H, Yang M, et al. A randomized controlled trial of group cognitive behavioral therapy for Chinese breast cancer patients with major depression. Journal of psychosomatic obstetrics and gynaecology. 2013;34(2):60-7.</t>
+          <t>Ransom D, Heckman TG, Anderson T, Garske J, Holroyd K, Basta T. Telephone-delivered, interpersonal psychotherapy for HIV-infected rural persons with depression: A pilot trial. Psychiatric Services. 2008;59(8):871-7.</t>
         </is>
       </c>
       <c r="C216" t="b">
@@ -7042,12 +7861,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ransom, 2008</t>
+          <t>Raue, 2019</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Ransom D, Heckman TG, Anderson T, Garske J, Holroyd K, Basta T. Telephone-delivered, interpersonal psychotherapy for HIV-infected rural persons with depression: A pilot trial. Psychiatric Services. 2008;59(8):871-7.</t>
+          <t>Raue, P. J., Sirey, J. A., Dawson, A., Berman, J., &amp; Bruce, M. L. (2019). Lay-delivered behavioral activation for depressed senior center clients: Pilot RCT. International journal of geriatric psychiatry, 34(11), 1715-1723. doi:10.1002/gps.5186</t>
         </is>
       </c>
       <c r="C217" t="b">
@@ -7057,12 +7876,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Raue, 2019</t>
+          <t>Richards, 2015</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Raue, P. J., Sirey, J. A., Dawson, A., Berman, J., &amp; Bruce, M. L. (2019). Lay-delivered behavioral activation for depressed senior center clients: Pilot RCT. International journal of geriatric psychiatry, 34(11), 1715-1723. doi:10.1002/gps.5186</t>
+          <t>Richards D, Timulak L, O'Brien E, Hayes C, Vigano N, Sharry J, et al. A randomized controlled trial of an internet-delivered treatment: Its potential as a low-intensity community intervention for adults with symptoms of depression. Behaviour Research and Therapy. 2015;75:20-31.</t>
         </is>
       </c>
       <c r="C218" t="b">
@@ -7072,12 +7891,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Richards, 2015</t>
+          <t>Richards, 2016</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Richards D, Timulak L, O'Brien E, Hayes C, Vigano N, Sharry J, et al. A randomized controlled trial of an internet-delivered treatment: Its potential as a low-intensity community intervention for adults with symptoms of depression. Behaviour Research and Therapy. 2015;75:20-31.</t>
+          <t>Richards, D. A., Ekers, D., McMillan, D., Taylor, R. S., Byford, S., Warren, F. C., . . . Finning, K. (2016). Cost and Outcome of Behavioural Activation versus Cognitive Behavioural Therapy for Depression (COBRA): a randomised, controlled, non-inferiority trial.</t>
         </is>
       </c>
       <c r="C219" t="b">
@@ -7087,12 +7906,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Richards, 2016</t>
+          <t>Richards, 2018</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Richards, D. A., Ekers, D., McMillan, D., Taylor, R. S., Byford, S., Warren, F. C., . . . Finning, K. (2016). Cost and Outcome of Behavioural Activation versus Cognitive Behavioural Therapy for Depression (COBRA): a randomised, controlled, non-inferiority trial.</t>
+          <t>Richards SH, Dickens C, Anderson R, et al. Assessing the effectiveness of Enhanced Psychological Care for patients with depressive symptoms attending cardiac rehabilitation compared with treatment as usual (CADENCE): a pilot cluster randomised controlled trial. Trials 2018; 19(1).</t>
         </is>
       </c>
       <c r="C220" t="b">
@@ -7102,12 +7921,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Richards, 2018</t>
+          <t>Rief, 2018</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Richards SH, Dickens C, Anderson R, et al. Assessing the effectiveness of Enhanced Psychological Care for patients with depressive symptoms attending cardiac rehabilitation compared with treatment as usual (CADENCE): a pilot cluster randomised controlled trial. Trials 2018; 19(1).</t>
+          <t>Rief W, Bleichhardt G, Dannehl K, Euteneuer F, Wambach K. Comparing the Efficacy of CBASP with Two Versions of CBT for Depression in a Routine Care Center: a Randomized Clinical Trial. Psychotherapy and psychosomatics 2018;</t>
         </is>
       </c>
       <c r="C221" t="b">
@@ -7117,12 +7936,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Rief, 2018</t>
+          <t>Rizvi, 2015</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Rief W, Bleichhardt G, Dannehl K, Euteneuer F, Wambach K. Comparing the Efficacy of CBASP with Two Versions of CBT for Depression in a Routine Care Center: a Randomized Clinical Trial. Psychotherapy and psychosomatics 2018;</t>
+          <t>Rizvi SJ, Zaretsky A, Schaffer A, Levitt A. Is immediate adjunctive CBT more beneficial than delayed CBT in treating depression?: A Pilot Study. Journal of Psychiatric Practice. 2015;21(2):107-13.</t>
         </is>
       </c>
       <c r="C222" t="b">
@@ -7132,12 +7951,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Rizvi, 2015</t>
+          <t>Rohan, 2007</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Rizvi SJ, Zaretsky A, Schaffer A, Levitt A. Is immediate adjunctive CBT more beneficial than delayed CBT in treating depression?: A Pilot Study. Journal of Psychiatric Practice. 2015;21(2):107-13.</t>
+          <t>Rohan KJ, Roecklein KA, Lindsey KT, Johnson LG, Lippy RD, Lacy TJ, et al. A randomized controlled trial of cognitive-behavioral therapy, light therapy, and their combination for seasonal affective disorder. Journal of Consulting and Clinical Psychology. 2007;75(3):489-500.</t>
         </is>
       </c>
       <c r="C223" t="b">
@@ -7147,12 +7966,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Rohan, 2007</t>
+          <t>Ross, 1985</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Rohan KJ, Roecklein KA, Lindsey KT, Johnson LG, Lippy RD, Lacy TJ, et al. A randomized controlled trial of cognitive-behavioral therapy, light therapy, and their combination for seasonal affective disorder. Journal of Consulting and Clinical Psychology. 2007;75(3):489-500.</t>
+          <t>Ross M, Scott M. An evaluation of the effectiveness of individual and group cognitive therapy in the treatment of depressed patients in an inner city health centre. The Journal of the Royal College of General Practitioners. 1985;35(274):239-42.</t>
         </is>
       </c>
       <c r="C224" t="b">
@@ -7162,12 +7981,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Ross, 1985</t>
+          <t>Rosso, 2013</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Ross M, Scott M. An evaluation of the effectiveness of individual and group cognitive therapy in the treatment of depressed patients in an inner city health centre. The Journal of the Royal College of General Practitioners. 1985;35(274):239-42.</t>
+          <t>Rosso G, Martini B, Maina G. Brief dynamic therapy and depression severity: A single-blind, randomized study. Journal of Affective Disorders. 2013;147(1-3):101-6.</t>
         </is>
       </c>
       <c r="C225" t="b">
@@ -7177,12 +7996,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Rosso, 2013</t>
+          <t>Russell, 2019</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Rosso G, Martini B, Maina G. Brief dynamic therapy and depression severity: A single-blind, randomized study. Journal of Affective Disorders. 2013;147(1-3):101-6.</t>
+          <t>Russell, A., Gaunt, D. M., Cooper, K., Barton, S., Horwood, J., Kessler, D., . . . et al. (2019). The feasibility of low-intensity psychological therapy for depression co-occurring with autism in adults: the Autism Depression Trial (ADEPT) â€“ a pilot randomised controlled trial. Autism. doi:10.1177/1362361319889272</t>
         </is>
       </c>
       <c r="C226" t="b">
@@ -7192,12 +8011,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Russell, 2019</t>
+          <t>Ruwaard, 2009</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Russell, A., Gaunt, D. M., Cooper, K., Barton, S., Horwood, J., Kessler, D., . . . et al. (2019). The feasibility of low-intensity psychological therapy for depression co-occurring with autism in adults: the Autism Depression Trial (ADEPT) â€“ a pilot randomised controlled trial. Autism. doi:10.1177/1362361319889272</t>
+          <t>Ruwaard J, Schrieken B, Schrijver M, Broeksteeg J, Dekker J, Vermeulen H, et al. Standardized web-based cognitive behavioural therapy of mild to moderate depression: A randomized controlled trial with a long-term follow-up. Cognitive Behaviour Therapy. 2009;38(4):206-21.</t>
         </is>
       </c>
       <c r="C227" t="b">
@@ -7207,12 +8026,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Ruwaard, 2009</t>
+          <t>Safren, 2009</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Ruwaard J, Schrieken B, Schrijver M, Broeksteeg J, Dekker J, Vermeulen H, et al. Standardized web-based cognitive behavioural therapy of mild to moderate depression: A randomized controlled trial with a long-term follow-up. Cognitive Behaviour Therapy. 2009;38(4):206-21.</t>
+          <t>Safren SA, O'Cleirigh C, Tan JY, Raminani SR, Reilly LC, Otto MW, et al. A randomized controlled trial of cognitive behavioral therapy for adherence and depression (CBT-AD) in HIV-infected individuals. Health Psychology. 2009;28(1):1-10.</t>
         </is>
       </c>
       <c r="C228" t="b">
@@ -7222,12 +8041,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Safren, 2009</t>
+          <t>Safren, 2014</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Safren SA, O'Cleirigh C, Tan JY, Raminani SR, Reilly LC, Otto MW, et al. A randomized controlled trial of cognitive behavioral therapy for adherence and depression (CBT-AD) in HIV-infected individuals. Health Psychology. 2009;28(1):1-10.</t>
+          <t>Safren SA, Gonzalez JS, Wexler DJ, Psaros C, Delahanty LM, Blashill AJ, et al. A randomized controlled trial of cognitive behavioral therapy for adherence and depression (CBT-AD) in patients with uncontrolled type 2 diabetes. Diabetes care. 2014;37(3):625-33.</t>
         </is>
       </c>
       <c r="C229" t="b">
@@ -7237,12 +8056,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Safren, 2014</t>
+          <t>Safren, 2016</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Safren SA, Gonzalez JS, Wexler DJ, Psaros C, Delahanty LM, Blashill AJ, et al. A randomized controlled trial of cognitive behavioral therapy for adherence and depression (CBT-AD) in patients with uncontrolled type 2 diabetes. Diabetes care. 2014;37(3):625-33.</t>
+          <t>Safren SA, Bedoya CA, O'Cleirigh C, Biello KB, Pinkston MM, Stein MD, et al. Cognitive behavioural therapy for adherence and depression in patients with HIV: A three-arm randomised controlled trial. The Lancet HIV. 2016;3(11):e529-e38.</t>
         </is>
       </c>
       <c r="C230" t="b">
@@ -7252,12 +8071,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Safren, 2016</t>
+          <t>Savard, 2006</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Safren SA, Bedoya CA, O'Cleirigh C, Biello KB, Pinkston MM, Stein MD, et al. Cognitive behavioural therapy for adherence and depression in patients with HIV: A three-arm randomised controlled trial. The Lancet HIV. 2016;3(11):e529-e38.</t>
+          <t>Savard J, Simard S, Giguere I, Ivers H, Morin CM, Maunsell E, et al. Randomized clinical trial on cognitive therapy for depression in women with metastatic breast cancer: Psychological and immunological effects. Palliative and Supportive Care. 2006;4(3):219-37.</t>
         </is>
       </c>
       <c r="C231" t="b">
@@ -7267,12 +8086,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Savard, 2006</t>
+          <t>Schulberg, 1996</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Savard J, Simard S, Giguere I, Ivers H, Morin CM, Maunsell E, et al. Randomized clinical trial on cognitive therapy for depression in women with metastatic breast cancer: Psychological and immunological effects. Palliative and Supportive Care. 2006;4(3):219-37.</t>
+          <t>Schulberg HC, Block MR, Madonia MJ, Scott CP, Rodriguez E, Imber SD, et al. Treating major depression in primary care practice. Eight-month clinical outcomes. Archives of General Psychiatry. 1996;53(10):913-9.</t>
         </is>
       </c>
       <c r="C232" t="b">
@@ -7282,12 +8101,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Schulberg, 1996</t>
+          <t>Scogin, 1987</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Schulberg HC, Block MR, Madonia MJ, Scott CP, Rodriguez E, Imber SD, et al. Treating major depression in primary care practice. Eight-month clinical outcomes. Archives of General Psychiatry. 1996;53(10):913-9.</t>
+          <t>Scogin F, Hamblin D, Beutler L. Bibliotherapy for depressed older adults: A self-help alternative. The Gerontologist. 1987;27(3):383-7.</t>
         </is>
       </c>
       <c r="C233" t="b">
@@ -7297,12 +8116,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Scogin, 1987</t>
+          <t>Scogin, 1989</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Scogin F, Hamblin D, Beutler L. Bibliotherapy for depressed older adults: A self-help alternative. The Gerontologist. 1987;27(3):383-7.</t>
+          <t>Scogin F, Jamison C, Gochneaur K. Comparative efficacy of cognitive and behavioral bibliotherapy for mildly and moderately depressed older adults. Journal of Consulting and Clinical Psychology. 1989;57(3):403-7.</t>
         </is>
       </c>
       <c r="C234" t="b">
@@ -7312,12 +8131,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Scogin, 1989</t>
+          <t>Scogin, 2018</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Scogin F, Jamison C, Gochneaur K. Comparative efficacy of cognitive and behavioral bibliotherapy for mildly and moderately depressed older adults. Journal of Consulting and Clinical Psychology. 1989;57(3):403-7.</t>
+          <t>Scogin F, Lichstein K, DiNapoli EA, et al. Effects of integrated telehealth-delivered cognitive-behavioral therapy for depression and insomnia in rural older adults. Journal of psychotherapy integration 2018; 28(3): 292‐309.</t>
         </is>
       </c>
       <c r="C235" t="b">
@@ -7327,12 +8146,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Scogin, 2018</t>
+          <t>Scott, 1990</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Scogin F, Lichstein K, DiNapoli EA, et al. Effects of integrated telehealth-delivered cognitive-behavioral therapy for depression and insomnia in rural older adults. Journal of psychotherapy integration 2018; 28(3): 292‐309.</t>
+          <t>Scott MJ, Stradling SG. Group cognitive therapy for depression produces clinically significant reliable change in community-based settings. Behavioural Psychotherapy. 1990;18(01):1-19.</t>
         </is>
       </c>
       <c r="C236" t="b">
@@ -7342,12 +8161,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Scott, 1990</t>
+          <t>Selmi, 1990</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Scott MJ, Stradling SG. Group cognitive therapy for depression produces clinically significant reliable change in community-based settings. Behavioural Psychotherapy. 1990;18(01):1-19.</t>
+          <t>Selmi PM, Klein MH, Greist JH, Sorrell SP, Erdman HP. Computer-administered cognitive-behavioral therapy for depression. American Journal of Psychiatry. 1990;147(1):51-6.</t>
         </is>
       </c>
       <c r="C237" t="b">
@@ -7357,12 +8176,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Selmi, 1990</t>
+          <t>Serfaty, 2009</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Selmi PM, Klein MH, Greist JH, Sorrell SP, Erdman HP. Computer-administered cognitive-behavioral therapy for depression. American Journal of Psychiatry. 1990;147(1):51-6.</t>
+          <t>Serfaty MA, Haworth D, Blanchard M, Buszewicz M, Murad S, King M. Clinical effectiveness of individual cognitive behavioral therapy for depressed older people in primary care: A randomized controlled trial. Archives of General Psychiatry. 2009;66(12):1332-40.</t>
         </is>
       </c>
       <c r="C238" t="b">
@@ -7372,12 +8191,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Serfaty, 2009</t>
+          <t>Serfaty, 2019</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Serfaty MA, Haworth D, Blanchard M, Buszewicz M, Murad S, King M. Clinical effectiveness of individual cognitive behavioral therapy for depressed older people in primary care: A randomized controlled trial. Archives of General Psychiatry. 2009;66(12):1332-40.</t>
+          <t>Serfaty, M., King, M., Nazareth, I., Moorey, S., Aspden, T., Tookman, A., . . . Jones, L. (2019). Manualised cognitive and behavioural therapy in treating depression in advanced cancer: the CanTalk RCT. Health Technology Assessment, 23(19), 1‐106. doi:10.3310/hta23190</t>
         </is>
       </c>
       <c r="C239" t="b">
@@ -7387,12 +8206,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Serfaty, 2019</t>
+          <t>Serrano, 2004</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Serfaty, M., King, M., Nazareth, I., Moorey, S., Aspden, T., Tookman, A., . . . Jones, L. (2019). Manualised cognitive and behavioural therapy in treating depression in advanced cancer: the CanTalk RCT. Health Technology Assessment, 23(19), 1‐106. doi:10.3310/hta23190</t>
+          <t>Serrano JP, Latorre JM, Gatz M, Montanes J. Life review therapy using autobiographical retrieval practice for older adults with depressive symptomatology. Psychology and Aging. 2004;19(2):270-7.</t>
         </is>
       </c>
       <c r="C240" t="b">
@@ -7402,7 +8221,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Serrano Selva, 2012</t>
+          <t>Serrano, 2012</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7417,12 +8236,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Serrano, 2004</t>
+          <t>Shapiro, 1990</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Serrano JP, Latorre JM, Gatz M, Montanes J. Life review therapy using autobiographical retrieval practice for older adults with depressive symptomatology. Psychology and Aging. 2004;19(2):270-7.</t>
+          <t>Shapiro DA, Barkham M, Hardy GE, Morrison LA. The Second Sheffield Psychotherapy Project: rationale, design and preliminary outcome data. The British journal of medical psychology. 1990;63(2):97-108.</t>
         </is>
       </c>
       <c r="C242" t="b">
@@ -7432,12 +8251,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Shapiro, 1990</t>
+          <t>Shaw, 1977</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Shapiro DA, Barkham M, Hardy GE, Morrison LA. The Second Sheffield Psychotherapy Project: rationale, design and preliminary outcome data. The British journal of medical psychology. 1990;63(2):97-108.</t>
+          <t>Shaw BF. Comparison of cognitive therapy and behavior therapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 1977;45(4):543.</t>
         </is>
       </c>
       <c r="C243" t="b">
@@ -7447,12 +8266,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Shaw, 1977</t>
+          <t>Sheeber, 2012</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Shaw BF. Comparison of cognitive therapy and behavior therapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 1977;45(4):543.</t>
+          <t>Sheeber LB, Seeley JR, Feil EG, Davis B, Sorensen E, Kosty DB, et al. Development and pilot evaluation of an Internet-facilitated cognitive-behavioral intervention for maternal depression. Journal of Consulting and Clinical Psychology. 2012;80(5):739-49.</t>
         </is>
       </c>
       <c r="C244" t="b">
@@ -7462,12 +8281,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Sheeber, 2012</t>
+          <t>Sikander, 2019</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sheeber LB, Seeley JR, Feil EG, Davis B, Sorensen E, Kosty DB, et al. Development and pilot evaluation of an Internet-facilitated cognitive-behavioral intervention for maternal depression. Journal of Consulting and Clinical Psychology. 2012;80(5):739-49.</t>
+          <t>Sikander, S., Ahmad, I., Atif, N., Zaidi, A., Vanobberghen, F., Weiss, H. A., . . . Rahman, A. (2019). Delivering the Thinking Healthy Programme for perinatal depression through volunteer peers: a cluster randomised controlled trial in Pakistan. The Lancet Psychiatry, 6(2), 128-139. doi:10.1016/S2215-0366(18)30467-X</t>
         </is>
       </c>
       <c r="C245" t="b">
@@ -7477,12 +8296,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Sikander, 2019</t>
+          <t>Simoni, 2013</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Sikander, S., Ahmad, I., Atif, N., Zaidi, A., Vanobberghen, F., Weiss, H. A., . . . Rahman, A. (2019). Delivering the Thinking Healthy Programme for perinatal depression through volunteer peers: a cluster randomised controlled trial in Pakistan. The Lancet Psychiatry, 6(2), 128-139. doi:10.1016/S2215-0366(18)30467-X</t>
+          <t>Simoni JM, Wiebe JS, Sauceda JA, Huh D, Sanchez G, Longoria V, et al. A preliminary RCT of CBT-AD for adherence and depression among HIV-positive Latinos on the U.S.-Mexico border: The Nuevo Dia study. AIDS and behavior. 2013;17(8):2816-29.</t>
         </is>
       </c>
       <c r="C246" t="b">
@@ -7492,12 +8311,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Simoni, 2013</t>
+          <t>Simpson, 2003</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Simoni JM, Wiebe JS, Sauceda JA, Huh D, Sanchez G, Longoria V, et al. A preliminary RCT of CBT-AD for adherence and depression among HIV-positive Latinos on the U.S.-Mexico border: The Nuevo Dia study. AIDS and behavior. 2013;17(8):2816-29.</t>
+          <t>Simpson S, Corney R, Beecham J. A randomized controlled trial to evaluate the effectiveness and cost-effectiveness of psychodynamic counselling for general practice patients with chronic depression. Psychological Medicine. 2003;33(2):229-39.</t>
         </is>
       </c>
       <c r="C247" t="b">
@@ -7507,12 +8326,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Simpson, 2003</t>
+          <t>Simson, 2008</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Simpson S, Corney R, Beecham J. A randomized controlled trial to evaluate the effectiveness and cost-effectiveness of psychodynamic counselling for general practice patients with chronic depression. Psychological Medicine. 2003;33(2):229-39.</t>
+          <t>Simson U, Nawarotzky U, Friese G, Porck W, Schottenfeld-Naor Y, Hahn S, et al. Psychotherapy intervention to reduce depressive symptoms in patients with diabetic foot syndrome. Diabetic Medicine. 2008;25(2):206-12.</t>
         </is>
       </c>
       <c r="C248" t="b">
@@ -7522,12 +8341,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Simson, 2008</t>
+          <t>Sinniah, 2017</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Simson U, Nawarotzky U, Friese G, Porck W, Schottenfeld-Naor Y, Hahn S, et al. Psychotherapy intervention to reduce depressive symptoms in patients with diabetic foot syndrome. Diabetic Medicine. 2008;25(2):206-12.</t>
+          <t>Sinniah, A., Oei, T., Maniam, T., &amp; Subramaniam, P. (2017). Positive effects of Individual Cognitive Behavior Therapy for patients with unipolar mood disorders with suicidal ideation in Malaysia: a randomised controlled trial. Psychiatry research, 254, 179-189.</t>
         </is>
       </c>
       <c r="C249" t="b">
@@ -7537,12 +8356,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Sinniah, 2017</t>
+          <t>Sloane, 1985</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Sinniah, A., Oei, T., Maniam, T., &amp; Subramaniam, P. (2017). Positive effects of Individual Cognitive Behavior Therapy for patients with unipolar mood disorders with suicidal ideation in Malaysia: a randomised controlled trial. Psychiatry research, 254, 179-189.</t>
+          <t>Sloane R, Staples F, Schneider L. Interpersonal therapy versus nortriptyline for depression in the elderly. Clinical and Pharmacological Studies in Psychiatric Disorders. 1985:344-6.</t>
         </is>
       </c>
       <c r="C250" t="b">
@@ -7552,12 +8371,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Sloane, 1985</t>
+          <t>Smit, 2006</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Sloane R, Staples F, Schneider L. Interpersonal therapy versus nortriptyline for depression in the elderly. Clinical and Pharmacological Studies in Psychiatric Disorders. 1985:344-6.</t>
+          <t>Smit A, Kluiter H, Conradi HJ, Meer K, Tiemens BG, Jenner JA, et al. Short-term effects of enhanced treatment for depression in primary care: Results from a randomized controlled trial. Psychological Medicine. 2006;36(1):15-26.</t>
         </is>
       </c>
       <c r="C251" t="b">
@@ -7567,12 +8386,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Smit, 2006</t>
+          <t>Smith, 2017</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Smit A, Kluiter H, Conradi HJ, Meer K, Tiemens BG, Jenner JA, et al. Short-term effects of enhanced treatment for depression in primary care: Results from a randomized controlled trial. Psychological Medicine. 2006;36(1):15-26.</t>
+          <t>Smith, J., Newby, J. M., Burston, N., Murphy, M. J., Michael, S., Mackenzie, A., . . . Andrews, G. (2017). Help from home for depression: A randomised controlled trial comparing internet-delivered cognitive behaviour therapy with bibliotherapy for depression. Internet Interventions, 9, 25-37.</t>
         </is>
       </c>
       <c r="C252" t="b">
@@ -7582,12 +8401,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Smith, 2017</t>
+          <t>Soares, 2018</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Smith, J., Newby, J. M., Burston, N., Murphy, M. J., Michael, S., Mackenzie, A., . . . Andrews, G. (2017). Help from home for depression: A randomised controlled trial comparing internet-delivered cognitive behaviour therapy with bibliotherapy for depression. Internet Interventions, 9, 25-37.</t>
+          <t>Soares MC, Mondin TC, Silva G, et al. Comparison of Clinical Significance of Cognitive-Behavioral Therapy and Psychodynamic Therapy for Major Depressive Disorder: a Randomized Clinical Trial. Journal of nervous and mental disease 2018; 206(9): 686‐93.</t>
         </is>
       </c>
       <c r="C253" t="b">
@@ -7597,12 +8416,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Soares, 2018</t>
+          <t>Songprakun, 2012</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Soares MC, Mondin TC, Silva G, et al. Comparison of Clinical Significance of Cognitive-Behavioral Therapy and Psychodynamic Therapy for Major Depressive Disorder: a Randomized Clinical Trial. Journal of nervous and mental disease 2018; 206(9): 686‐93.</t>
+          <t>Songprakun W, McCann TV. Evaluation of a cognitive behavioural self-help manual for reducing depression: A randomized controlled trial. Journal of psychiatric and mental health nursing. 2012;19(7):647-53.</t>
         </is>
       </c>
       <c r="C254" t="b">
@@ -7612,12 +8431,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Songprakun, 2012</t>
+          <t>Spek, 2007</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Songprakun W, McCann TV. Evaluation of a cognitive behavioural self-help manual for reducing depression: A randomized controlled trial. Journal of psychiatric and mental health nursing. 2012;19(7):647-53.</t>
+          <t>Spek V, Nyklicek I, Smits N, Cuijpers P, Riper H, Keyzer J, et al. Internet-based cognitive behavioural therapy for subthreshold depression in people over 50 years old: A randomized controlled clinical trial. Psychological Medicine. 2007;37(12):1797-806.</t>
         </is>
       </c>
       <c r="C255" t="b">
@@ -7627,12 +8446,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Spek, 2007</t>
+          <t>Stiles-Shields, 2018</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Spek V, Nyklicek I, Smits N, Cuijpers P, Riper H, Keyzer J, et al. Internet-based cognitive behavioural therapy for subthreshold depression in people over 50 years old: A randomized controlled clinical trial. Psychological Medicine. 2007;37(12):1797-806.</t>
+          <t>Stiles-Shields C, Montague E, Kwasny MJ, Mohr DC. Behavioral and cognitive intervention strategies delivered via coached apps for depression: Pilot trial. Psychological Services 2018.</t>
         </is>
       </c>
       <c r="C256" t="b">
@@ -7642,12 +8461,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Stiles-Shields, 2018</t>
+          <t>Strauss, 2012</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Stiles-Shields C, Montague E, Kwasny MJ, Mohr DC. Behavioral and cognitive intervention strategies delivered via coached apps for depression: Pilot trial. Psychological Services 2018.</t>
+          <t>Strauss C, Hayward M, Chadwick P. Group person-based cognitive therapy for chronic depression: A pilot randomized controlled trial. British Journal of Clinical Psychology. 2012;51(3):345-50.</t>
         </is>
       </c>
       <c r="C257" t="b">
@@ -7657,12 +8476,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Strauss, 2012</t>
+          <t>Strong, 2008</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Strauss C, Hayward M, Chadwick P. Group person-based cognitive therapy for chronic depression: A pilot randomized controlled trial. British Journal of Clinical Psychology. 2012;51(3):345-50.</t>
+          <t>Strong V, Waters R, Hibberd C, Murray G, Wall L, Walker J, et al. Management of depression for people with cancer (SMaRT oncology 1): A randomised trial. Lancet. 2008;372(9632):40-8.</t>
         </is>
       </c>
       <c r="C258" t="b">
@@ -7672,12 +8491,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Strong, 2008</t>
+          <t>Swartz, 2008</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Strong V, Waters R, Hibberd C, Murray G, Wall L, Walker J, et al. Management of depression for people with cancer (SMaRT oncology 1): A randomised trial. Lancet. 2008;372(9632):40-8.</t>
+          <t>Swartz HA, Frank E, Zuckoff A, Cyranowski JM, Houck PR, Cheng Y, et al. Brief interpersonal psychotherapy for depressed mothers whose children are receiving psychiatric treatment. American Journal of Psychiatry. 2008;165(9):1155-62.</t>
         </is>
       </c>
       <c r="C259" t="b">
@@ -7687,12 +8506,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Swartz, 2008</t>
+          <t>Takagaki, 2016</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Swartz HA, Frank E, Zuckoff A, Cyranowski JM, Houck PR, Cheng Y, et al. Brief interpersonal psychotherapy for depressed mothers whose children are receiving psychiatric treatment. American Journal of Psychiatry. 2008;165(9):1155-62.</t>
+          <t>Takagaki K, Okamoto Y, Jinnin R, Mori A, Nishiyama Y, Yamamura T, et al. Behavioral activation for late adolescents with subthreshold depression: A randomized controlled trial. European Child and Adolescent Psychiatry. 2016;25(11):1171-82.</t>
         </is>
       </c>
       <c r="C260" t="b">
@@ -7702,12 +8521,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Takagaki, 2016</t>
+          <t>Talbot, 2011</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Takagaki K, Okamoto Y, Jinnin R, Mori A, Nishiyama Y, Yamamura T, et al. Behavioral activation for late adolescents with subthreshold depression: A randomized controlled trial. European Child and Adolescent Psychiatry. 2016;25(11):1171-82.</t>
+          <t>Talbot NL, Chaudron LH, Ward EA, Duberstein PR, Conwell Y, O'Hara MW, et al. A randomized effectiveness trial of interpersonal psychotherapy for depressed women with sexual abuse histories. Psychiatric Services. 2011;62(4):374-80.</t>
         </is>
       </c>
       <c r="C261" t="b">
@@ -7717,12 +8536,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Talbot, 2011</t>
+          <t>Taylor, 1977</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Talbot NL, Chaudron LH, Ward EA, Duberstein PR, Conwell Y, O'Hara MW, et al. A randomized effectiveness trial of interpersonal psychotherapy for depressed women with sexual abuse histories. Psychiatric Services. 2011;62(4):374-80.</t>
+          <t>Taylor FG, Marshall WL. Experimental analysis of a cognitive-behavioral therapy for depression. Cognitive Therapy and Research. 1977;1(1):59-72.</t>
         </is>
       </c>
       <c r="C262" t="b">
@@ -7732,12 +8551,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Taylor, 1977</t>
+          <t>Taylor, 2009</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Taylor FG, Marshall WL. Experimental analysis of a cognitive-behavioral therapy for depression. Cognitive Therapy and Research. 1977;1(1):59-72.</t>
+          <t>Taylor CB, Conrad A, Wilhelm FH, Strachowski D, Khaylis A, Neri E, et al. Does improving mood in depressed patients alter factors that may affect cardiovascular disease risk? Journal of Psychiatric Research. 2009;43(16):1246-52.</t>
         </is>
       </c>
       <c r="C263" t="b">
@@ -7747,12 +8566,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Taylor, 2009</t>
+          <t>Teasdale, 1984</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Taylor CB, Conrad A, Wilhelm FH, Strachowski D, Khaylis A, Neri E, et al. Does improving mood in depressed patients alter factors that may affect cardiovascular disease risk? Journal of Psychiatric Research. 2009;43(16):1246-52.</t>
+          <t>Teasdale JD, Fennell MJ, Hibbert GA, Amies PL. Cognitive therapy for major depressive disorder in primary care. The British Journal of Psychiatry. 1984;144:400-6.</t>
         </is>
       </c>
       <c r="C264" t="b">
@@ -7762,12 +8581,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Teasdale, 1984</t>
+          <t>Teichman, 1995</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Teasdale JD, Fennell MJ, Hibbert GA, Amies PL. Cognitive therapy for major depressive disorder in primary care. The British Journal of Psychiatry. 1984;144:400-6.</t>
+          <t>Teichman Y, Bar-el Z, Shor H, Sirota P, Elizur A. A comparison of two modalities of cognitive therapy (individual and marital) in treating depression. Psychiatry. 1995;58(2):136-48.</t>
         </is>
       </c>
       <c r="C265" t="b">
@@ -7777,12 +8596,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Teichman, 1995</t>
+          <t>Teri, 1997</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Teichman Y, Bar-el Z, Shor H, Sirota P, Elizur A. A comparison of two modalities of cognitive therapy (individual and marital) in treating depression. Psychiatry. 1995;58(2):136-48.</t>
+          <t>Teri L, Logsdon RG, Uomoto J, McCurry SM. Behavioral treatment of depression in dementia patients: A controlled clinical trial. The journals of gerontology Series B, Psychological sciences and social sciences. 1997;52(4):P159-66.</t>
         </is>
       </c>
       <c r="C266" t="b">
@@ -7792,12 +8611,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Teri, 1997</t>
+          <t>Thomas, 2019</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Teri L, Logsdon RG, Uomoto J, McCurry SM. Behavioral treatment of depression in dementia patients: A controlled clinical trial. The journals of gerontology Series B, Psychological sciences and social sciences. 1997;52(4):P159-66.</t>
+          <t>Thomas, S. A., Drummond, A. E., Lincoln, N. B., Palmer, R. L., das Nair, R., Latimer, N. R., . . . Topcu, G. (2019). Behavioural activation therapy for post-stroke depression: the BEADS feasibility RCT. Health Technol Assess, 23(47), 1-176. doi:10.3310/hta23470</t>
         </is>
       </c>
       <c r="C267" t="b">
@@ -7807,12 +8626,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Thomas, 2019</t>
+          <t>Thompson, 1987</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Thomas, S. A., Drummond, A. E., Lincoln, N. B., Palmer, R. L., das Nair, R., Latimer, N. R., . . . Topcu, G. (2019). Behavioural activation therapy for post-stroke depression: the BEADS feasibility RCT. Health Technol Assess, 23(47), 1-176. doi:10.3310/hta23470</t>
+          <t>Thompson LW, Gallagher D, Breckenridge JS. Comparative effectiveness of psychotherapies for depressed elders. Journal of Consulting and Clinical Psychology. 1987;55(3):385.</t>
         </is>
       </c>
       <c r="C268" t="b">
@@ -7822,12 +8641,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Thompson, 1987</t>
+          <t>Titov, 2010</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Thompson LW, Gallagher D, Breckenridge JS. Comparative effectiveness of psychotherapies for depressed elders. Journal of Consulting and Clinical Psychology. 1987;55(3):385.</t>
+          <t>Titov N, Andrews G, Davies M, McIntyre K, Robinson E, Solley K. Internet treatment for depression: A randomized controlled trial comparing clinician vs. technician assistance. PLoS One. 2010;5(6):e10939.</t>
         </is>
       </c>
       <c r="C269" t="b">
@@ -7837,12 +8656,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Titov, 2010</t>
+          <t>Titov, 2015</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Titov N, Andrews G, Davies M, McIntyre K, Robinson E, Solley K. Internet treatment for depression: A randomized controlled trial comparing clinician vs. technician assistance. PLoS One. 2010;5(6):e10939.</t>
+          <t>Titov N, Dear BF, Ali S, Zou JB, Lorian CN, Johnston L, et al. Clinical and cost-effectiveness of therapist-guided internet-delivered cognitive behavior therapy for older adults with symptoms of depression: A randomized controlled trial. Behavior Therapy. 2015;46(2):193-205.</t>
         </is>
       </c>
       <c r="C270" t="b">
@@ -7852,12 +8671,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Titov, 2015</t>
+          <t>Tomasino, 2017</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Titov N, Dear BF, Ali S, Zou JB, Lorian CN, Johnston L, et al. Clinical and cost-effectiveness of therapist-guided internet-delivered cognitive behavior therapy for older adults with symptoms of depression: A randomized controlled trial. Behavior Therapy. 2015;46(2):193-205.</t>
+          <t>Tomasino, K., Lattie, E., Ho, J., Palac, H., Kaiser, S., &amp; Mohr, D. (2017). Harnessing Peer Support in an Online Intervention for Older Adults with Depression. American Journal of Geriatric Psychiatry, 25(10), 1109-1119.</t>
         </is>
       </c>
       <c r="C271" t="b">
@@ -7867,12 +8686,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Tomasino, 2017</t>
+          <t>Tong, 2019</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Tomasino, K., Lattie, E., Ho, J., Palac, H., Kaiser, S., &amp; Mohr, D. (2017). Harnessing Peer Support in an Online Intervention for Older Adults with Depression. American Journal of Geriatric Psychiatry, 25(10), 1109-1119.</t>
+          <t>Tong, P., Bu, P., Yang, Y., Dong, L., Sun, T., &amp; Shi, Y. (2019). Group cognitive behavioural therapy can reduce stigma and improve treatment compliance in major depressive disorder patients. Early intervention in psychiatry. doi:10.1111/eip.12841</t>
         </is>
       </c>
       <c r="C272" t="b">
@@ -7882,12 +8701,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Tong, 2019</t>
+          <t>Tovote, 2014</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Tong, P., Bu, P., Yang, Y., Dong, L., Sun, T., &amp; Shi, Y. (2019). Group cognitive behavioural therapy can reduce stigma and improve treatment compliance in major depressive disorder patients. Early intervention in psychiatry. doi:10.1111/eip.12841</t>
+          <t>Tovote KA, Fleer J, Snippe E, Peeters A, Emmelkamp PMG, Sanderman R, et al. Individual mindfulness-based cognitive therapy and cognitive behavior therapy for treating depressive symptoms in patients with diabetes: Results of a randomized controlled trial. Diabetes care. 2014;37(9):2427-34.</t>
         </is>
       </c>
       <c r="C273" t="b">
@@ -7897,12 +8716,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Tovote, 2014</t>
+          <t>Town, 2017</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Tovote KA, Fleer J, Snippe E, Peeters A, Emmelkamp PMG, Sanderman R, et al. Individual mindfulness-based cognitive therapy and cognitive behavior therapy for treating depressive symptoms in patients with diabetes: Results of a randomized controlled trial. Diabetes care. 2014;37(9):2427-34.</t>
+          <t>Town, J., Abbass, A., Stride, C., &amp; Bernier, D. (2017). A randomised controlled trial of Intensive Short-Term Dynamic Psychotherapy for treatment resistant depression: the Halifax Depression Study. Journal of Affective Disorders, 214, 15-25.</t>
         </is>
       </c>
       <c r="C274" t="b">
@@ -7912,12 +8731,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Town, 2017</t>
+          <t>Tulbure, 2018</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Town, J., Abbass, A., Stride, C., &amp; Bernier, D. (2017). A randomised controlled trial of Intensive Short-Term Dynamic Psychotherapy for treatment resistant depression: the Halifax Depression Study. Journal of Affective Disorders, 214, 15-25.</t>
+          <t>Tulbure BT, Andersson G, Salagean N, Pearce M, Koenig HG. Religious versus Conventional Internet-based Cognitive Behavioral Therapy for Depression. J Relig Health 2018; 57(5): 1634-48.</t>
         </is>
       </c>
       <c r="C275" t="b">
@@ -7927,12 +8746,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Tulbure, 2018</t>
+          <t>Turner, 1979</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Tulbure BT, Andersson G, Salagean N, Pearce M, Koenig HG. Religious versus Conventional Internet-based Cognitive Behavioral Therapy for Depression. J Relig Health 2018; 57(5): 1634-48.</t>
+          <t>Turner RW, Ward MF, Turner DJ. Behavioral treatment for depression: An evaluation of therapeutic components. Journal of clinical psychology. 1979;35(1):166-75.</t>
         </is>
       </c>
       <c r="C276" t="b">
@@ -7942,12 +8761,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Turner, 1979</t>
+          <t>Unlu, 2013</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Turner RW, Ward MF, Turner DJ. Behavioral treatment for depression: An evaluation of therapeutic components. Journal of clinical psychology. 1979;35(1):166-75.</t>
+          <t>Unlu Ince B, Cuijpers P, t Hof E, Ballegooijen W, Christensen H, Riper H. Internet-based, culturally sensitive, problem-solving therapy for Turkish migrants with depression: Randomized controlled trial. Journal of Medical Internet Research. 2013;15(10):e227.</t>
         </is>
       </c>
       <c r="C277" t="b">
@@ -7957,12 +8776,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Unlu, 2013</t>
+          <t>Van Bastelaar, 2011</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Unlu Ince B, Cuijpers P, t Hof E, Ballegooijen W, Christensen H, Riper H. Internet-based, culturally sensitive, problem-solving therapy for Turkish migrants with depression: Randomized controlled trial. Journal of Medical Internet Research. 2013;15(10):e227.</t>
+          <t>van Bastelaar KM, Pouwer F, Cuijpers P, Riper H, Snoek FJ. Web-based depression treatment for type 1 and type 2 diabetic patients: A randomized, controlled trial. Diabetes care. 2011;34(2):320-5.</t>
         </is>
       </c>
       <c r="C278" t="b">
@@ -7972,12 +8791,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Van Bastelaar, 2011</t>
+          <t>Van Schaik, 2006</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>van Bastelaar KM, Pouwer F, Cuijpers P, Riper H, Snoek FJ. Web-based depression treatment for type 1 and type 2 diabetic patients: A randomized, controlled trial. Diabetes care. 2011;34(2):320-5.</t>
+          <t>van Schaik A, van Marwijk H, Adèr H, van Dyck R, de Haan M, Penninx B, et al. Interpersonal psychotherapy for elderly patients in primary care. The American Journal of Geriatric Psychiatry. 2006;14(9):777-86.</t>
         </is>
       </c>
       <c r="C279" t="b">
@@ -7987,12 +8806,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Van Schaik, 2006</t>
+          <t>Vazquez, 2013</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>van Schaik A, van Marwijk H, Adèr H, van Dyck R, de Haan M, Penninx B, et al. Interpersonal psychotherapy for elderly patients in primary care. The American Journal of Geriatric Psychiatry. 2006;14(9):777-86.</t>
+          <t>Vázquez González FL, Otero Otero P, Torres Iglesias A, Hermida Garcìa E, Blanco Seoane V, Dìaz Fernández O. A brief problem-solving indicated-prevention intervention for prevention of depression in nonprofessional caregivers. Psicothema. 2013;25(1):87-92.</t>
         </is>
       </c>
       <c r="C280" t="b">
@@ -8002,12 +8821,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Vazquez, 2013</t>
+          <t>Verduyn, 2003</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Vázquez González FL, Otero Otero P, Torres Iglesias A, Hermida Garcìa E, Blanco Seoane V, Dìaz Fernández O. A brief problem-solving indicated-prevention intervention for prevention of depression in nonprofessional caregivers. Psicothema. 2013;25(1):87-92.</t>
+          <t>Verduyn C, Barrowclough C, Roberts J, Tarrier N, Harrington R. Maternal depression and child behaviour problems: Randomised placebo-controlled trial of a cognitive-behavioural group intervention. British Journal of Psychiatry. 2003;183(OCT.):342-8.</t>
         </is>
       </c>
       <c r="C281" t="b">
@@ -8017,12 +8836,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Verduyn, 2003</t>
+          <t>Vázquez, 2017</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Verduyn C, Barrowclough C, Roberts J, Tarrier N, Harrington R. Maternal depression and child behaviour problems: Randomised placebo-controlled trial of a cognitive-behavioural group intervention. British Journal of Psychiatry. 2003;183(OCT.):342-8.</t>
+          <t>Vázquez, F. L., Torres, Á., Otero, P., Blanco, V., Díaz, O., &amp; Estévez, L. E. (2017). Analysis of the components of a cognitive-behavioral intervention administered via conference call for preventing depression among non-professional caregivers: A pilot study. Aging Ment Health, 21(9), 938-946.</t>
         </is>
       </c>
       <c r="C282" t="b">
@@ -8032,12 +8851,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Vázquez, 2017</t>
+          <t>Warmerdam, 2008</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Vázquez, F. L., Torres, Á., Otero, P., Blanco, V., Díaz, O., &amp; Estévez, L. E. (2017). Analysis of the components of a cognitive-behavioral intervention administered via conference call for preventing depression among non-professional caregivers: A pilot study. Aging Ment Health, 21(9), 938-946.</t>
+          <t>Warmerdam L, Straten A, Twisk J, Riper H, Cuijpers P. Internet-based treatment for adults with depressive symptoms: Randomized controlled trial. Journal of Medical Internet Research. 2008;10(4):e44.</t>
         </is>
       </c>
       <c r="C283" t="b">
@@ -8047,12 +8866,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Warmerdam, 2008</t>
+          <t>Watson, 2003</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Warmerdam L, Straten A, Twisk J, Riper H, Cuijpers P. Internet-based treatment for adults with depressive symptoms: Randomized controlled trial. Journal of Medical Internet Research. 2008;10(4):e44.</t>
+          <t>Watson JC, Gordon LB, Stermac L, Kalogerakos F, Steckley P. Comparing the effectiveness of process-experiential with cognitive-behavioral psychotherapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 2003;71(4):773-81.</t>
         </is>
       </c>
       <c r="C284" t="b">
@@ -8062,12 +8881,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Watson, 2003</t>
+          <t>Westerhof, 2019</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Watson JC, Gordon LB, Stermac L, Kalogerakos F, Steckley P. Comparing the effectiveness of process-experiential with cognitive-behavioral psychotherapy in the treatment of depression. Journal of Consulting and Clinical Psychology. 2003;71(4):773-81.</t>
+          <t>Westerhof, G. J., Lamers, S. M. A., Postel, M. G., &amp; Bohlmeijer, E. T. (2019). Online Therapy for Depressive Symptoms: An Evaluation of Counselor-Led and Peer-Supported Life Review Therapy. The Gerontologist, 59(1), 135-146. doi:10.1093/geront/gnx140</t>
         </is>
       </c>
       <c r="C285" t="b">
@@ -8077,12 +8896,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Westerhof, 2019</t>
+          <t>Wickberg, 1996</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Westerhof, G. J., Lamers, S. M. A., Postel, M. G., &amp; Bohlmeijer, E. T. (2019). Online Therapy for Depressive Symptoms: An Evaluation of Counselor-Led and Peer-Supported Life Review Therapy. The Gerontologist, 59(1), 135-146. doi:10.1093/geront/gnx140</t>
+          <t>Wickberg B, Hwang CP. Counselling of postnatal depression: A controlled study on a population based Swedish sample. Journal of Affective Disorders. 1996;39(3):209-16.</t>
         </is>
       </c>
       <c r="C286" t="b">
@@ -8092,12 +8911,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Wickberg, 1996</t>
+          <t>Wiklund, 2010</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Wickberg B, Hwang CP. Counselling of postnatal depression: A controlled study on a population based Swedish sample. Journal of Affective Disorders. 1996;39(3):209-16.</t>
+          <t>Wiklund I, Mohlkert P, Edman G. Evaluation of a brief cognitive intervention in patients with signs of postnatal depression: A randomized controlled trial. Acta obstetricia et gynecologica Scandinavica. 2010;89(8):1100-4.</t>
         </is>
       </c>
       <c r="C287" t="b">
@@ -8107,12 +8926,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Wiklund, 2010</t>
+          <t>Williams, 2000</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Wiklund I, Mohlkert P, Edman G. Evaluation of a brief cognitive intervention in patients with signs of postnatal depression: A randomized controlled trial. Acta obstetricia et gynecologica Scandinavica. 2010;89(8):1100-4.</t>
+          <t>Williams JW, Barrett J, Oxman T, Frank E, Katon W, Sullivan M, et al. Treatment of dysthymia and minor depression in primary care: A randomized controlled trial in older adults. JAMA. 2000;284(12):1519-26.</t>
         </is>
       </c>
       <c r="C288" t="b">
@@ -8122,12 +8941,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Williams, 2000</t>
+          <t>Williams, 2013 I</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Williams JW, Barrett J, Oxman T, Frank E, Katon W, Sullivan M, et al. Treatment of dysthymia and minor depression in primary care: A randomized controlled trial in older adults. JAMA. 2000;284(12):1519-26.</t>
+          <t>Williams AD, Blackwell SE, Mackenzie A, Holmes EA, Andrews G. Combining imagination and reason in the treatment of depression: A randomized controlled trial of internet-based cognitive-bias modification and internet-CBT for depression. Journal of Consulting and Clinical Psychology. 2013;81(5):793-9.</t>
         </is>
       </c>
       <c r="C289" t="b">
@@ -8137,12 +8956,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Williams, 2013 I</t>
+          <t>Williams, 2013 II</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Williams AD, Blackwell SE, Mackenzie A, Holmes EA, Andrews G. Combining imagination and reason in the treatment of depression: A randomized controlled trial of internet-based cognitive-bias modification and internet-CBT for depression. Journal of Consulting and Clinical Psychology. 2013;81(5):793-9.</t>
+          <t>Williams C, Wilson P, Morrison J, McMahon A, Andrew W, Allan L, et al. Guided self-help cognitive behavioural therapy for depression in primary care: A randomised controlled trial. PLoS One. 2013;8(1):e52735.</t>
         </is>
       </c>
       <c r="C290" t="b">
@@ -8152,12 +8971,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Williams, 2013 II</t>
+          <t>Williams, 2018</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Williams C, Wilson P, Morrison J, McMahon A, Andrew W, Allan L, et al. Guided self-help cognitive behavioural therapy for depression in primary care: A randomised controlled trial. PLoS One. 2013;8(1):e52735.</t>
+          <t>Williams C, McClay CA, Matthews L, et al. Community-based group guided self-help intervention for low mood and stress: Randomised controlled trial. British Journal of Psychiatry 2018; 212(2): 88-95.</t>
         </is>
       </c>
       <c r="C291" t="b">
@@ -8167,12 +8986,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Williams, 2018</t>
+          <t>Wilson, 1983</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Williams C, McClay CA, Matthews L, et al. Community-based group guided self-help intervention for low mood and stress: Randomised controlled trial. British Journal of Psychiatry 2018; 212(2): 88-95.</t>
+          <t>Wilson PH, Goldin JC, Charbonneau-Powis M. Comparative efficacy of behavioral and cognitive treatments of depression. Cognitive Therapy and Research. 1983;7(2):111-24.</t>
         </is>
       </c>
       <c r="C292" t="b">
@@ -8182,12 +9001,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Wilson, 1983</t>
+          <t>Wollersheim, 1991</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Wilson PH, Goldin JC, Charbonneau-Powis M. Comparative efficacy of behavioral and cognitive treatments of depression. Cognitive Therapy and Research. 1983;7(2):111-24.</t>
+          <t>Wollersheim JP, Wilson GL. Group treatment of unipolar depression: A comparison of coping, supportive, bibliotherapy, and delayed treatment groups. Professional Psychology: Research and Practice. 1991;22(6):496.</t>
         </is>
       </c>
       <c r="C293" t="b">
@@ -8197,12 +9016,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Wollersheim, 1991</t>
+          <t>Wong I, 2008</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Wollersheim JP, Wilson GL. Group treatment of unipolar depression: A comparison of coping, supportive, bibliotherapy, and delayed treatment groups. Professional Psychology: Research and Practice. 1991;22(6):496.</t>
+          <t>Wong DF. Cognitive and health-related outcomes of group cognitive behavioural treatment for people with depressive symptoms in Hong Kong: Randomized wait-list control study. Australian and New Zealand Journal of Psychiatry. 2008;42(8):702-11.</t>
         </is>
       </c>
       <c r="C294" t="b">
@@ -8212,12 +9031,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Wong I, 2008</t>
+          <t>Wong II, 2008</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Wong DF. Cognitive and health-related outcomes of group cognitive behavioural treatment for people with depressive symptoms in Hong Kong: Randomized wait-list control study. Australian and New Zealand Journal of Psychiatry. 2008;42(8):702-11.</t>
+          <t>Wong DF. Cognitive behavioral treatment groups for people with chronic depression in Hong Kong: A randomized wait-list control design. Depression and anxiety. 2008;25(2):142-8.</t>
         </is>
       </c>
       <c r="C295" t="b">
@@ -8227,12 +9046,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Wong II, 2008</t>
+          <t>Wong, 2018</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Wong DF. Cognitive behavioral treatment groups for people with chronic depression in Hong Kong: A randomized wait-list control design. Depression and anxiety. 2008;25(2):142-8.</t>
+          <t>Wong SYS, Sun YY, Chan ATY, et al. Treating Subthreshold Depression in Primary Care: a Randomized Controlled Trial of Behavioral Activation With Mindfulness. Annals of family medicine 2018; 16(2): 111‐9.</t>
         </is>
       </c>
       <c r="C296" t="b">
@@ -8242,12 +9061,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Wong, 2018</t>
+          <t>Wuthrich, 2013</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Wong SYS, Sun YY, Chan ATY, et al. Treating Subthreshold Depression in Primary Care: a Randomized Controlled Trial of Behavioral Activation With Mindfulness. Annals of family medicine 2018; 16(2): 111‐9.</t>
+          <t>Wuthrich VM, Rapee RM. Randomised controlled trial of group cognitive behavioural therapy for comorbid anxiety and depression in older adults. Behaviour Research and Therapy. 2013;51(12):779-86.</t>
         </is>
       </c>
       <c r="C297" t="b">
@@ -8257,12 +9076,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Wuthrich, 2013</t>
+          <t>Xie, 2019</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Wuthrich VM, Rapee RM. Randomised controlled trial of group cognitive behavioural therapy for comorbid anxiety and depression in older adults. Behaviour Research and Therapy. 2013;51(12):779-86.</t>
+          <t>Xie, J., He, G., Ding, S., Pan, C., Zhang, X., Zhou, J., &amp; Iennaco, J. D. (2019). A randomized study on the effect of modified behavioral activation treatment for depressive symptoms in rural left-behind elderly. Psychotherapy research : journal of the Society for Psychotherapy Research, 29(3), 372-382. doi:10.1080/10503307.2017.1364444</t>
         </is>
       </c>
       <c r="C298" t="b">
@@ -8272,12 +9091,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Xie, 2019</t>
+          <t>Yeung, 2017</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Xie, J., He, G., Ding, S., Pan, C., Zhang, X., Zhou, J., &amp; Iennaco, J. D. (2019). A randomized study on the effect of modified behavioral activation treatment for depressive symptoms in rural left-behind elderly. Psychotherapy research : journal of the Society for Psychotherapy Research, 29(3), 372-382. doi:10.1080/10503307.2017.1364444</t>
+          <t>Yeung, A., Wang, F., Feng, F., Zhang, J., Cooper, A., Hong, L., . . . Fava, M. (2017). Outcomes of an online computerized cognitive behavioral treatment program for treating chinese patients with depression: A pilot study. Asian journal of psychiatry. doi:10.1016/j.ajp.2017</t>
         </is>
       </c>
       <c r="C299" t="b">
@@ -8287,12 +9106,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Yeung, 2017</t>
+          <t>Zemestani, 2016</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Yeung, A., Wang, F., Feng, F., Zhang, J., Cooper, A., Hong, L., . . . Fava, M. (2017). Outcomes of an online computerized cognitive behavioral treatment program for treating chinese patients with depression: A pilot study. Asian journal of psychiatry. doi:10.1016/j.ajp.2017</t>
+          <t>Zemestani M, Davoodi I, Honarmand MM, Zargar Y, Ottaviani C. Comparative effects of group metacognitive therapy versus behavioural activation in moderately depressed students. Journal of Mental Health. 2016;25(6):479-85.</t>
         </is>
       </c>
       <c r="C300" t="b">
@@ -8302,12 +9121,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Zemestani, 2016</t>
+          <t>Zemestani, 2019</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Zemestani M, Davoodi I, Honarmand MM, Zargar Y, Ottaviani C. Comparative effects of group metacognitive therapy versus behavioural activation in moderately depressed students. Journal of Mental Health. 2016;25(6):479-85.</t>
+          <t>Zemestani, M., &amp; Fazeli Nikoo, Z. (2019). Effectiveness of mindfulness-based cognitive therapy for comorbid depression and anxiety in pregnancy: a randomized controlled trial. Archives of Women's Mental Health. doi:10.1007/s00737-019-00962-8</t>
         </is>
       </c>
       <c r="C301" t="b">
@@ -8317,30 +9136,15 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Zemestani, 2019</t>
+          <t>Zettle, 1989</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Zemestani, M., &amp; Fazeli Nikoo, Z. (2019). Effectiveness of mindfulness-based cognitive therapy for comorbid depression and anxiety in pregnancy: a randomized controlled trial. Archives of Women's Mental Health. doi:10.1007/s00737-019-00962-8</t>
+          <t>Zettle RD, Rains JC. Group cognitive and contextual therapies in treatment of depression. Journal of clinical psychology. 1989;45(3):436-45.</t>
         </is>
       </c>
       <c r="C302" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>Zettle, 1989</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Zettle RD, Rains JC. Group cognitive and contextual therapies in treatment of depression. Journal of clinical psychology. 1989;45(3):436-45.</t>
-        </is>
-      </c>
-      <c r="C303" t="b">
         <v>0</v>
       </c>
     </row>
